--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\All City Tow\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\All City Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8581449-37D9-438F-80BC-8E9BB94B4CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9469291C-93C6-40B9-9A86-397878692D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="1065" windowWidth="24720" windowHeight="14235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23057,10 +23057,10 @@
         <v>29</v>
       </c>
       <c r="G800" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H800" s="2">
-        <v>0</v>
+        <v>5.8564814814814816E-3</v>
       </c>
       <c r="I800" s="1">
         <v>46083.761458333334</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\All City Tow\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\All City Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9469291C-93C6-40B9-9A86-397878692D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DFD8F9E-F97B-4508-B34B-07CAE18A545F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4018" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4013" uniqueCount="100">
   <si>
     <t>Company Name</t>
   </si>
@@ -22941,16 +22941,16 @@
         <v>29</v>
       </c>
       <c r="G796" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H796" s="2">
-        <v>0</v>
+        <v>5.2662037037037035E-3</v>
       </c>
       <c r="I796" s="1">
         <v>46083.759375000001</v>
       </c>
       <c r="J796">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K796" t="s">
         <v>11</v>
@@ -22979,7 +22979,7 @@
         <v>46083.760069444441</v>
       </c>
       <c r="J797">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K797" t="s">
         <v>11</v>
@@ -23008,7 +23008,7 @@
         <v>46083.760069444441</v>
       </c>
       <c r="J798">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K798" t="s">
         <v>11</v>
@@ -23037,7 +23037,7 @@
         <v>46083.760763888888</v>
       </c>
       <c r="J799">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K799" t="s">
         <v>11</v>
@@ -23124,7 +23124,7 @@
         <v>46083.762152777781</v>
       </c>
       <c r="J802">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K802" t="s">
         <v>11</v>
@@ -23153,7 +23153,7 @@
         <v>46083.762152777781</v>
       </c>
       <c r="J803">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K803" t="s">
         <v>11</v>
@@ -23182,7 +23182,7 @@
         <v>46083.76284722222</v>
       </c>
       <c r="J804">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K804" t="s">
         <v>11</v>
@@ -23211,7 +23211,7 @@
         <v>46083.763541666667</v>
       </c>
       <c r="J805">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K805" t="s">
         <v>11</v>
@@ -23287,25 +23287,25 @@
         <v>37</v>
       </c>
       <c r="C809">
-        <v>5023</v>
+        <v>3791</v>
       </c>
       <c r="D809" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F809" t="s">
         <v>29</v>
       </c>
       <c r="G809" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H809" s="2">
-        <v>0</v>
+        <v>7.1990740740740739E-3</v>
       </c>
       <c r="I809" s="1">
         <v>46083.764930555553</v>
       </c>
       <c r="J809">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K809" t="s">
         <v>11</v>
@@ -23316,25 +23316,25 @@
         <v>37</v>
       </c>
       <c r="C810">
-        <v>3791</v>
+        <v>2435</v>
       </c>
       <c r="D810" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="F810" t="s">
         <v>29</v>
       </c>
       <c r="G810" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H810" s="2">
-        <v>7.1990740740740739E-3</v>
+        <v>0</v>
       </c>
       <c r="I810" s="1">
-        <v>46083.764930555553</v>
+        <v>46083.765625</v>
       </c>
       <c r="J810">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K810" t="s">
         <v>11</v>
@@ -23345,25 +23345,25 @@
         <v>37</v>
       </c>
       <c r="C811">
-        <v>2435</v>
+        <v>2439</v>
       </c>
       <c r="D811" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F811" t="s">
         <v>29</v>
       </c>
       <c r="G811" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H811" s="2">
-        <v>0</v>
+        <v>4.8379629629629632E-3</v>
       </c>
       <c r="I811" s="1">
         <v>46083.765625</v>
       </c>
       <c r="J811">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K811" t="s">
         <v>11</v>
@@ -23374,10 +23374,10 @@
         <v>37</v>
       </c>
       <c r="C812">
-        <v>2439</v>
+        <v>2432</v>
       </c>
       <c r="D812" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F812" t="s">
         <v>29</v>
@@ -23386,10 +23386,10 @@
         <v>10</v>
       </c>
       <c r="H812" s="2">
-        <v>4.8379629629629632E-3</v>
+        <v>4.363425925925926E-3</v>
       </c>
       <c r="I812" s="1">
-        <v>46083.765625</v>
+        <v>46083.766319444447</v>
       </c>
       <c r="J812">
         <v>0</v>
@@ -23403,19 +23403,19 @@
         <v>37</v>
       </c>
       <c r="C813">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="D813" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F813" t="s">
         <v>29</v>
       </c>
       <c r="G813" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H813" s="2">
-        <v>4.363425925925926E-3</v>
+        <v>0</v>
       </c>
       <c r="I813" s="1">
         <v>46083.766319444447</v>
@@ -23428,39 +23428,39 @@
       </c>
     </row>
     <row r="814" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B814" t="s">
-        <v>37</v>
-      </c>
-      <c r="C814">
-        <v>2431</v>
-      </c>
-      <c r="D814" t="s">
-        <v>57</v>
-      </c>
-      <c r="F814" t="s">
+      <c r="H814" s="2"/>
+      <c r="I814" s="1"/>
+      <c r="K814" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="815" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B815" t="s">
+        <v>37</v>
+      </c>
+      <c r="C815">
+        <v>2772</v>
+      </c>
+      <c r="D815" t="s">
+        <v>77</v>
+      </c>
+      <c r="F815" t="s">
         <v>29</v>
       </c>
-      <c r="G814" t="s">
-        <v>14</v>
-      </c>
-      <c r="H814" s="2">
-        <v>0</v>
-      </c>
-      <c r="I814" s="1">
-        <v>46083.766319444447</v>
-      </c>
-      <c r="J814">
-        <v>0</v>
-      </c>
-      <c r="K814" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="815" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H815" s="2"/>
-      <c r="I815" s="1"/>
+      <c r="G815" t="s">
+        <v>10</v>
+      </c>
+      <c r="H815" s="2">
+        <v>4.7222222222222223E-3</v>
+      </c>
+      <c r="I815" s="1">
+        <v>46083.767013888886</v>
+      </c>
+      <c r="J815">
+        <v>0</v>
+      </c>
       <c r="K815" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="816" spans="2:11" x14ac:dyDescent="0.25">
@@ -23468,10 +23468,10 @@
         <v>37</v>
       </c>
       <c r="C816">
-        <v>2772</v>
+        <v>3482</v>
       </c>
       <c r="D816" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F816" t="s">
         <v>29</v>
@@ -23480,10 +23480,10 @@
         <v>10</v>
       </c>
       <c r="H816" s="2">
-        <v>4.7222222222222223E-3</v>
+        <v>5.6828703703703702E-3</v>
       </c>
       <c r="I816" s="1">
-        <v>46083.767013888886</v>
+        <v>46083.767708333333</v>
       </c>
       <c r="J816">
         <v>0</v>
@@ -23497,25 +23497,25 @@
         <v>37</v>
       </c>
       <c r="C817">
-        <v>3482</v>
+        <v>3807</v>
       </c>
       <c r="D817" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F817" t="s">
         <v>29</v>
       </c>
       <c r="G817" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H817" s="2">
-        <v>5.6828703703703702E-3</v>
+        <v>0</v>
       </c>
       <c r="I817" s="1">
         <v>46083.767708333333</v>
       </c>
       <c r="J817">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K817" t="s">
         <v>11</v>
@@ -23526,25 +23526,25 @@
         <v>37</v>
       </c>
       <c r="C818">
-        <v>3807</v>
+        <v>5204</v>
       </c>
       <c r="D818" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F818" t="s">
         <v>29</v>
       </c>
       <c r="G818" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H818" s="2">
-        <v>0</v>
+        <v>5.7754629629629631E-3</v>
       </c>
       <c r="I818" s="1">
-        <v>46083.767708333333</v>
+        <v>46083.76840277778</v>
       </c>
       <c r="J818">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K818" t="s">
         <v>11</v>
@@ -23555,10 +23555,10 @@
         <v>37</v>
       </c>
       <c r="C819">
-        <v>5204</v>
+        <v>2449</v>
       </c>
       <c r="D819" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="F819" t="s">
         <v>29</v>
@@ -23567,10 +23567,10 @@
         <v>10</v>
       </c>
       <c r="H819" s="2">
-        <v>5.7754629629629631E-3</v>
+        <v>5.8680555555555552E-3</v>
       </c>
       <c r="I819" s="1">
-        <v>46083.76840277778</v>
+        <v>46083.769097222219</v>
       </c>
       <c r="J819">
         <v>0</v>
@@ -23584,10 +23584,10 @@
         <v>37</v>
       </c>
       <c r="C820">
-        <v>2449</v>
+        <v>2418</v>
       </c>
       <c r="D820" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F820" t="s">
         <v>29</v>
@@ -23596,7 +23596,7 @@
         <v>10</v>
       </c>
       <c r="H820" s="2">
-        <v>5.8680555555555552E-3</v>
+        <v>5.37037037037037E-3</v>
       </c>
       <c r="I820" s="1">
         <v>46083.769097222219</v>
@@ -23613,25 +23613,25 @@
         <v>37</v>
       </c>
       <c r="C821">
-        <v>2418</v>
+        <v>2444</v>
       </c>
       <c r="D821" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F821" t="s">
         <v>29</v>
       </c>
       <c r="G821" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H821" s="2">
-        <v>5.37037037037037E-3</v>
+        <v>0</v>
       </c>
       <c r="I821" s="1">
-        <v>46083.769097222219</v>
+        <v>46083.769791666666</v>
       </c>
       <c r="J821">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K821" t="s">
         <v>11</v>
@@ -23642,10 +23642,10 @@
         <v>37</v>
       </c>
       <c r="C822">
-        <v>2444</v>
+        <v>2426</v>
       </c>
       <c r="D822" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F822" t="s">
         <v>29</v>
@@ -23657,10 +23657,10 @@
         <v>0</v>
       </c>
       <c r="I822" s="1">
-        <v>46083.769791666666</v>
+        <v>46083.770486111112</v>
       </c>
       <c r="J822">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K822" t="s">
         <v>11</v>
@@ -23671,64 +23671,64 @@
         <v>37</v>
       </c>
       <c r="C823">
-        <v>2426</v>
+        <v>4630</v>
       </c>
       <c r="D823" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="F823" t="s">
         <v>29</v>
       </c>
       <c r="G823" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H823" s="2">
-        <v>0</v>
+        <v>1.736111111111111E-3</v>
       </c>
       <c r="I823" s="1">
         <v>46083.770486111112</v>
       </c>
       <c r="J823">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K823" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="824" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B824" t="s">
-        <v>37</v>
-      </c>
-      <c r="C824">
-        <v>4630</v>
-      </c>
-      <c r="D824" t="s">
-        <v>89</v>
-      </c>
-      <c r="F824" t="s">
+      <c r="H824" s="2"/>
+      <c r="I824" s="1"/>
+      <c r="K824" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="825" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B825" t="s">
+        <v>37</v>
+      </c>
+      <c r="C825">
+        <v>2452</v>
+      </c>
+      <c r="D825" t="s">
+        <v>68</v>
+      </c>
+      <c r="F825" t="s">
         <v>29</v>
       </c>
-      <c r="G824" t="s">
-        <v>12</v>
-      </c>
-      <c r="H824" s="2">
-        <v>1.736111111111111E-3</v>
-      </c>
-      <c r="I824" s="1">
-        <v>46083.770486111112</v>
-      </c>
-      <c r="J824">
-        <v>0</v>
-      </c>
-      <c r="K824" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="825" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H825" s="2"/>
-      <c r="I825" s="1"/>
+      <c r="G825" t="s">
+        <v>13</v>
+      </c>
+      <c r="H825" s="2">
+        <v>0</v>
+      </c>
+      <c r="I825" s="1">
+        <v>46083.771180555559</v>
+      </c>
+      <c r="J825">
+        <v>3</v>
+      </c>
       <c r="K825" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="826" spans="2:11" x14ac:dyDescent="0.25">
@@ -23736,25 +23736,25 @@
         <v>37</v>
       </c>
       <c r="C826">
-        <v>2452</v>
+        <v>2447</v>
       </c>
       <c r="D826" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F826" t="s">
         <v>29</v>
       </c>
       <c r="G826" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H826" s="2">
-        <v>0</v>
+        <v>5.6249999999999998E-3</v>
       </c>
       <c r="I826" s="1">
-        <v>46083.771180555559</v>
+        <v>46083.771874999999</v>
       </c>
       <c r="J826">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K826" t="s">
         <v>11</v>
@@ -23765,10 +23765,10 @@
         <v>37</v>
       </c>
       <c r="C827">
-        <v>2447</v>
+        <v>2436</v>
       </c>
       <c r="D827" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F827" t="s">
         <v>29</v>
@@ -23777,7 +23777,7 @@
         <v>10</v>
       </c>
       <c r="H827" s="2">
-        <v>5.6249999999999998E-3</v>
+        <v>6.5393518518518517E-3</v>
       </c>
       <c r="I827" s="1">
         <v>46083.771874999999</v>
@@ -23794,25 +23794,25 @@
         <v>37</v>
       </c>
       <c r="C828">
-        <v>2436</v>
+        <v>2982</v>
       </c>
       <c r="D828" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F828" t="s">
         <v>29</v>
       </c>
       <c r="G828" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H828" s="2">
-        <v>6.5393518518518517E-3</v>
+        <v>0</v>
       </c>
       <c r="I828" s="1">
-        <v>46083.771874999999</v>
+        <v>46083.772569444445</v>
       </c>
       <c r="J828">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K828" t="s">
         <v>11</v>
@@ -23823,64 +23823,64 @@
         <v>37</v>
       </c>
       <c r="C829">
-        <v>2982</v>
+        <v>3854</v>
       </c>
       <c r="D829" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F829" t="s">
         <v>29</v>
       </c>
       <c r="G829" t="s">
+        <v>14</v>
+      </c>
+      <c r="H829" s="2">
+        <v>0</v>
+      </c>
+      <c r="I829" s="1">
+        <v>46083.773263888892</v>
+      </c>
+      <c r="J829">
+        <v>1</v>
+      </c>
+      <c r="K829" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="830" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H830" s="2"/>
+      <c r="I830" s="1"/>
+      <c r="K830" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="831" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B831" t="s">
+        <v>37</v>
+      </c>
+      <c r="C831">
+        <v>4885</v>
+      </c>
+      <c r="D831" t="s">
+        <v>90</v>
+      </c>
+      <c r="F831" t="s">
+        <v>29</v>
+      </c>
+      <c r="G831" t="s">
         <v>13</v>
       </c>
-      <c r="H829" s="2">
-        <v>0</v>
-      </c>
-      <c r="I829" s="1">
-        <v>46083.772569444445</v>
-      </c>
-      <c r="J829">
-        <v>2</v>
-      </c>
-      <c r="K829" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="830" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B830" t="s">
-        <v>37</v>
-      </c>
-      <c r="C830">
-        <v>3854</v>
-      </c>
-      <c r="D830" t="s">
-        <v>88</v>
-      </c>
-      <c r="F830" t="s">
-        <v>29</v>
-      </c>
-      <c r="G830" t="s">
-        <v>14</v>
-      </c>
-      <c r="H830" s="2">
-        <v>0</v>
-      </c>
-      <c r="I830" s="1">
+      <c r="H831" s="2">
+        <v>0</v>
+      </c>
+      <c r="I831" s="1">
         <v>46083.773263888892</v>
       </c>
-      <c r="J830">
-        <v>1</v>
-      </c>
-      <c r="K830" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="831" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H831" s="2"/>
-      <c r="I831" s="1"/>
+      <c r="J831">
+        <v>3</v>
+      </c>
       <c r="K831" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="832" spans="2:11" x14ac:dyDescent="0.25">
@@ -23888,22 +23888,22 @@
         <v>37</v>
       </c>
       <c r="C832">
-        <v>4885</v>
+        <v>2423</v>
       </c>
       <c r="D832" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F832" t="s">
         <v>29</v>
       </c>
       <c r="G832" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H832" s="2">
-        <v>0</v>
+        <v>4.43287037037037E-3</v>
       </c>
       <c r="I832" s="1">
-        <v>46083.773263888892</v>
+        <v>46083.773958333331</v>
       </c>
       <c r="J832">
         <v>2</v>
@@ -23917,10 +23917,10 @@
         <v>37</v>
       </c>
       <c r="C833">
-        <v>2423</v>
+        <v>2441</v>
       </c>
       <c r="D833" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F833" t="s">
         <v>29</v>
@@ -23929,13 +23929,13 @@
         <v>10</v>
       </c>
       <c r="H833" s="2">
-        <v>4.43287037037037E-3</v>
+        <v>4.2708333333333331E-3</v>
       </c>
       <c r="I833" s="1">
         <v>46083.773958333331</v>
       </c>
       <c r="J833">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K833" t="s">
         <v>11</v>
@@ -23946,10 +23946,10 @@
         <v>37</v>
       </c>
       <c r="C834">
-        <v>2441</v>
+        <v>2437</v>
       </c>
       <c r="D834" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F834" t="s">
         <v>29</v>
@@ -23958,10 +23958,10 @@
         <v>10</v>
       </c>
       <c r="H834" s="2">
-        <v>4.2708333333333331E-3</v>
+        <v>7.8356481481481489E-3</v>
       </c>
       <c r="I834" s="1">
-        <v>46083.773958333331</v>
+        <v>46083.774652777778</v>
       </c>
       <c r="J834">
         <v>0</v>
@@ -23975,25 +23975,25 @@
         <v>37</v>
       </c>
       <c r="C835">
-        <v>2437</v>
+        <v>4886</v>
       </c>
       <c r="D835" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="F835" t="s">
         <v>29</v>
       </c>
       <c r="G835" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H835" s="2">
-        <v>7.8356481481481489E-3</v>
+        <v>0</v>
       </c>
       <c r="I835" s="1">
-        <v>46083.774652777778</v>
+        <v>46083.751851851855</v>
       </c>
       <c r="J835">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K835" t="s">
         <v>11</v>
@@ -24004,58 +24004,33 @@
         <v>37</v>
       </c>
       <c r="C836">
-        <v>4886</v>
+        <v>5188</v>
       </c>
       <c r="D836" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F836" t="s">
         <v>29</v>
       </c>
       <c r="G836" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H836" s="2">
-        <v>0</v>
+        <v>5.3356481481481484E-3</v>
       </c>
       <c r="I836" s="1">
         <v>46083.751851851855</v>
       </c>
       <c r="J836">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K836" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="837" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B837" t="s">
-        <v>37</v>
-      </c>
-      <c r="C837">
-        <v>5188</v>
-      </c>
-      <c r="D837" t="s">
-        <v>97</v>
-      </c>
-      <c r="F837" t="s">
-        <v>29</v>
-      </c>
-      <c r="G837" t="s">
-        <v>10</v>
-      </c>
-      <c r="H837" s="2">
-        <v>5.3356481481481484E-3</v>
-      </c>
-      <c r="I837" s="1">
-        <v>46083.751851851855</v>
-      </c>
-      <c r="J837">
-        <v>0</v>
-      </c>
-      <c r="K837" t="s">
-        <v>11</v>
-      </c>
+      <c r="H837" s="2"/>
+      <c r="I837" s="1"/>
     </row>
     <row r="838" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H838" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\All City Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DFD8F9E-F97B-4508-B34B-07CAE18A545F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83670C53-96B9-4EE3-B7F7-B1A4A30E960D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -22999,10 +22999,10 @@
         <v>29</v>
       </c>
       <c r="G798" t="s">
-        <v>13</v>
-      </c>
-      <c r="H798">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H798" s="2">
+        <v>7.1180555555555554E-3</v>
       </c>
       <c r="I798" s="1">
         <v>46083.760069444441</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\All City Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83670C53-96B9-4EE3-B7F7-B1A4A30E960D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE3142E-DB5B-415E-9A99-2ED1E652C536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4013" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4186" uniqueCount="101">
   <si>
     <t>Company Name</t>
   </si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t>Scene of an Accident Procedures</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
   </si>
 </sst>
 </file>
@@ -24029,176 +24032,1036 @@
       </c>
     </row>
     <row r="837" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H837" s="2"/>
-      <c r="I837" s="1"/>
+      <c r="B837" t="s">
+        <v>37</v>
+      </c>
+      <c r="C837">
+        <v>2434</v>
+      </c>
+      <c r="D837" t="s">
+        <v>39</v>
+      </c>
+      <c r="F837" t="s">
+        <v>100</v>
+      </c>
+      <c r="G837" t="s">
+        <v>13</v>
+      </c>
+      <c r="H837" s="2">
+        <v>0</v>
+      </c>
+      <c r="I837" s="1">
+        <v>46118.768634259257</v>
+      </c>
+      <c r="J837">
+        <v>1</v>
+      </c>
+      <c r="K837" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="838" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H838" s="2"/>
-      <c r="I838" s="1"/>
+      <c r="B838" t="s">
+        <v>37</v>
+      </c>
+      <c r="C838">
+        <v>3855</v>
+      </c>
+      <c r="D838" t="s">
+        <v>86</v>
+      </c>
+      <c r="F838" t="s">
+        <v>100</v>
+      </c>
+      <c r="G838" t="s">
+        <v>13</v>
+      </c>
+      <c r="H838" s="2">
+        <v>0</v>
+      </c>
+      <c r="I838" s="1">
+        <v>46118.769328703704</v>
+      </c>
+      <c r="J838">
+        <v>1</v>
+      </c>
+      <c r="K838" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="839" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H839" s="2"/>
-      <c r="I839" s="1"/>
+      <c r="B839" t="s">
+        <v>37</v>
+      </c>
+      <c r="C839">
+        <v>2424</v>
+      </c>
+      <c r="D839" t="s">
+        <v>41</v>
+      </c>
+      <c r="F839" t="s">
+        <v>100</v>
+      </c>
+      <c r="G839" t="s">
+        <v>13</v>
+      </c>
+      <c r="H839" s="2">
+        <v>0</v>
+      </c>
+      <c r="I839" s="1">
+        <v>46118.769328703704</v>
+      </c>
+      <c r="J839">
+        <v>1</v>
+      </c>
+      <c r="K839" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="840" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H840" s="2"/>
-      <c r="I840" s="1"/>
+      <c r="B840" t="s">
+        <v>37</v>
+      </c>
+      <c r="C840">
+        <v>2433</v>
+      </c>
+      <c r="D840" t="s">
+        <v>42</v>
+      </c>
+      <c r="F840" t="s">
+        <v>100</v>
+      </c>
+      <c r="G840" t="s">
+        <v>13</v>
+      </c>
+      <c r="H840" s="2">
+        <v>0</v>
+      </c>
+      <c r="I840" s="1">
+        <v>46118.77002314815</v>
+      </c>
+      <c r="J840">
+        <v>1</v>
+      </c>
+      <c r="K840" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="841" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H841" s="2"/>
-      <c r="I841" s="1"/>
+      <c r="B841" t="s">
+        <v>37</v>
+      </c>
+      <c r="C841">
+        <v>2454</v>
+      </c>
+      <c r="D841" t="s">
+        <v>38</v>
+      </c>
+      <c r="F841" t="s">
+        <v>100</v>
+      </c>
+      <c r="G841" t="s">
+        <v>10</v>
+      </c>
+      <c r="H841" s="2">
+        <v>8.4027777777777781E-3</v>
+      </c>
+      <c r="I841" s="1">
+        <v>46118.77071759259</v>
+      </c>
+      <c r="J841">
+        <v>1</v>
+      </c>
+      <c r="K841" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="842" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H842" s="2"/>
-      <c r="I842" s="1"/>
+      <c r="B842" t="s">
+        <v>37</v>
+      </c>
+      <c r="C842">
+        <v>2645</v>
+      </c>
+      <c r="D842" t="s">
+        <v>44</v>
+      </c>
+      <c r="F842" t="s">
+        <v>100</v>
+      </c>
+      <c r="G842" t="s">
+        <v>13</v>
+      </c>
+      <c r="H842" s="2">
+        <v>0</v>
+      </c>
+      <c r="I842" s="1">
+        <v>46118.77071759259</v>
+      </c>
+      <c r="J842">
+        <v>1</v>
+      </c>
+      <c r="K842" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="843" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H843" s="2"/>
-      <c r="I843" s="1"/>
+      <c r="B843" t="s">
+        <v>37</v>
+      </c>
+      <c r="C843">
+        <v>2428</v>
+      </c>
+      <c r="D843" t="s">
+        <v>45</v>
+      </c>
+      <c r="F843" t="s">
+        <v>100</v>
+      </c>
+      <c r="G843" t="s">
+        <v>13</v>
+      </c>
+      <c r="H843" s="2">
+        <v>0</v>
+      </c>
+      <c r="I843" s="1">
+        <v>46118.771412037036</v>
+      </c>
+      <c r="J843">
+        <v>1</v>
+      </c>
+      <c r="K843" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="844" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H844" s="2"/>
-      <c r="I844" s="1"/>
+      <c r="B844" t="s">
+        <v>37</v>
+      </c>
+      <c r="C844">
+        <v>2983</v>
+      </c>
+      <c r="D844" t="s">
+        <v>78</v>
+      </c>
+      <c r="F844" t="s">
+        <v>100</v>
+      </c>
+      <c r="G844" t="s">
+        <v>13</v>
+      </c>
+      <c r="H844" s="2">
+        <v>0</v>
+      </c>
+      <c r="I844" s="1">
+        <v>46118.771412037036</v>
+      </c>
+      <c r="J844">
+        <v>1</v>
+      </c>
+      <c r="K844" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="845" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H845" s="2"/>
-      <c r="I845" s="1"/>
+      <c r="B845" t="s">
+        <v>37</v>
+      </c>
+      <c r="C845">
+        <v>2425</v>
+      </c>
+      <c r="D845" t="s">
+        <v>49</v>
+      </c>
+      <c r="F845" t="s">
+        <v>100</v>
+      </c>
+      <c r="G845" t="s">
+        <v>10</v>
+      </c>
+      <c r="H845" s="2">
+        <v>9.3761574074074081E-2</v>
+      </c>
+      <c r="I845" s="1">
+        <v>46118.772106481483</v>
+      </c>
+      <c r="J845">
+        <v>1</v>
+      </c>
+      <c r="K845" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="846" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H846" s="2"/>
-      <c r="I846" s="1"/>
+      <c r="B846" t="s">
+        <v>37</v>
+      </c>
+      <c r="C846">
+        <v>5189</v>
+      </c>
+      <c r="D846" t="s">
+        <v>95</v>
+      </c>
+      <c r="F846" t="s">
+        <v>100</v>
+      </c>
+      <c r="G846" t="s">
+        <v>10</v>
+      </c>
+      <c r="H846" s="2">
+        <v>9.2476851851851852E-3</v>
+      </c>
+      <c r="I846" s="1">
+        <v>46118.772800925923</v>
+      </c>
+      <c r="J846">
+        <v>0</v>
+      </c>
+      <c r="K846" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="847" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H847" s="2"/>
-      <c r="I847" s="1"/>
+      <c r="B847" t="s">
+        <v>37</v>
+      </c>
+      <c r="C847">
+        <v>3791</v>
+      </c>
+      <c r="D847" t="s">
+        <v>83</v>
+      </c>
+      <c r="F847" t="s">
+        <v>100</v>
+      </c>
+      <c r="G847" t="s">
+        <v>13</v>
+      </c>
+      <c r="H847" s="2">
+        <v>0</v>
+      </c>
+      <c r="I847" s="1">
+        <v>46118.793055555558</v>
+      </c>
+      <c r="J847">
+        <v>1</v>
+      </c>
+      <c r="K847" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="848" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H848" s="2"/>
-      <c r="I848" s="1"/>
-    </row>
-    <row r="849" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H849" s="2"/>
-      <c r="I849" s="1"/>
-    </row>
-    <row r="850" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H850" s="2"/>
-      <c r="I850" s="1"/>
-    </row>
-    <row r="851" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H851" s="2"/>
-      <c r="I851" s="1"/>
-    </row>
-    <row r="852" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B848" t="s">
+        <v>37</v>
+      </c>
+      <c r="C848">
+        <v>2435</v>
+      </c>
+      <c r="D848" t="s">
+        <v>53</v>
+      </c>
+      <c r="F848" t="s">
+        <v>100</v>
+      </c>
+      <c r="G848" t="s">
+        <v>13</v>
+      </c>
+      <c r="H848" s="2">
+        <v>0</v>
+      </c>
+      <c r="I848" s="1">
+        <v>46118.793749999997</v>
+      </c>
+      <c r="J848">
+        <v>1</v>
+      </c>
+      <c r="K848" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="849" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B849" t="s">
+        <v>37</v>
+      </c>
+      <c r="C849">
+        <v>2439</v>
+      </c>
+      <c r="D849" t="s">
+        <v>55</v>
+      </c>
+      <c r="F849" t="s">
+        <v>100</v>
+      </c>
+      <c r="G849" t="s">
+        <v>10</v>
+      </c>
+      <c r="H849" s="2">
+        <v>7.0254629629629634E-3</v>
+      </c>
+      <c r="I849" s="1">
+        <v>46118.794444444444</v>
+      </c>
+      <c r="J849">
+        <v>1</v>
+      </c>
+      <c r="K849" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="850" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B850" t="s">
+        <v>37</v>
+      </c>
+      <c r="C850">
+        <v>2432</v>
+      </c>
+      <c r="D850" t="s">
+        <v>56</v>
+      </c>
+      <c r="F850" t="s">
+        <v>100</v>
+      </c>
+      <c r="G850" t="s">
+        <v>10</v>
+      </c>
+      <c r="H850" s="2">
+        <v>1.3101851851851852E-2</v>
+      </c>
+      <c r="I850" s="1">
+        <v>46118.794444444444</v>
+      </c>
+      <c r="J850">
+        <v>0</v>
+      </c>
+      <c r="K850" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="851" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B851" t="s">
+        <v>37</v>
+      </c>
+      <c r="C851">
+        <v>2431</v>
+      </c>
+      <c r="D851" t="s">
+        <v>57</v>
+      </c>
+      <c r="F851" t="s">
+        <v>100</v>
+      </c>
+      <c r="G851" t="s">
+        <v>12</v>
+      </c>
+      <c r="H851" s="2">
+        <v>0</v>
+      </c>
+      <c r="I851" s="1">
+        <v>46118.795138888891</v>
+      </c>
+      <c r="J851">
+        <v>1</v>
+      </c>
+      <c r="K851" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="852" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H852" s="2"/>
       <c r="I852" s="1"/>
-    </row>
-    <row r="853" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H853" s="2"/>
-      <c r="I853" s="1"/>
-    </row>
-    <row r="854" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H854" s="2"/>
-      <c r="I854" s="1"/>
-    </row>
-    <row r="855" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H855" s="2"/>
-      <c r="I855" s="1"/>
-    </row>
-    <row r="856" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H856" s="2"/>
-      <c r="I856" s="1"/>
-    </row>
-    <row r="857" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H857" s="2"/>
-      <c r="I857" s="1"/>
-    </row>
-    <row r="858" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H858" s="2"/>
-      <c r="I858" s="1"/>
-    </row>
-    <row r="859" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H859" s="2"/>
-      <c r="I859" s="1"/>
-    </row>
-    <row r="860" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H860" s="2"/>
-      <c r="I860" s="1"/>
-    </row>
-    <row r="861" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H861" s="2"/>
-      <c r="I861" s="1"/>
-    </row>
-    <row r="862" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K852" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="853" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B853" t="s">
+        <v>37</v>
+      </c>
+      <c r="C853">
+        <v>2772</v>
+      </c>
+      <c r="D853" t="s">
+        <v>77</v>
+      </c>
+      <c r="F853" t="s">
+        <v>100</v>
+      </c>
+      <c r="G853" t="s">
+        <v>10</v>
+      </c>
+      <c r="H853" s="2">
+        <v>7.2106481481481483E-3</v>
+      </c>
+      <c r="I853" s="1">
+        <v>46118.79583333333</v>
+      </c>
+      <c r="J853">
+        <v>0</v>
+      </c>
+      <c r="K853" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="854" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B854" t="s">
+        <v>37</v>
+      </c>
+      <c r="C854">
+        <v>3482</v>
+      </c>
+      <c r="D854" t="s">
+        <v>81</v>
+      </c>
+      <c r="F854" t="s">
+        <v>100</v>
+      </c>
+      <c r="G854" t="s">
+        <v>10</v>
+      </c>
+      <c r="H854" s="2">
+        <v>7.0254629629629634E-3</v>
+      </c>
+      <c r="I854" s="1">
+        <v>46118.79583333333</v>
+      </c>
+      <c r="J854">
+        <v>1</v>
+      </c>
+      <c r="K854" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="855" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B855" t="s">
+        <v>37</v>
+      </c>
+      <c r="C855">
+        <v>5204</v>
+      </c>
+      <c r="D855" t="s">
+        <v>96</v>
+      </c>
+      <c r="F855" t="s">
+        <v>100</v>
+      </c>
+      <c r="G855" t="s">
+        <v>13</v>
+      </c>
+      <c r="H855" s="2">
+        <v>0</v>
+      </c>
+      <c r="I855" s="1">
+        <v>46118.796527777777</v>
+      </c>
+      <c r="J855">
+        <v>1</v>
+      </c>
+      <c r="K855" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="856" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B856" t="s">
+        <v>37</v>
+      </c>
+      <c r="C856">
+        <v>2449</v>
+      </c>
+      <c r="D856" t="s">
+        <v>60</v>
+      </c>
+      <c r="F856" t="s">
+        <v>100</v>
+      </c>
+      <c r="G856" t="s">
+        <v>10</v>
+      </c>
+      <c r="H856" s="2">
+        <v>7.8009259259259256E-3</v>
+      </c>
+      <c r="I856" s="1">
+        <v>46118.797222222223</v>
+      </c>
+      <c r="J856">
+        <v>0</v>
+      </c>
+      <c r="K856" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="857" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B857" t="s">
+        <v>37</v>
+      </c>
+      <c r="C857">
+        <v>2418</v>
+      </c>
+      <c r="D857" t="s">
+        <v>63</v>
+      </c>
+      <c r="F857" t="s">
+        <v>100</v>
+      </c>
+      <c r="G857" t="s">
+        <v>13</v>
+      </c>
+      <c r="H857" s="2">
+        <v>0</v>
+      </c>
+      <c r="I857" s="1">
+        <v>46118.797222222223</v>
+      </c>
+      <c r="J857">
+        <v>1</v>
+      </c>
+      <c r="K857" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="858" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B858" t="s">
+        <v>37</v>
+      </c>
+      <c r="C858">
+        <v>2444</v>
+      </c>
+      <c r="D858" t="s">
+        <v>66</v>
+      </c>
+      <c r="F858" t="s">
+        <v>100</v>
+      </c>
+      <c r="G858" t="s">
+        <v>13</v>
+      </c>
+      <c r="H858" s="2">
+        <v>0</v>
+      </c>
+      <c r="I858" s="1">
+        <v>46118.79791666667</v>
+      </c>
+      <c r="J858">
+        <v>1</v>
+      </c>
+      <c r="K858" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="859" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B859" t="s">
+        <v>37</v>
+      </c>
+      <c r="C859">
+        <v>2426</v>
+      </c>
+      <c r="D859" t="s">
+        <v>67</v>
+      </c>
+      <c r="F859" t="s">
+        <v>100</v>
+      </c>
+      <c r="G859" t="s">
+        <v>13</v>
+      </c>
+      <c r="H859" s="2">
+        <v>0</v>
+      </c>
+      <c r="I859" s="1">
+        <v>46118.798611111109</v>
+      </c>
+      <c r="J859">
+        <v>1</v>
+      </c>
+      <c r="K859" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="860" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B860" t="s">
+        <v>37</v>
+      </c>
+      <c r="C860">
+        <v>4630</v>
+      </c>
+      <c r="D860" t="s">
+        <v>89</v>
+      </c>
+      <c r="F860" t="s">
+        <v>100</v>
+      </c>
+      <c r="G860" t="s">
+        <v>10</v>
+      </c>
+      <c r="H860" s="2">
+        <v>8.5069444444444437E-3</v>
+      </c>
+      <c r="I860" s="1">
+        <v>46118.798611111109</v>
+      </c>
+      <c r="J860">
+        <v>0</v>
+      </c>
+      <c r="K860" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="861" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B861" t="s">
+        <v>37</v>
+      </c>
+      <c r="C861">
+        <v>2452</v>
+      </c>
+      <c r="D861" t="s">
+        <v>68</v>
+      </c>
+      <c r="F861" t="s">
+        <v>100</v>
+      </c>
+      <c r="G861" t="s">
+        <v>12</v>
+      </c>
+      <c r="H861" s="2">
+        <v>0</v>
+      </c>
+      <c r="I861" s="1">
+        <v>46118.799305555556</v>
+      </c>
+      <c r="J861">
+        <v>0</v>
+      </c>
+      <c r="K861" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="862" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H862" s="2"/>
       <c r="I862" s="1"/>
-    </row>
-    <row r="863" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H863" s="2"/>
-      <c r="I863" s="1"/>
-    </row>
-    <row r="864" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H864" s="2"/>
-      <c r="I864" s="1"/>
-    </row>
-    <row r="865" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H865" s="2"/>
-      <c r="I865" s="1"/>
-    </row>
-    <row r="866" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H866" s="2"/>
-      <c r="I866" s="1"/>
-    </row>
-    <row r="867" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K862" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="863" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B863" t="s">
+        <v>37</v>
+      </c>
+      <c r="C863">
+        <v>2447</v>
+      </c>
+      <c r="D863" t="s">
+        <v>69</v>
+      </c>
+      <c r="F863" t="s">
+        <v>100</v>
+      </c>
+      <c r="G863" t="s">
+        <v>10</v>
+      </c>
+      <c r="H863" s="2">
+        <v>8.0787037037037043E-3</v>
+      </c>
+      <c r="I863" s="1">
+        <v>46118.799305555556</v>
+      </c>
+      <c r="J863">
+        <v>0</v>
+      </c>
+      <c r="K863" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="864" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B864" t="s">
+        <v>37</v>
+      </c>
+      <c r="C864">
+        <v>2436</v>
+      </c>
+      <c r="D864" t="s">
+        <v>70</v>
+      </c>
+      <c r="F864" t="s">
+        <v>100</v>
+      </c>
+      <c r="G864" t="s">
+        <v>10</v>
+      </c>
+      <c r="H864" s="2">
+        <v>9.0162037037037034E-3</v>
+      </c>
+      <c r="I864" s="1">
+        <v>46118.8</v>
+      </c>
+      <c r="J864">
+        <v>0</v>
+      </c>
+      <c r="K864" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="865" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B865" t="s">
+        <v>37</v>
+      </c>
+      <c r="C865">
+        <v>2982</v>
+      </c>
+      <c r="D865" t="s">
+        <v>80</v>
+      </c>
+      <c r="F865" t="s">
+        <v>100</v>
+      </c>
+      <c r="G865" t="s">
+        <v>13</v>
+      </c>
+      <c r="H865" s="2">
+        <v>0</v>
+      </c>
+      <c r="I865" s="1">
+        <v>46118.800694444442</v>
+      </c>
+      <c r="J865">
+        <v>1</v>
+      </c>
+      <c r="K865" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="866" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B866" t="s">
+        <v>37</v>
+      </c>
+      <c r="C866">
+        <v>3854</v>
+      </c>
+      <c r="D866" t="s">
+        <v>88</v>
+      </c>
+      <c r="F866" t="s">
+        <v>100</v>
+      </c>
+      <c r="G866" t="s">
+        <v>14</v>
+      </c>
+      <c r="H866" s="2">
+        <v>0</v>
+      </c>
+      <c r="I866" s="1">
+        <v>46118.800694444442</v>
+      </c>
+      <c r="J866">
+        <v>1</v>
+      </c>
+      <c r="K866" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="867" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H867" s="2"/>
       <c r="I867" s="1"/>
-    </row>
-    <row r="868" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H868" s="2"/>
-      <c r="I868" s="1"/>
-    </row>
-    <row r="869" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H869" s="2"/>
-      <c r="I869" s="1"/>
-    </row>
-    <row r="870" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H870" s="2"/>
-      <c r="I870" s="1"/>
-    </row>
-    <row r="871" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H871" s="2"/>
-      <c r="I871" s="1"/>
-    </row>
-    <row r="872" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I872" s="1"/>
-    </row>
-    <row r="873" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H873" s="2"/>
-      <c r="I873" s="1"/>
-    </row>
-    <row r="874" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K867" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="868" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B868" t="s">
+        <v>37</v>
+      </c>
+      <c r="C868">
+        <v>4885</v>
+      </c>
+      <c r="D868" t="s">
+        <v>90</v>
+      </c>
+      <c r="F868" t="s">
+        <v>100</v>
+      </c>
+      <c r="G868" t="s">
+        <v>13</v>
+      </c>
+      <c r="H868" s="2">
+        <v>0</v>
+      </c>
+      <c r="I868" s="1">
+        <v>46118.801388888889</v>
+      </c>
+      <c r="J868">
+        <v>1</v>
+      </c>
+      <c r="K868" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="869" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B869" t="s">
+        <v>37</v>
+      </c>
+      <c r="C869">
+        <v>2423</v>
+      </c>
+      <c r="D869" t="s">
+        <v>72</v>
+      </c>
+      <c r="F869" t="s">
+        <v>100</v>
+      </c>
+      <c r="G869" t="s">
+        <v>10</v>
+      </c>
+      <c r="H869" s="2">
+        <v>6.7013888888888887E-3</v>
+      </c>
+      <c r="I869" s="1">
+        <v>46118.801388888889</v>
+      </c>
+      <c r="J869">
+        <v>0</v>
+      </c>
+      <c r="K869" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="870" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B870" t="s">
+        <v>37</v>
+      </c>
+      <c r="C870">
+        <v>2441</v>
+      </c>
+      <c r="D870" t="s">
+        <v>73</v>
+      </c>
+      <c r="F870" t="s">
+        <v>100</v>
+      </c>
+      <c r="G870" t="s">
+        <v>10</v>
+      </c>
+      <c r="H870" s="2">
+        <v>6.7476851851851856E-3</v>
+      </c>
+      <c r="I870" s="1">
+        <v>46118.802083333336</v>
+      </c>
+      <c r="J870">
+        <v>1</v>
+      </c>
+      <c r="K870" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="871" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B871" t="s">
+        <v>37</v>
+      </c>
+      <c r="C871">
+        <v>2437</v>
+      </c>
+      <c r="D871" t="s">
+        <v>75</v>
+      </c>
+      <c r="F871" t="s">
+        <v>100</v>
+      </c>
+      <c r="G871" t="s">
+        <v>13</v>
+      </c>
+      <c r="H871" s="2">
+        <v>0</v>
+      </c>
+      <c r="I871" s="1">
+        <v>46118.802777777775</v>
+      </c>
+      <c r="J871">
+        <v>1</v>
+      </c>
+      <c r="K871" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="872" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B872" t="s">
+        <v>37</v>
+      </c>
+      <c r="C872">
+        <v>4886</v>
+      </c>
+      <c r="D872" t="s">
+        <v>91</v>
+      </c>
+      <c r="F872" t="s">
+        <v>100</v>
+      </c>
+      <c r="G872" t="s">
+        <v>13</v>
+      </c>
+      <c r="H872">
+        <v>0</v>
+      </c>
+      <c r="I872" s="1">
+        <v>46118.802777777775</v>
+      </c>
+      <c r="J872">
+        <v>1</v>
+      </c>
+      <c r="K872" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="873" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B873" t="s">
+        <v>37</v>
+      </c>
+      <c r="C873">
+        <v>5188</v>
+      </c>
+      <c r="D873" t="s">
+        <v>97</v>
+      </c>
+      <c r="F873" t="s">
+        <v>100</v>
+      </c>
+      <c r="G873" t="s">
+        <v>10</v>
+      </c>
+      <c r="H873" s="2">
+        <v>8.1944444444444452E-3</v>
+      </c>
+      <c r="I873" s="1">
+        <v>46118.803472222222</v>
+      </c>
+      <c r="J873">
+        <v>0</v>
+      </c>
+      <c r="K873" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="874" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H874" s="2"/>
       <c r="I874" s="1"/>
     </row>
-    <row r="875" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="875" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H875" s="2"/>
       <c r="I875" s="1"/>
     </row>
-    <row r="876" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="876" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H876" s="2"/>
       <c r="I876" s="1"/>
     </row>
-    <row r="877" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="877" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H877" s="2"/>
       <c r="I877" s="1"/>
     </row>
-    <row r="878" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="878" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H878" s="2"/>
       <c r="I878" s="1"/>
     </row>
-    <row r="879" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="879" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I879" s="1"/>
     </row>
-    <row r="880" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="880" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H880" s="2"/>
       <c r="I880" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\All City Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE3142E-DB5B-415E-9A99-2ED1E652C536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4069F35E-1B5F-488A-9DE3-735CC7AE3752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4186" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4188" uniqueCount="101">
   <si>
     <t>Company Name</t>
   </si>
@@ -24054,7 +24054,7 @@
         <v>46118.768634259257</v>
       </c>
       <c r="J837">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K837" t="s">
         <v>11</v>
@@ -24083,7 +24083,7 @@
         <v>46118.769328703704</v>
       </c>
       <c r="J838">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K838" t="s">
         <v>11</v>
@@ -24112,7 +24112,7 @@
         <v>46118.769328703704</v>
       </c>
       <c r="J839">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K839" t="s">
         <v>11</v>
@@ -24132,16 +24132,16 @@
         <v>100</v>
       </c>
       <c r="G840" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H840" s="2">
-        <v>0</v>
+        <v>8.4490740740740741E-3</v>
       </c>
       <c r="I840" s="1">
         <v>46118.77002314815</v>
       </c>
       <c r="J840">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K840" t="s">
         <v>11</v>
@@ -24199,7 +24199,7 @@
         <v>46118.77071759259</v>
       </c>
       <c r="J842">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K842" t="s">
         <v>11</v>
@@ -24228,7 +24228,7 @@
         <v>46118.771412037036</v>
       </c>
       <c r="J843">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K843" t="s">
         <v>11</v>
@@ -24257,7 +24257,7 @@
         <v>46118.771412037036</v>
       </c>
       <c r="J844">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K844" t="s">
         <v>11</v>
@@ -24335,16 +24335,16 @@
         <v>100</v>
       </c>
       <c r="G847" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H847" s="2">
-        <v>0</v>
+        <v>7.8472222222222224E-3</v>
       </c>
       <c r="I847" s="1">
         <v>46118.793055555558</v>
       </c>
       <c r="J847">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K847" t="s">
         <v>11</v>
@@ -24373,7 +24373,7 @@
         <v>46118.793749999997</v>
       </c>
       <c r="J848">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K848" t="s">
         <v>11</v>
@@ -24554,7 +24554,7 @@
         <v>46118.796527777777</v>
       </c>
       <c r="J855">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K855" t="s">
         <v>11</v>
@@ -24612,7 +24612,7 @@
         <v>46118.797222222223</v>
       </c>
       <c r="J857">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K857" t="s">
         <v>11</v>
@@ -24641,7 +24641,7 @@
         <v>46118.79791666667</v>
       </c>
       <c r="J858">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K858" t="s">
         <v>11</v>
@@ -24670,7 +24670,7 @@
         <v>46118.798611111109</v>
       </c>
       <c r="J859">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K859" t="s">
         <v>11</v>
@@ -24813,84 +24813,62 @@
         <v>100</v>
       </c>
       <c r="G865" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H865" s="2">
-        <v>0</v>
+        <v>5.3240740740740744E-4</v>
       </c>
       <c r="I865" s="1">
         <v>46118.800694444442</v>
       </c>
       <c r="J865">
+        <v>2</v>
+      </c>
+      <c r="K865" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="866" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H866" s="2"/>
+      <c r="I866" s="1"/>
+      <c r="K866" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="867" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B867" t="s">
+        <v>37</v>
+      </c>
+      <c r="C867">
+        <v>3854</v>
+      </c>
+      <c r="D867" t="s">
+        <v>88</v>
+      </c>
+      <c r="F867" t="s">
+        <v>100</v>
+      </c>
+      <c r="G867" t="s">
+        <v>14</v>
+      </c>
+      <c r="H867" s="2">
+        <v>0</v>
+      </c>
+      <c r="I867" s="1">
+        <v>46118.800694444442</v>
+      </c>
+      <c r="J867">
         <v>1</v>
       </c>
-      <c r="K865" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="866" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B866" t="s">
-        <v>37</v>
-      </c>
-      <c r="C866">
-        <v>3854</v>
-      </c>
-      <c r="D866" t="s">
-        <v>88</v>
-      </c>
-      <c r="F866" t="s">
-        <v>100</v>
-      </c>
-      <c r="G866" t="s">
-        <v>14</v>
-      </c>
-      <c r="H866" s="2">
-        <v>0</v>
-      </c>
-      <c r="I866" s="1">
-        <v>46118.800694444442</v>
-      </c>
-      <c r="J866">
-        <v>1</v>
-      </c>
-      <c r="K866" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="867" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H867" s="2"/>
-      <c r="I867" s="1"/>
       <c r="K867" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="868" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H868" s="2"/>
+      <c r="I868" s="1"/>
+      <c r="K868" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="868" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B868" t="s">
-        <v>37</v>
-      </c>
-      <c r="C868">
-        <v>4885</v>
-      </c>
-      <c r="D868" t="s">
-        <v>90</v>
-      </c>
-      <c r="F868" t="s">
-        <v>100</v>
-      </c>
-      <c r="G868" t="s">
-        <v>13</v>
-      </c>
-      <c r="H868" s="2">
-        <v>0</v>
-      </c>
-      <c r="I868" s="1">
-        <v>46118.801388888889</v>
-      </c>
-      <c r="J868">
-        <v>1</v>
-      </c>
-      <c r="K868" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="869" spans="2:11" x14ac:dyDescent="0.25">
@@ -24898,57 +24876,35 @@
         <v>37</v>
       </c>
       <c r="C869">
-        <v>2423</v>
+        <v>4885</v>
       </c>
       <c r="D869" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F869" t="s">
         <v>100</v>
       </c>
       <c r="G869" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H869" s="2">
-        <v>6.7013888888888887E-3</v>
+        <v>9.2592592592592588E-5</v>
       </c>
       <c r="I869" s="1">
         <v>46118.801388888889</v>
       </c>
       <c r="J869">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K869" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="870" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B870" t="s">
-        <v>37</v>
-      </c>
-      <c r="C870">
-        <v>2441</v>
-      </c>
-      <c r="D870" t="s">
-        <v>73</v>
-      </c>
-      <c r="F870" t="s">
-        <v>100</v>
-      </c>
-      <c r="G870" t="s">
-        <v>10</v>
-      </c>
-      <c r="H870" s="2">
-        <v>6.7476851851851856E-3</v>
-      </c>
-      <c r="I870" s="1">
-        <v>46118.802083333336</v>
-      </c>
-      <c r="J870">
-        <v>1</v>
-      </c>
+      <c r="H870" s="2"/>
+      <c r="I870" s="1"/>
       <c r="K870" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="871" spans="2:11" x14ac:dyDescent="0.25">
@@ -24956,25 +24912,25 @@
         <v>37</v>
       </c>
       <c r="C871">
-        <v>2437</v>
+        <v>2423</v>
       </c>
       <c r="D871" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F871" t="s">
         <v>100</v>
       </c>
       <c r="G871" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H871" s="2">
-        <v>0</v>
+        <v>6.7013888888888887E-3</v>
       </c>
       <c r="I871" s="1">
-        <v>46118.802777777775</v>
+        <v>46118.801388888889</v>
       </c>
       <c r="J871">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K871" t="s">
         <v>11</v>
@@ -24985,22 +24941,22 @@
         <v>37</v>
       </c>
       <c r="C872">
-        <v>4886</v>
+        <v>2441</v>
       </c>
       <c r="D872" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="F872" t="s">
         <v>100</v>
       </c>
       <c r="G872" t="s">
-        <v>13</v>
-      </c>
-      <c r="H872">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H872" s="2">
+        <v>6.7476851851851856E-3</v>
       </c>
       <c r="I872" s="1">
-        <v>46118.802777777775</v>
+        <v>46118.802083333336</v>
       </c>
       <c r="J872">
         <v>1</v>
@@ -25014,37 +24970,87 @@
         <v>37</v>
       </c>
       <c r="C873">
-        <v>5188</v>
+        <v>2437</v>
       </c>
       <c r="D873" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="F873" t="s">
         <v>100</v>
       </c>
       <c r="G873" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H873" s="2">
+        <v>0</v>
+      </c>
+      <c r="I873" s="1">
+        <v>46118.802777777775</v>
+      </c>
+      <c r="J873">
+        <v>2</v>
+      </c>
+      <c r="K873" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="874" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B874" t="s">
+        <v>37</v>
+      </c>
+      <c r="C874">
+        <v>4886</v>
+      </c>
+      <c r="D874" t="s">
+        <v>91</v>
+      </c>
+      <c r="F874" t="s">
+        <v>100</v>
+      </c>
+      <c r="G874" t="s">
+        <v>13</v>
+      </c>
+      <c r="H874" s="2">
+        <v>0</v>
+      </c>
+      <c r="I874" s="1">
+        <v>46118.802777777775</v>
+      </c>
+      <c r="J874">
+        <v>2</v>
+      </c>
+      <c r="K874" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="875" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B875" t="s">
+        <v>37</v>
+      </c>
+      <c r="C875">
+        <v>5188</v>
+      </c>
+      <c r="D875" t="s">
+        <v>97</v>
+      </c>
+      <c r="F875" t="s">
+        <v>100</v>
+      </c>
+      <c r="G875" t="s">
+        <v>10</v>
+      </c>
+      <c r="H875" s="2">
         <v>8.1944444444444452E-3</v>
       </c>
-      <c r="I873" s="1">
+      <c r="I875" s="1">
         <v>46118.803472222222</v>
       </c>
-      <c r="J873">
-        <v>0</v>
-      </c>
-      <c r="K873" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="874" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H874" s="2"/>
-      <c r="I874" s="1"/>
-    </row>
-    <row r="875" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H875" s="2"/>
-      <c r="I875" s="1"/>
+      <c r="J875">
+        <v>0</v>
+      </c>
+      <c r="K875" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="876" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H876" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\All City Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4069F35E-1B5F-488A-9DE3-735CC7AE3752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4F314B-00AE-4313-AF87-A9B7D6ED4857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4188" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4324" uniqueCount="106">
   <si>
     <t>Company Name</t>
   </si>
@@ -342,6 +342,21 @@
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
+  </si>
+  <si>
+    <t>Grant Betts-Norman</t>
+  </si>
+  <si>
+    <t>Safe Backing</t>
+  </si>
+  <si>
+    <t>Jamie Wood</t>
+  </si>
+  <si>
+    <t>Jonathan McDowell</t>
+  </si>
+  <si>
+    <t>3 Points of Contact</t>
   </si>
 </sst>
 </file>
@@ -24054,7 +24069,7 @@
         <v>46118.768634259257</v>
       </c>
       <c r="J837">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K837" t="s">
         <v>11</v>
@@ -24083,7 +24098,7 @@
         <v>46118.769328703704</v>
       </c>
       <c r="J838">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K838" t="s">
         <v>11</v>
@@ -24112,7 +24127,7 @@
         <v>46118.769328703704</v>
       </c>
       <c r="J839">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K839" t="s">
         <v>11</v>
@@ -24190,16 +24205,16 @@
         <v>100</v>
       </c>
       <c r="G842" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H842" s="2">
-        <v>0</v>
+        <v>7.0717592592592594E-3</v>
       </c>
       <c r="I842" s="1">
         <v>46118.77071759259</v>
       </c>
       <c r="J842">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K842" t="s">
         <v>11</v>
@@ -24228,7 +24243,7 @@
         <v>46118.771412037036</v>
       </c>
       <c r="J843">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K843" t="s">
         <v>11</v>
@@ -24248,7 +24263,7 @@
         <v>100</v>
       </c>
       <c r="G844" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H844" s="2">
         <v>0</v>
@@ -24264,32 +24279,10 @@
       </c>
     </row>
     <row r="845" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B845" t="s">
-        <v>37</v>
-      </c>
-      <c r="C845">
-        <v>2425</v>
-      </c>
-      <c r="D845" t="s">
-        <v>49</v>
-      </c>
-      <c r="F845" t="s">
-        <v>100</v>
-      </c>
-      <c r="G845" t="s">
-        <v>10</v>
-      </c>
-      <c r="H845" s="2">
-        <v>9.3761574074074081E-2</v>
-      </c>
-      <c r="I845" s="1">
-        <v>46118.772106481483</v>
-      </c>
-      <c r="J845">
-        <v>1</v>
-      </c>
+      <c r="H845" s="2"/>
+      <c r="I845" s="1"/>
       <c r="K845" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="846" spans="2:11" x14ac:dyDescent="0.25">
@@ -24297,10 +24290,10 @@
         <v>37</v>
       </c>
       <c r="C846">
-        <v>5189</v>
+        <v>2425</v>
       </c>
       <c r="D846" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="F846" t="s">
         <v>100</v>
@@ -24309,13 +24302,13 @@
         <v>10</v>
       </c>
       <c r="H846" s="2">
-        <v>9.2476851851851852E-3</v>
+        <v>9.3761574074074081E-2</v>
       </c>
       <c r="I846" s="1">
-        <v>46118.772800925923</v>
+        <v>46118.772106481483</v>
       </c>
       <c r="J846">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K846" t="s">
         <v>11</v>
@@ -24326,10 +24319,10 @@
         <v>37</v>
       </c>
       <c r="C847">
-        <v>3791</v>
+        <v>5189</v>
       </c>
       <c r="D847" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F847" t="s">
         <v>100</v>
@@ -24338,13 +24331,13 @@
         <v>10</v>
       </c>
       <c r="H847" s="2">
-        <v>7.8472222222222224E-3</v>
+        <v>9.2476851851851852E-3</v>
       </c>
       <c r="I847" s="1">
-        <v>46118.793055555558</v>
+        <v>46118.772800925923</v>
       </c>
       <c r="J847">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K847" t="s">
         <v>11</v>
@@ -24355,22 +24348,22 @@
         <v>37</v>
       </c>
       <c r="C848">
-        <v>2435</v>
+        <v>3791</v>
       </c>
       <c r="D848" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="F848" t="s">
         <v>100</v>
       </c>
       <c r="G848" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H848" s="2">
-        <v>0</v>
+        <v>7.8472222222222224E-3</v>
       </c>
       <c r="I848" s="1">
-        <v>46118.793749999997</v>
+        <v>46118.793055555558</v>
       </c>
       <c r="J848">
         <v>2</v>
@@ -24384,25 +24377,25 @@
         <v>37</v>
       </c>
       <c r="C849">
-        <v>2439</v>
+        <v>2435</v>
       </c>
       <c r="D849" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F849" t="s">
         <v>100</v>
       </c>
       <c r="G849" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H849" s="2">
-        <v>7.0254629629629634E-3</v>
+        <v>0</v>
       </c>
       <c r="I849" s="1">
-        <v>46118.794444444444</v>
+        <v>46118.793749999997</v>
       </c>
       <c r="J849">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K849" t="s">
         <v>11</v>
@@ -24413,10 +24406,10 @@
         <v>37</v>
       </c>
       <c r="C850">
-        <v>2432</v>
+        <v>2439</v>
       </c>
       <c r="D850" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F850" t="s">
         <v>100</v>
@@ -24425,13 +24418,13 @@
         <v>10</v>
       </c>
       <c r="H850" s="2">
-        <v>1.3101851851851852E-2</v>
+        <v>7.0254629629629634E-3</v>
       </c>
       <c r="I850" s="1">
         <v>46118.794444444444</v>
       </c>
       <c r="J850">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K850" t="s">
         <v>11</v>
@@ -24442,64 +24435,64 @@
         <v>37</v>
       </c>
       <c r="C851">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="D851" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F851" t="s">
         <v>100</v>
       </c>
       <c r="G851" t="s">
+        <v>10</v>
+      </c>
+      <c r="H851" s="2">
+        <v>1.3101851851851852E-2</v>
+      </c>
+      <c r="I851" s="1">
+        <v>46118.794444444444</v>
+      </c>
+      <c r="J851">
+        <v>0</v>
+      </c>
+      <c r="K851" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="852" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B852" t="s">
+        <v>37</v>
+      </c>
+      <c r="C852">
+        <v>2431</v>
+      </c>
+      <c r="D852" t="s">
+        <v>57</v>
+      </c>
+      <c r="F852" t="s">
+        <v>100</v>
+      </c>
+      <c r="G852" t="s">
         <v>12</v>
       </c>
-      <c r="H851" s="2">
-        <v>0</v>
-      </c>
-      <c r="I851" s="1">
+      <c r="H852" s="2">
+        <v>0</v>
+      </c>
+      <c r="I852" s="1">
         <v>46118.795138888891</v>
       </c>
-      <c r="J851">
+      <c r="J852">
         <v>1</v>
       </c>
-      <c r="K851" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="852" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H852" s="2"/>
-      <c r="I852" s="1"/>
       <c r="K852" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="853" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H853" s="2"/>
+      <c r="I853" s="1"/>
+      <c r="K853" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="853" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B853" t="s">
-        <v>37</v>
-      </c>
-      <c r="C853">
-        <v>2772</v>
-      </c>
-      <c r="D853" t="s">
-        <v>77</v>
-      </c>
-      <c r="F853" t="s">
-        <v>100</v>
-      </c>
-      <c r="G853" t="s">
-        <v>10</v>
-      </c>
-      <c r="H853" s="2">
-        <v>7.2106481481481483E-3</v>
-      </c>
-      <c r="I853" s="1">
-        <v>46118.79583333333</v>
-      </c>
-      <c r="J853">
-        <v>0</v>
-      </c>
-      <c r="K853" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="854" spans="2:11" x14ac:dyDescent="0.25">
@@ -24507,10 +24500,10 @@
         <v>37</v>
       </c>
       <c r="C854">
-        <v>3482</v>
+        <v>2772</v>
       </c>
       <c r="D854" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F854" t="s">
         <v>100</v>
@@ -24519,13 +24512,13 @@
         <v>10</v>
       </c>
       <c r="H854" s="2">
-        <v>7.0254629629629634E-3</v>
+        <v>7.2106481481481483E-3</v>
       </c>
       <c r="I854" s="1">
         <v>46118.79583333333</v>
       </c>
       <c r="J854">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K854" t="s">
         <v>11</v>
@@ -24536,25 +24529,25 @@
         <v>37</v>
       </c>
       <c r="C855">
-        <v>5204</v>
+        <v>3482</v>
       </c>
       <c r="D855" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="F855" t="s">
         <v>100</v>
       </c>
       <c r="G855" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H855" s="2">
-        <v>0</v>
+        <v>7.0254629629629634E-3</v>
       </c>
       <c r="I855" s="1">
-        <v>46118.796527777777</v>
+        <v>46118.79583333333</v>
       </c>
       <c r="J855">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K855" t="s">
         <v>11</v>
@@ -24565,25 +24558,25 @@
         <v>37</v>
       </c>
       <c r="C856">
-        <v>2449</v>
+        <v>5204</v>
       </c>
       <c r="D856" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="F856" t="s">
         <v>100</v>
       </c>
       <c r="G856" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H856" s="2">
-        <v>7.8009259259259256E-3</v>
+        <v>0</v>
       </c>
       <c r="I856" s="1">
-        <v>46118.797222222223</v>
+        <v>46118.796527777777</v>
       </c>
       <c r="J856">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K856" t="s">
         <v>11</v>
@@ -24594,25 +24587,25 @@
         <v>37</v>
       </c>
       <c r="C857">
-        <v>2418</v>
+        <v>2449</v>
       </c>
       <c r="D857" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F857" t="s">
         <v>100</v>
       </c>
       <c r="G857" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H857" s="2">
-        <v>0</v>
+        <v>7.8009259259259256E-3</v>
       </c>
       <c r="I857" s="1">
         <v>46118.797222222223</v>
       </c>
       <c r="J857">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K857" t="s">
         <v>11</v>
@@ -24623,10 +24616,10 @@
         <v>37</v>
       </c>
       <c r="C858">
-        <v>2444</v>
+        <v>2418</v>
       </c>
       <c r="D858" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F858" t="s">
         <v>100</v>
@@ -24638,10 +24631,10 @@
         <v>0</v>
       </c>
       <c r="I858" s="1">
-        <v>46118.79791666667</v>
+        <v>46118.797222222223</v>
       </c>
       <c r="J858">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K858" t="s">
         <v>11</v>
@@ -24652,10 +24645,10 @@
         <v>37</v>
       </c>
       <c r="C859">
-        <v>2426</v>
+        <v>2444</v>
       </c>
       <c r="D859" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F859" t="s">
         <v>100</v>
@@ -24667,10 +24660,10 @@
         <v>0</v>
       </c>
       <c r="I859" s="1">
-        <v>46118.798611111109</v>
+        <v>46118.79791666667</v>
       </c>
       <c r="J859">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K859" t="s">
         <v>11</v>
@@ -24681,25 +24674,25 @@
         <v>37</v>
       </c>
       <c r="C860">
-        <v>4630</v>
+        <v>2426</v>
       </c>
       <c r="D860" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="F860" t="s">
         <v>100</v>
       </c>
       <c r="G860" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H860" s="2">
-        <v>8.5069444444444437E-3</v>
+        <v>0</v>
       </c>
       <c r="I860" s="1">
         <v>46118.798611111109</v>
       </c>
       <c r="J860">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K860" t="s">
         <v>11</v>
@@ -24710,64 +24703,64 @@
         <v>37</v>
       </c>
       <c r="C861">
-        <v>2452</v>
+        <v>4630</v>
       </c>
       <c r="D861" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="F861" t="s">
         <v>100</v>
       </c>
       <c r="G861" t="s">
+        <v>10</v>
+      </c>
+      <c r="H861" s="2">
+        <v>8.5069444444444437E-3</v>
+      </c>
+      <c r="I861" s="1">
+        <v>46118.798611111109</v>
+      </c>
+      <c r="J861">
+        <v>0</v>
+      </c>
+      <c r="K861" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="862" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B862" t="s">
+        <v>37</v>
+      </c>
+      <c r="C862">
+        <v>2452</v>
+      </c>
+      <c r="D862" t="s">
+        <v>68</v>
+      </c>
+      <c r="F862" t="s">
+        <v>100</v>
+      </c>
+      <c r="G862" t="s">
         <v>12</v>
       </c>
-      <c r="H861" s="2">
-        <v>0</v>
-      </c>
-      <c r="I861" s="1">
+      <c r="H862" s="2">
+        <v>0</v>
+      </c>
+      <c r="I862" s="1">
         <v>46118.799305555556</v>
       </c>
-      <c r="J861">
-        <v>0</v>
-      </c>
-      <c r="K861" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="862" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H862" s="2"/>
-      <c r="I862" s="1"/>
+      <c r="J862">
+        <v>0</v>
+      </c>
       <c r="K862" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="863" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H863" s="2"/>
+      <c r="I863" s="1"/>
+      <c r="K863" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="863" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B863" t="s">
-        <v>37</v>
-      </c>
-      <c r="C863">
-        <v>2447</v>
-      </c>
-      <c r="D863" t="s">
-        <v>69</v>
-      </c>
-      <c r="F863" t="s">
-        <v>100</v>
-      </c>
-      <c r="G863" t="s">
-        <v>10</v>
-      </c>
-      <c r="H863" s="2">
-        <v>8.0787037037037043E-3</v>
-      </c>
-      <c r="I863" s="1">
-        <v>46118.799305555556</v>
-      </c>
-      <c r="J863">
-        <v>0</v>
-      </c>
-      <c r="K863" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="864" spans="2:11" x14ac:dyDescent="0.25">
@@ -24775,10 +24768,10 @@
         <v>37</v>
       </c>
       <c r="C864">
-        <v>2436</v>
+        <v>2447</v>
       </c>
       <c r="D864" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F864" t="s">
         <v>100</v>
@@ -24787,10 +24780,10 @@
         <v>10</v>
       </c>
       <c r="H864" s="2">
-        <v>9.0162037037037034E-3</v>
+        <v>8.0787037037037043E-3</v>
       </c>
       <c r="I864" s="1">
-        <v>46118.8</v>
+        <v>46118.799305555556</v>
       </c>
       <c r="J864">
         <v>0</v>
@@ -24804,136 +24797,136 @@
         <v>37</v>
       </c>
       <c r="C865">
-        <v>2982</v>
+        <v>2436</v>
       </c>
       <c r="D865" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F865" t="s">
         <v>100</v>
       </c>
       <c r="G865" t="s">
+        <v>10</v>
+      </c>
+      <c r="H865" s="2">
+        <v>9.0162037037037034E-3</v>
+      </c>
+      <c r="I865" s="1">
+        <v>46118.8</v>
+      </c>
+      <c r="J865">
+        <v>0</v>
+      </c>
+      <c r="K865" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="866" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B866" t="s">
+        <v>37</v>
+      </c>
+      <c r="C866">
+        <v>2982</v>
+      </c>
+      <c r="D866" t="s">
+        <v>80</v>
+      </c>
+      <c r="F866" t="s">
+        <v>100</v>
+      </c>
+      <c r="G866" t="s">
         <v>12</v>
       </c>
-      <c r="H865" s="2">
+      <c r="H866" s="2">
         <v>5.3240740740740744E-4</v>
       </c>
-      <c r="I865" s="1">
+      <c r="I866" s="1">
         <v>46118.800694444442</v>
       </c>
-      <c r="J865">
+      <c r="J866">
         <v>2</v>
       </c>
-      <c r="K865" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="866" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H866" s="2"/>
-      <c r="I866" s="1"/>
       <c r="K866" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="867" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H867" s="2"/>
+      <c r="I867" s="1"/>
+      <c r="K867" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="867" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B867" t="s">
-        <v>37</v>
-      </c>
-      <c r="C867">
+    <row r="868" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B868" t="s">
+        <v>37</v>
+      </c>
+      <c r="C868">
         <v>3854</v>
       </c>
-      <c r="D867" t="s">
+      <c r="D868" t="s">
         <v>88</v>
       </c>
-      <c r="F867" t="s">
+      <c r="F868" t="s">
         <v>100</v>
       </c>
-      <c r="G867" t="s">
+      <c r="G868" t="s">
         <v>14</v>
       </c>
-      <c r="H867" s="2">
-        <v>0</v>
-      </c>
-      <c r="I867" s="1">
+      <c r="H868" s="2">
+        <v>0</v>
+      </c>
+      <c r="I868" s="1">
         <v>46118.800694444442</v>
       </c>
-      <c r="J867">
+      <c r="J868">
         <v>1</v>
       </c>
-      <c r="K867" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="868" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H868" s="2"/>
-      <c r="I868" s="1"/>
       <c r="K868" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="869" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H869" s="2"/>
+      <c r="I869" s="1"/>
+      <c r="K869" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="869" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B869" t="s">
-        <v>37</v>
-      </c>
-      <c r="C869">
+    <row r="870" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B870" t="s">
+        <v>37</v>
+      </c>
+      <c r="C870">
         <v>4885</v>
       </c>
-      <c r="D869" t="s">
+      <c r="D870" t="s">
         <v>90</v>
       </c>
-      <c r="F869" t="s">
+      <c r="F870" t="s">
         <v>100</v>
       </c>
-      <c r="G869" t="s">
+      <c r="G870" t="s">
         <v>12</v>
       </c>
-      <c r="H869" s="2">
+      <c r="H870" s="2">
         <v>9.2592592592592588E-5</v>
       </c>
-      <c r="I869" s="1">
+      <c r="I870" s="1">
         <v>46118.801388888889</v>
       </c>
-      <c r="J869">
+      <c r="J870">
         <v>2</v>
       </c>
-      <c r="K869" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="870" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H870" s="2"/>
-      <c r="I870" s="1"/>
       <c r="K870" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="871" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H871" s="2"/>
+      <c r="I871" s="1"/>
+      <c r="K871" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="871" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B871" t="s">
-        <v>37</v>
-      </c>
-      <c r="C871">
-        <v>2423</v>
-      </c>
-      <c r="D871" t="s">
-        <v>72</v>
-      </c>
-      <c r="F871" t="s">
-        <v>100</v>
-      </c>
-      <c r="G871" t="s">
-        <v>10</v>
-      </c>
-      <c r="H871" s="2">
-        <v>6.7013888888888887E-3</v>
-      </c>
-      <c r="I871" s="1">
-        <v>46118.801388888889</v>
-      </c>
-      <c r="J871">
-        <v>0</v>
-      </c>
-      <c r="K871" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="872" spans="2:11" x14ac:dyDescent="0.25">
@@ -24941,10 +24934,10 @@
         <v>37</v>
       </c>
       <c r="C872">
-        <v>2441</v>
+        <v>2423</v>
       </c>
       <c r="D872" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F872" t="s">
         <v>100</v>
@@ -24953,13 +24946,13 @@
         <v>10</v>
       </c>
       <c r="H872" s="2">
-        <v>6.7476851851851856E-3</v>
+        <v>6.7013888888888887E-3</v>
       </c>
       <c r="I872" s="1">
-        <v>46118.802083333336</v>
+        <v>46118.801388888889</v>
       </c>
       <c r="J872">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K872" t="s">
         <v>11</v>
@@ -24970,25 +24963,25 @@
         <v>37</v>
       </c>
       <c r="C873">
-        <v>2437</v>
+        <v>2441</v>
       </c>
       <c r="D873" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F873" t="s">
         <v>100</v>
       </c>
       <c r="G873" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H873" s="2">
-        <v>0</v>
+        <v>6.7476851851851856E-3</v>
       </c>
       <c r="I873" s="1">
-        <v>46118.802777777775</v>
+        <v>46118.802083333336</v>
       </c>
       <c r="J873">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K873" t="s">
         <v>11</v>
@@ -24999,10 +24992,10 @@
         <v>37</v>
       </c>
       <c r="C874">
-        <v>4886</v>
+        <v>2437</v>
       </c>
       <c r="D874" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="F874" t="s">
         <v>100</v>
@@ -25017,7 +25010,7 @@
         <v>46118.802777777775</v>
       </c>
       <c r="J874">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K874" t="s">
         <v>11</v>
@@ -25028,173 +25021,874 @@
         <v>37</v>
       </c>
       <c r="C875">
-        <v>5188</v>
+        <v>4886</v>
       </c>
       <c r="D875" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F875" t="s">
         <v>100</v>
       </c>
       <c r="G875" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H875" s="2">
+        <v>0</v>
+      </c>
+      <c r="I875" s="1">
+        <v>46118.802777777775</v>
+      </c>
+      <c r="J875">
+        <v>3</v>
+      </c>
+      <c r="K875" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="876" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B876" t="s">
+        <v>37</v>
+      </c>
+      <c r="C876">
+        <v>5188</v>
+      </c>
+      <c r="D876" t="s">
+        <v>97</v>
+      </c>
+      <c r="F876" t="s">
+        <v>100</v>
+      </c>
+      <c r="G876" t="s">
+        <v>10</v>
+      </c>
+      <c r="H876" s="2">
         <v>8.1944444444444452E-3</v>
       </c>
-      <c r="I875" s="1">
+      <c r="I876" s="1">
         <v>46118.803472222222</v>
       </c>
-      <c r="J875">
-        <v>0</v>
-      </c>
-      <c r="K875" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="876" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H876" s="2"/>
-      <c r="I876" s="1"/>
+      <c r="J876">
+        <v>0</v>
+      </c>
+      <c r="K876" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="877" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H877" s="2"/>
-      <c r="I877" s="1"/>
+      <c r="B877" t="s">
+        <v>37</v>
+      </c>
+      <c r="C877">
+        <v>5523</v>
+      </c>
+      <c r="D877" t="s">
+        <v>101</v>
+      </c>
+      <c r="F877" t="s">
+        <v>102</v>
+      </c>
+      <c r="G877" t="s">
+        <v>13</v>
+      </c>
+      <c r="H877" s="2">
+        <v>0</v>
+      </c>
+      <c r="I877" s="1">
+        <v>46136.710763888892</v>
+      </c>
+      <c r="J877">
+        <v>0</v>
+      </c>
+      <c r="K877" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="878" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H878" s="2"/>
-      <c r="I878" s="1"/>
+      <c r="B878" t="s">
+        <v>37</v>
+      </c>
+      <c r="C878">
+        <v>5448</v>
+      </c>
+      <c r="D878" t="s">
+        <v>103</v>
+      </c>
+      <c r="F878" t="s">
+        <v>102</v>
+      </c>
+      <c r="G878" t="s">
+        <v>13</v>
+      </c>
+      <c r="H878" s="2">
+        <v>0</v>
+      </c>
+      <c r="I878" s="1">
+        <v>46136.711458333331</v>
+      </c>
+      <c r="J878">
+        <v>0</v>
+      </c>
+      <c r="K878" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="879" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="I879" s="1"/>
+      <c r="B879" t="s">
+        <v>37</v>
+      </c>
+      <c r="C879">
+        <v>5447</v>
+      </c>
+      <c r="D879" t="s">
+        <v>104</v>
+      </c>
+      <c r="F879" t="s">
+        <v>102</v>
+      </c>
+      <c r="G879" t="s">
+        <v>13</v>
+      </c>
+      <c r="H879">
+        <v>0</v>
+      </c>
+      <c r="I879" s="1">
+        <v>46136.712152777778</v>
+      </c>
+      <c r="J879">
+        <v>0</v>
+      </c>
+      <c r="K879" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="880" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H880" s="2"/>
-      <c r="I880" s="1"/>
-    </row>
-    <row r="881" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H881" s="2"/>
-      <c r="I881" s="1"/>
-    </row>
-    <row r="882" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H882" s="2"/>
-      <c r="I882" s="1"/>
-    </row>
-    <row r="883" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H883" s="2"/>
-      <c r="I883" s="1"/>
-    </row>
-    <row r="884" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H884" s="2"/>
-      <c r="I884" s="1"/>
-    </row>
-    <row r="885" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H885" s="2"/>
-      <c r="I885" s="1"/>
-    </row>
-    <row r="886" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H886" s="2"/>
-      <c r="I886" s="1"/>
-    </row>
-    <row r="887" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H887" s="2"/>
-      <c r="I887" s="1"/>
-    </row>
-    <row r="888" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H888" s="2"/>
-      <c r="I888" s="1"/>
-    </row>
-    <row r="889" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H889" s="2"/>
-      <c r="I889" s="1"/>
-    </row>
-    <row r="890" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H890" s="2"/>
-      <c r="I890" s="1"/>
-    </row>
-    <row r="891" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H891" s="2"/>
-      <c r="I891" s="1"/>
-    </row>
-    <row r="892" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H892" s="2"/>
-      <c r="I892" s="1"/>
-    </row>
-    <row r="893" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H893" s="2"/>
-      <c r="I893" s="1"/>
-    </row>
-    <row r="894" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H894" s="2"/>
-      <c r="I894" s="1"/>
-    </row>
-    <row r="895" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H895" s="2"/>
-      <c r="I895" s="1"/>
-    </row>
-    <row r="896" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H896" s="2"/>
-      <c r="I896" s="1"/>
-    </row>
-    <row r="897" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H897" s="2"/>
-      <c r="I897" s="1"/>
-    </row>
-    <row r="898" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H898" s="2"/>
-      <c r="I898" s="1"/>
-    </row>
-    <row r="899" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H899" s="2"/>
-      <c r="I899" s="1"/>
-    </row>
-    <row r="900" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H900" s="2"/>
-      <c r="I900" s="1"/>
-    </row>
-    <row r="901" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H901" s="2"/>
-      <c r="I901" s="1"/>
-    </row>
-    <row r="902" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H902" s="2"/>
-      <c r="I902" s="1"/>
-    </row>
-    <row r="903" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H903" s="2"/>
-      <c r="I903" s="1"/>
-    </row>
-    <row r="904" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B880" t="s">
+        <v>37</v>
+      </c>
+      <c r="C880">
+        <v>5523</v>
+      </c>
+      <c r="D880" t="s">
+        <v>101</v>
+      </c>
+      <c r="F880" t="s">
+        <v>99</v>
+      </c>
+      <c r="G880" t="s">
+        <v>13</v>
+      </c>
+      <c r="H880" s="2">
+        <v>0</v>
+      </c>
+      <c r="I880" s="1">
+        <v>46136.712152777778</v>
+      </c>
+      <c r="J880">
+        <v>0</v>
+      </c>
+      <c r="K880" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="881" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B881" t="s">
+        <v>37</v>
+      </c>
+      <c r="C881">
+        <v>5448</v>
+      </c>
+      <c r="D881" t="s">
+        <v>103</v>
+      </c>
+      <c r="F881" t="s">
+        <v>99</v>
+      </c>
+      <c r="G881" t="s">
+        <v>13</v>
+      </c>
+      <c r="H881" s="2">
+        <v>0</v>
+      </c>
+      <c r="I881" s="1">
+        <v>46136.712847222225</v>
+      </c>
+      <c r="J881">
+        <v>0</v>
+      </c>
+      <c r="K881" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="882" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B882" t="s">
+        <v>37</v>
+      </c>
+      <c r="C882">
+        <v>5447</v>
+      </c>
+      <c r="D882" t="s">
+        <v>104</v>
+      </c>
+      <c r="F882" t="s">
+        <v>99</v>
+      </c>
+      <c r="G882" t="s">
+        <v>10</v>
+      </c>
+      <c r="H882" s="2">
+        <v>8.2175925925925923E-3</v>
+      </c>
+      <c r="I882" s="1">
+        <v>46136.713541666664</v>
+      </c>
+      <c r="J882">
+        <v>0</v>
+      </c>
+      <c r="K882" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="883" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B883" t="s">
+        <v>37</v>
+      </c>
+      <c r="C883">
+        <v>5523</v>
+      </c>
+      <c r="D883" t="s">
+        <v>101</v>
+      </c>
+      <c r="F883" t="s">
+        <v>36</v>
+      </c>
+      <c r="G883" t="s">
+        <v>13</v>
+      </c>
+      <c r="H883" s="2">
+        <v>0</v>
+      </c>
+      <c r="I883" s="1">
+        <v>46136.713541666664</v>
+      </c>
+      <c r="J883">
+        <v>0</v>
+      </c>
+      <c r="K883" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="884" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B884" t="s">
+        <v>37</v>
+      </c>
+      <c r="C884">
+        <v>5448</v>
+      </c>
+      <c r="D884" t="s">
+        <v>103</v>
+      </c>
+      <c r="F884" t="s">
+        <v>36</v>
+      </c>
+      <c r="G884" t="s">
+        <v>13</v>
+      </c>
+      <c r="H884" s="2">
+        <v>0</v>
+      </c>
+      <c r="I884" s="1">
+        <v>46136.714236111111</v>
+      </c>
+      <c r="J884">
+        <v>0</v>
+      </c>
+      <c r="K884" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="885" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B885" t="s">
+        <v>37</v>
+      </c>
+      <c r="C885">
+        <v>5447</v>
+      </c>
+      <c r="D885" t="s">
+        <v>104</v>
+      </c>
+      <c r="F885" t="s">
+        <v>36</v>
+      </c>
+      <c r="G885" t="s">
+        <v>13</v>
+      </c>
+      <c r="H885" s="2">
+        <v>0</v>
+      </c>
+      <c r="I885" s="1">
+        <v>46136.714930555558</v>
+      </c>
+      <c r="J885">
+        <v>0</v>
+      </c>
+      <c r="K885" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="886" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B886" t="s">
+        <v>37</v>
+      </c>
+      <c r="C886">
+        <v>5523</v>
+      </c>
+      <c r="D886" t="s">
+        <v>101</v>
+      </c>
+      <c r="F886" t="s">
+        <v>35</v>
+      </c>
+      <c r="G886" t="s">
+        <v>13</v>
+      </c>
+      <c r="H886" s="2">
+        <v>0</v>
+      </c>
+      <c r="I886" s="1">
+        <v>46136.715624999997</v>
+      </c>
+      <c r="J886">
+        <v>0</v>
+      </c>
+      <c r="K886" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="887" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B887" t="s">
+        <v>37</v>
+      </c>
+      <c r="C887">
+        <v>5448</v>
+      </c>
+      <c r="D887" t="s">
+        <v>103</v>
+      </c>
+      <c r="F887" t="s">
+        <v>35</v>
+      </c>
+      <c r="G887" t="s">
+        <v>13</v>
+      </c>
+      <c r="H887" s="2">
+        <v>0</v>
+      </c>
+      <c r="I887" s="1">
+        <v>46136.715624999997</v>
+      </c>
+      <c r="J887">
+        <v>0</v>
+      </c>
+      <c r="K887" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="888" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B888" t="s">
+        <v>37</v>
+      </c>
+      <c r="C888">
+        <v>5447</v>
+      </c>
+      <c r="D888" t="s">
+        <v>104</v>
+      </c>
+      <c r="F888" t="s">
+        <v>35</v>
+      </c>
+      <c r="G888" t="s">
+        <v>13</v>
+      </c>
+      <c r="H888" s="2">
+        <v>0</v>
+      </c>
+      <c r="I888" s="1">
+        <v>46136.716319444444</v>
+      </c>
+      <c r="J888">
+        <v>0</v>
+      </c>
+      <c r="K888" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="889" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B889" t="s">
+        <v>37</v>
+      </c>
+      <c r="C889">
+        <v>5523</v>
+      </c>
+      <c r="D889" t="s">
+        <v>101</v>
+      </c>
+      <c r="F889" t="s">
+        <v>20</v>
+      </c>
+      <c r="G889" t="s">
+        <v>13</v>
+      </c>
+      <c r="H889" s="2">
+        <v>0</v>
+      </c>
+      <c r="I889" s="1">
+        <v>46136.717013888891</v>
+      </c>
+      <c r="J889">
+        <v>0</v>
+      </c>
+      <c r="K889" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="890" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B890" t="s">
+        <v>37</v>
+      </c>
+      <c r="C890">
+        <v>5448</v>
+      </c>
+      <c r="D890" t="s">
+        <v>103</v>
+      </c>
+      <c r="F890" t="s">
+        <v>20</v>
+      </c>
+      <c r="G890" t="s">
+        <v>13</v>
+      </c>
+      <c r="H890" s="2">
+        <v>0</v>
+      </c>
+      <c r="I890" s="1">
+        <v>46136.717013888891</v>
+      </c>
+      <c r="J890">
+        <v>0</v>
+      </c>
+      <c r="K890" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="891" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B891" t="s">
+        <v>37</v>
+      </c>
+      <c r="C891">
+        <v>5447</v>
+      </c>
+      <c r="D891" t="s">
+        <v>104</v>
+      </c>
+      <c r="F891" t="s">
+        <v>20</v>
+      </c>
+      <c r="G891" t="s">
+        <v>13</v>
+      </c>
+      <c r="H891" s="2">
+        <v>0</v>
+      </c>
+      <c r="I891" s="1">
+        <v>46136.71770833333</v>
+      </c>
+      <c r="J891">
+        <v>0</v>
+      </c>
+      <c r="K891" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="892" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B892" t="s">
+        <v>37</v>
+      </c>
+      <c r="C892">
+        <v>5523</v>
+      </c>
+      <c r="D892" t="s">
+        <v>101</v>
+      </c>
+      <c r="F892" t="s">
+        <v>100</v>
+      </c>
+      <c r="G892" t="s">
+        <v>13</v>
+      </c>
+      <c r="H892" s="2">
+        <v>0</v>
+      </c>
+      <c r="I892" s="1">
+        <v>46136.718402777777</v>
+      </c>
+      <c r="J892">
+        <v>0</v>
+      </c>
+      <c r="K892" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="893" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B893" t="s">
+        <v>37</v>
+      </c>
+      <c r="C893">
+        <v>5448</v>
+      </c>
+      <c r="D893" t="s">
+        <v>103</v>
+      </c>
+      <c r="F893" t="s">
+        <v>100</v>
+      </c>
+      <c r="G893" t="s">
+        <v>13</v>
+      </c>
+      <c r="H893" s="2">
+        <v>0</v>
+      </c>
+      <c r="I893" s="1">
+        <v>46136.718402777777</v>
+      </c>
+      <c r="J893">
+        <v>0</v>
+      </c>
+      <c r="K893" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="894" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B894" t="s">
+        <v>37</v>
+      </c>
+      <c r="C894">
+        <v>5447</v>
+      </c>
+      <c r="D894" t="s">
+        <v>104</v>
+      </c>
+      <c r="F894" t="s">
+        <v>100</v>
+      </c>
+      <c r="G894" t="s">
+        <v>13</v>
+      </c>
+      <c r="H894" s="2">
+        <v>0</v>
+      </c>
+      <c r="I894" s="1">
+        <v>46136.719097222223</v>
+      </c>
+      <c r="J894">
+        <v>0</v>
+      </c>
+      <c r="K894" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="895" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B895" t="s">
+        <v>37</v>
+      </c>
+      <c r="C895">
+        <v>5523</v>
+      </c>
+      <c r="D895" t="s">
+        <v>101</v>
+      </c>
+      <c r="F895" t="s">
+        <v>16</v>
+      </c>
+      <c r="G895" t="s">
+        <v>13</v>
+      </c>
+      <c r="H895" s="2">
+        <v>0</v>
+      </c>
+      <c r="I895" s="1">
+        <v>46136.71979166667</v>
+      </c>
+      <c r="J895">
+        <v>0</v>
+      </c>
+      <c r="K895" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="896" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B896" t="s">
+        <v>37</v>
+      </c>
+      <c r="C896">
+        <v>5448</v>
+      </c>
+      <c r="D896" t="s">
+        <v>103</v>
+      </c>
+      <c r="F896" t="s">
+        <v>16</v>
+      </c>
+      <c r="G896" t="s">
+        <v>13</v>
+      </c>
+      <c r="H896" s="2">
+        <v>0</v>
+      </c>
+      <c r="I896" s="1">
+        <v>46136.71979166667</v>
+      </c>
+      <c r="J896">
+        <v>0</v>
+      </c>
+      <c r="K896" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="897" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B897" t="s">
+        <v>37</v>
+      </c>
+      <c r="C897">
+        <v>5447</v>
+      </c>
+      <c r="D897" t="s">
+        <v>104</v>
+      </c>
+      <c r="F897" t="s">
+        <v>16</v>
+      </c>
+      <c r="G897" t="s">
+        <v>13</v>
+      </c>
+      <c r="H897" s="2">
+        <v>0</v>
+      </c>
+      <c r="I897" s="1">
+        <v>46136.720486111109</v>
+      </c>
+      <c r="J897">
+        <v>0</v>
+      </c>
+      <c r="K897" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="898" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B898" t="s">
+        <v>37</v>
+      </c>
+      <c r="C898">
+        <v>5523</v>
+      </c>
+      <c r="D898" t="s">
+        <v>101</v>
+      </c>
+      <c r="F898" t="s">
+        <v>29</v>
+      </c>
+      <c r="G898" t="s">
+        <v>13</v>
+      </c>
+      <c r="H898" s="2">
+        <v>0</v>
+      </c>
+      <c r="I898" s="1">
+        <v>46136.721180555556</v>
+      </c>
+      <c r="J898">
+        <v>0</v>
+      </c>
+      <c r="K898" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="899" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B899" t="s">
+        <v>37</v>
+      </c>
+      <c r="C899">
+        <v>5448</v>
+      </c>
+      <c r="D899" t="s">
+        <v>103</v>
+      </c>
+      <c r="F899" t="s">
+        <v>29</v>
+      </c>
+      <c r="G899" t="s">
+        <v>13</v>
+      </c>
+      <c r="H899" s="2">
+        <v>0</v>
+      </c>
+      <c r="I899" s="1">
+        <v>46136.721875000003</v>
+      </c>
+      <c r="J899">
+        <v>0</v>
+      </c>
+      <c r="K899" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="900" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B900" t="s">
+        <v>37</v>
+      </c>
+      <c r="C900">
+        <v>5447</v>
+      </c>
+      <c r="D900" t="s">
+        <v>104</v>
+      </c>
+      <c r="F900" t="s">
+        <v>29</v>
+      </c>
+      <c r="G900" t="s">
+        <v>13</v>
+      </c>
+      <c r="H900" s="2">
+        <v>0</v>
+      </c>
+      <c r="I900" s="1">
+        <v>46136.721875000003</v>
+      </c>
+      <c r="J900">
+        <v>0</v>
+      </c>
+      <c r="K900" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="901" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B901" t="s">
+        <v>37</v>
+      </c>
+      <c r="C901">
+        <v>5523</v>
+      </c>
+      <c r="D901" t="s">
+        <v>101</v>
+      </c>
+      <c r="F901" t="s">
+        <v>105</v>
+      </c>
+      <c r="G901" t="s">
+        <v>13</v>
+      </c>
+      <c r="H901" s="2">
+        <v>0</v>
+      </c>
+      <c r="I901" s="1">
+        <v>46136.722569444442</v>
+      </c>
+      <c r="J901">
+        <v>0</v>
+      </c>
+      <c r="K901" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="902" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B902" t="s">
+        <v>37</v>
+      </c>
+      <c r="C902">
+        <v>5448</v>
+      </c>
+      <c r="D902" t="s">
+        <v>103</v>
+      </c>
+      <c r="F902" t="s">
+        <v>105</v>
+      </c>
+      <c r="G902" t="s">
+        <v>13</v>
+      </c>
+      <c r="H902" s="2">
+        <v>0</v>
+      </c>
+      <c r="I902" s="1">
+        <v>46136.723263888889</v>
+      </c>
+      <c r="J902">
+        <v>0</v>
+      </c>
+      <c r="K902" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="903" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B903" t="s">
+        <v>37</v>
+      </c>
+      <c r="C903">
+        <v>5447</v>
+      </c>
+      <c r="D903" t="s">
+        <v>104</v>
+      </c>
+      <c r="F903" t="s">
+        <v>105</v>
+      </c>
+      <c r="G903" t="s">
+        <v>13</v>
+      </c>
+      <c r="H903" s="2">
+        <v>0</v>
+      </c>
+      <c r="I903" s="1">
+        <v>46136.723958333336</v>
+      </c>
+      <c r="J903">
+        <v>0</v>
+      </c>
+      <c r="K903" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="904" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H904" s="2"/>
       <c r="I904" s="1"/>
     </row>
-    <row r="905" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="905" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H905" s="2"/>
       <c r="I905" s="1"/>
     </row>
-    <row r="906" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="906" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H906" s="2"/>
       <c r="I906" s="1"/>
     </row>
-    <row r="907" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="907" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I907" s="1"/>
     </row>
-    <row r="908" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="908" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H908" s="2"/>
       <c r="I908" s="1"/>
     </row>
-    <row r="909" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="909" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H909" s="2"/>
       <c r="I909" s="1"/>
     </row>
-    <row r="910" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="910" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H910" s="2"/>
       <c r="I910" s="1"/>
     </row>
-    <row r="911" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="911" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
     </row>
-    <row r="912" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="912" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H912" s="2"/>
       <c r="I912" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\All City Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4F314B-00AE-4313-AF87-A9B7D6ED4857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F35AA3D-287E-4518-8024-9FB10B96C78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4324" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4517" uniqueCount="107">
   <si>
     <t>Company Name</t>
   </si>
@@ -357,6 +357,9 @@
   </si>
   <si>
     <t>3 Points of Contact</t>
+  </si>
+  <si>
+    <t>Charles Hernandez</t>
   </si>
 </sst>
 </file>
@@ -24069,7 +24072,7 @@
         <v>46118.768634259257</v>
       </c>
       <c r="J837">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K837" t="s">
         <v>11</v>
@@ -24098,7 +24101,7 @@
         <v>46118.769328703704</v>
       </c>
       <c r="J838">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K838" t="s">
         <v>11</v>
@@ -24118,16 +24121,16 @@
         <v>100</v>
       </c>
       <c r="G839" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H839" s="2">
-        <v>0</v>
+        <v>7.013888888888889E-3</v>
       </c>
       <c r="I839" s="1">
         <v>46118.769328703704</v>
       </c>
       <c r="J839">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K839" t="s">
         <v>11</v>
@@ -24234,84 +24237,62 @@
         <v>100</v>
       </c>
       <c r="G843" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H843" s="2">
-        <v>0</v>
+        <v>5.5092592592592589E-3</v>
       </c>
       <c r="I843" s="1">
         <v>46118.771412037036</v>
       </c>
       <c r="J843">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K843" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="844" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B844" t="s">
-        <v>37</v>
-      </c>
-      <c r="C844">
+      <c r="H844" s="2"/>
+      <c r="I844" s="1"/>
+      <c r="K844" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="845" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B845" t="s">
+        <v>37</v>
+      </c>
+      <c r="C845">
         <v>2983</v>
       </c>
-      <c r="D844" t="s">
+      <c r="D845" t="s">
         <v>78</v>
       </c>
-      <c r="F844" t="s">
+      <c r="F845" t="s">
         <v>100</v>
       </c>
-      <c r="G844" t="s">
+      <c r="G845" t="s">
         <v>14</v>
       </c>
-      <c r="H844" s="2">
-        <v>0</v>
-      </c>
-      <c r="I844" s="1">
+      <c r="H845" s="2">
+        <v>0</v>
+      </c>
+      <c r="I845" s="1">
         <v>46118.771412037036</v>
       </c>
-      <c r="J844">
+      <c r="J845">
         <v>2</v>
       </c>
-      <c r="K844" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="845" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H845" s="2"/>
-      <c r="I845" s="1"/>
       <c r="K845" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="846" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H846" s="2"/>
+      <c r="I846" s="1"/>
+      <c r="K846" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="846" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B846" t="s">
-        <v>37</v>
-      </c>
-      <c r="C846">
-        <v>2425</v>
-      </c>
-      <c r="D846" t="s">
-        <v>49</v>
-      </c>
-      <c r="F846" t="s">
-        <v>100</v>
-      </c>
-      <c r="G846" t="s">
-        <v>10</v>
-      </c>
-      <c r="H846" s="2">
-        <v>9.3761574074074081E-2</v>
-      </c>
-      <c r="I846" s="1">
-        <v>46118.772106481483</v>
-      </c>
-      <c r="J846">
-        <v>1</v>
-      </c>
-      <c r="K846" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="847" spans="2:11" x14ac:dyDescent="0.25">
@@ -24319,10 +24300,10 @@
         <v>37</v>
       </c>
       <c r="C847">
-        <v>5189</v>
+        <v>2425</v>
       </c>
       <c r="D847" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="F847" t="s">
         <v>100</v>
@@ -24331,13 +24312,13 @@
         <v>10</v>
       </c>
       <c r="H847" s="2">
-        <v>9.2476851851851852E-3</v>
+        <v>9.3761574074074081E-2</v>
       </c>
       <c r="I847" s="1">
-        <v>46118.772800925923</v>
+        <v>46118.772106481483</v>
       </c>
       <c r="J847">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K847" t="s">
         <v>11</v>
@@ -24348,10 +24329,10 @@
         <v>37</v>
       </c>
       <c r="C848">
-        <v>3791</v>
+        <v>5189</v>
       </c>
       <c r="D848" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F848" t="s">
         <v>100</v>
@@ -24360,13 +24341,13 @@
         <v>10</v>
       </c>
       <c r="H848" s="2">
-        <v>7.8472222222222224E-3</v>
+        <v>9.2476851851851852E-3</v>
       </c>
       <c r="I848" s="1">
-        <v>46118.793055555558</v>
+        <v>46118.772800925923</v>
       </c>
       <c r="J848">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K848" t="s">
         <v>11</v>
@@ -24377,25 +24358,25 @@
         <v>37</v>
       </c>
       <c r="C849">
-        <v>2435</v>
+        <v>3791</v>
       </c>
       <c r="D849" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="F849" t="s">
         <v>100</v>
       </c>
       <c r="G849" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H849" s="2">
-        <v>0</v>
+        <v>7.8472222222222224E-3</v>
       </c>
       <c r="I849" s="1">
-        <v>46118.793749999997</v>
+        <v>46118.793055555558</v>
       </c>
       <c r="J849">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K849" t="s">
         <v>11</v>
@@ -24406,25 +24387,25 @@
         <v>37</v>
       </c>
       <c r="C850">
-        <v>2439</v>
+        <v>2435</v>
       </c>
       <c r="D850" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F850" t="s">
         <v>100</v>
       </c>
       <c r="G850" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H850" s="2">
-        <v>7.0254629629629634E-3</v>
+        <v>0</v>
       </c>
       <c r="I850" s="1">
-        <v>46118.794444444444</v>
+        <v>46118.793749999997</v>
       </c>
       <c r="J850">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K850" t="s">
         <v>11</v>
@@ -24435,10 +24416,10 @@
         <v>37</v>
       </c>
       <c r="C851">
-        <v>2432</v>
+        <v>2439</v>
       </c>
       <c r="D851" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F851" t="s">
         <v>100</v>
@@ -24447,13 +24428,13 @@
         <v>10</v>
       </c>
       <c r="H851" s="2">
-        <v>1.3101851851851852E-2</v>
+        <v>7.0254629629629634E-3</v>
       </c>
       <c r="I851" s="1">
         <v>46118.794444444444</v>
       </c>
       <c r="J851">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K851" t="s">
         <v>11</v>
@@ -24464,64 +24445,64 @@
         <v>37</v>
       </c>
       <c r="C852">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="D852" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F852" t="s">
         <v>100</v>
       </c>
       <c r="G852" t="s">
+        <v>10</v>
+      </c>
+      <c r="H852" s="2">
+        <v>1.3101851851851852E-2</v>
+      </c>
+      <c r="I852" s="1">
+        <v>46118.794444444444</v>
+      </c>
+      <c r="J852">
+        <v>0</v>
+      </c>
+      <c r="K852" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="853" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B853" t="s">
+        <v>37</v>
+      </c>
+      <c r="C853">
+        <v>2431</v>
+      </c>
+      <c r="D853" t="s">
+        <v>57</v>
+      </c>
+      <c r="F853" t="s">
+        <v>100</v>
+      </c>
+      <c r="G853" t="s">
         <v>12</v>
       </c>
-      <c r="H852" s="2">
-        <v>0</v>
-      </c>
-      <c r="I852" s="1">
+      <c r="H853" s="2">
+        <v>0</v>
+      </c>
+      <c r="I853" s="1">
         <v>46118.795138888891</v>
       </c>
-      <c r="J852">
+      <c r="J853">
         <v>1</v>
       </c>
-      <c r="K852" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="853" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H853" s="2"/>
-      <c r="I853" s="1"/>
       <c r="K853" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="854" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H854" s="2"/>
+      <c r="I854" s="1"/>
+      <c r="K854" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="854" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B854" t="s">
-        <v>37</v>
-      </c>
-      <c r="C854">
-        <v>2772</v>
-      </c>
-      <c r="D854" t="s">
-        <v>77</v>
-      </c>
-      <c r="F854" t="s">
-        <v>100</v>
-      </c>
-      <c r="G854" t="s">
-        <v>10</v>
-      </c>
-      <c r="H854" s="2">
-        <v>7.2106481481481483E-3</v>
-      </c>
-      <c r="I854" s="1">
-        <v>46118.79583333333</v>
-      </c>
-      <c r="J854">
-        <v>0</v>
-      </c>
-      <c r="K854" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="855" spans="2:11" x14ac:dyDescent="0.25">
@@ -24529,10 +24510,10 @@
         <v>37</v>
       </c>
       <c r="C855">
-        <v>3482</v>
+        <v>2772</v>
       </c>
       <c r="D855" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F855" t="s">
         <v>100</v>
@@ -24541,13 +24522,13 @@
         <v>10</v>
       </c>
       <c r="H855" s="2">
-        <v>7.0254629629629634E-3</v>
+        <v>7.2106481481481483E-3</v>
       </c>
       <c r="I855" s="1">
         <v>46118.79583333333</v>
       </c>
       <c r="J855">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K855" t="s">
         <v>11</v>
@@ -24558,25 +24539,25 @@
         <v>37</v>
       </c>
       <c r="C856">
-        <v>5204</v>
+        <v>3482</v>
       </c>
       <c r="D856" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="F856" t="s">
         <v>100</v>
       </c>
       <c r="G856" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H856" s="2">
-        <v>0</v>
+        <v>7.0254629629629634E-3</v>
       </c>
       <c r="I856" s="1">
-        <v>46118.796527777777</v>
+        <v>46118.79583333333</v>
       </c>
       <c r="J856">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K856" t="s">
         <v>11</v>
@@ -24587,25 +24568,25 @@
         <v>37</v>
       </c>
       <c r="C857">
-        <v>2449</v>
+        <v>5204</v>
       </c>
       <c r="D857" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="F857" t="s">
         <v>100</v>
       </c>
       <c r="G857" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H857" s="2">
-        <v>7.8009259259259256E-3</v>
+        <v>0</v>
       </c>
       <c r="I857" s="1">
-        <v>46118.797222222223</v>
+        <v>46118.796527777777</v>
       </c>
       <c r="J857">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K857" t="s">
         <v>11</v>
@@ -24616,25 +24597,25 @@
         <v>37</v>
       </c>
       <c r="C858">
-        <v>2418</v>
+        <v>2449</v>
       </c>
       <c r="D858" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F858" t="s">
         <v>100</v>
       </c>
       <c r="G858" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H858" s="2">
-        <v>0</v>
+        <v>7.8009259259259256E-3</v>
       </c>
       <c r="I858" s="1">
         <v>46118.797222222223</v>
       </c>
       <c r="J858">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K858" t="s">
         <v>11</v>
@@ -24645,10 +24626,10 @@
         <v>37</v>
       </c>
       <c r="C859">
-        <v>2444</v>
+        <v>2418</v>
       </c>
       <c r="D859" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F859" t="s">
         <v>100</v>
@@ -24660,10 +24641,10 @@
         <v>0</v>
       </c>
       <c r="I859" s="1">
-        <v>46118.79791666667</v>
+        <v>46118.797222222223</v>
       </c>
       <c r="J859">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K859" t="s">
         <v>11</v>
@@ -24674,10 +24655,10 @@
         <v>37</v>
       </c>
       <c r="C860">
-        <v>2426</v>
+        <v>2444</v>
       </c>
       <c r="D860" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F860" t="s">
         <v>100</v>
@@ -24689,10 +24670,10 @@
         <v>0</v>
       </c>
       <c r="I860" s="1">
-        <v>46118.798611111109</v>
+        <v>46118.79791666667</v>
       </c>
       <c r="J860">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K860" t="s">
         <v>11</v>
@@ -24703,25 +24684,25 @@
         <v>37</v>
       </c>
       <c r="C861">
-        <v>4630</v>
+        <v>2426</v>
       </c>
       <c r="D861" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="F861" t="s">
         <v>100</v>
       </c>
       <c r="G861" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H861" s="2">
-        <v>8.5069444444444437E-3</v>
+        <v>0</v>
       </c>
       <c r="I861" s="1">
         <v>46118.798611111109</v>
       </c>
       <c r="J861">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K861" t="s">
         <v>11</v>
@@ -24732,64 +24713,64 @@
         <v>37</v>
       </c>
       <c r="C862">
-        <v>2452</v>
+        <v>4630</v>
       </c>
       <c r="D862" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="F862" t="s">
         <v>100</v>
       </c>
       <c r="G862" t="s">
+        <v>10</v>
+      </c>
+      <c r="H862" s="2">
+        <v>8.5069444444444437E-3</v>
+      </c>
+      <c r="I862" s="1">
+        <v>46118.798611111109</v>
+      </c>
+      <c r="J862">
+        <v>0</v>
+      </c>
+      <c r="K862" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="863" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B863" t="s">
+        <v>37</v>
+      </c>
+      <c r="C863">
+        <v>2452</v>
+      </c>
+      <c r="D863" t="s">
+        <v>68</v>
+      </c>
+      <c r="F863" t="s">
+        <v>100</v>
+      </c>
+      <c r="G863" t="s">
         <v>12</v>
       </c>
-      <c r="H862" s="2">
-        <v>0</v>
-      </c>
-      <c r="I862" s="1">
+      <c r="H863" s="2">
+        <v>0</v>
+      </c>
+      <c r="I863" s="1">
         <v>46118.799305555556</v>
       </c>
-      <c r="J862">
-        <v>0</v>
-      </c>
-      <c r="K862" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="863" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H863" s="2"/>
-      <c r="I863" s="1"/>
+      <c r="J863">
+        <v>0</v>
+      </c>
       <c r="K863" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="864" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H864" s="2"/>
+      <c r="I864" s="1"/>
+      <c r="K864" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="864" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B864" t="s">
-        <v>37</v>
-      </c>
-      <c r="C864">
-        <v>2447</v>
-      </c>
-      <c r="D864" t="s">
-        <v>69</v>
-      </c>
-      <c r="F864" t="s">
-        <v>100</v>
-      </c>
-      <c r="G864" t="s">
-        <v>10</v>
-      </c>
-      <c r="H864" s="2">
-        <v>8.0787037037037043E-3</v>
-      </c>
-      <c r="I864" s="1">
-        <v>46118.799305555556</v>
-      </c>
-      <c r="J864">
-        <v>0</v>
-      </c>
-      <c r="K864" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="865" spans="2:11" x14ac:dyDescent="0.25">
@@ -24797,10 +24778,10 @@
         <v>37</v>
       </c>
       <c r="C865">
-        <v>2436</v>
+        <v>2447</v>
       </c>
       <c r="D865" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F865" t="s">
         <v>100</v>
@@ -24809,10 +24790,10 @@
         <v>10</v>
       </c>
       <c r="H865" s="2">
-        <v>9.0162037037037034E-3</v>
+        <v>8.0787037037037043E-3</v>
       </c>
       <c r="I865" s="1">
-        <v>46118.8</v>
+        <v>46118.799305555556</v>
       </c>
       <c r="J865">
         <v>0</v>
@@ -24826,136 +24807,136 @@
         <v>37</v>
       </c>
       <c r="C866">
-        <v>2982</v>
+        <v>2436</v>
       </c>
       <c r="D866" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F866" t="s">
         <v>100</v>
       </c>
       <c r="G866" t="s">
+        <v>10</v>
+      </c>
+      <c r="H866" s="2">
+        <v>9.0162037037037034E-3</v>
+      </c>
+      <c r="I866" s="1">
+        <v>46118.8</v>
+      </c>
+      <c r="J866">
+        <v>0</v>
+      </c>
+      <c r="K866" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="867" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B867" t="s">
+        <v>37</v>
+      </c>
+      <c r="C867">
+        <v>2982</v>
+      </c>
+      <c r="D867" t="s">
+        <v>80</v>
+      </c>
+      <c r="F867" t="s">
+        <v>100</v>
+      </c>
+      <c r="G867" t="s">
         <v>12</v>
       </c>
-      <c r="H866" s="2">
+      <c r="H867" s="2">
         <v>5.3240740740740744E-4</v>
       </c>
-      <c r="I866" s="1">
+      <c r="I867" s="1">
         <v>46118.800694444442</v>
       </c>
-      <c r="J866">
+      <c r="J867">
         <v>2</v>
       </c>
-      <c r="K866" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="867" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H867" s="2"/>
-      <c r="I867" s="1"/>
       <c r="K867" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="868" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H868" s="2"/>
+      <c r="I868" s="1"/>
+      <c r="K868" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="868" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B868" t="s">
-        <v>37</v>
-      </c>
-      <c r="C868">
+    <row r="869" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B869" t="s">
+        <v>37</v>
+      </c>
+      <c r="C869">
         <v>3854</v>
       </c>
-      <c r="D868" t="s">
+      <c r="D869" t="s">
         <v>88</v>
       </c>
-      <c r="F868" t="s">
+      <c r="F869" t="s">
         <v>100</v>
       </c>
-      <c r="G868" t="s">
+      <c r="G869" t="s">
         <v>14</v>
       </c>
-      <c r="H868" s="2">
-        <v>0</v>
-      </c>
-      <c r="I868" s="1">
+      <c r="H869" s="2">
+        <v>0</v>
+      </c>
+      <c r="I869" s="1">
         <v>46118.800694444442</v>
       </c>
-      <c r="J868">
+      <c r="J869">
         <v>1</v>
       </c>
-      <c r="K868" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="869" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H869" s="2"/>
-      <c r="I869" s="1"/>
       <c r="K869" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="870" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H870" s="2"/>
+      <c r="I870" s="1"/>
+      <c r="K870" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="870" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B870" t="s">
-        <v>37</v>
-      </c>
-      <c r="C870">
+    <row r="871" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B871" t="s">
+        <v>37</v>
+      </c>
+      <c r="C871">
         <v>4885</v>
       </c>
-      <c r="D870" t="s">
+      <c r="D871" t="s">
         <v>90</v>
       </c>
-      <c r="F870" t="s">
+      <c r="F871" t="s">
         <v>100</v>
       </c>
-      <c r="G870" t="s">
+      <c r="G871" t="s">
         <v>12</v>
       </c>
-      <c r="H870" s="2">
+      <c r="H871" s="2">
         <v>9.2592592592592588E-5</v>
       </c>
-      <c r="I870" s="1">
+      <c r="I871" s="1">
         <v>46118.801388888889</v>
       </c>
-      <c r="J870">
+      <c r="J871">
         <v>2</v>
       </c>
-      <c r="K870" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="871" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H871" s="2"/>
-      <c r="I871" s="1"/>
       <c r="K871" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="872" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H872" s="2"/>
+      <c r="I872" s="1"/>
+      <c r="K872" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="872" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B872" t="s">
-        <v>37</v>
-      </c>
-      <c r="C872">
-        <v>2423</v>
-      </c>
-      <c r="D872" t="s">
-        <v>72</v>
-      </c>
-      <c r="F872" t="s">
-        <v>100</v>
-      </c>
-      <c r="G872" t="s">
-        <v>10</v>
-      </c>
-      <c r="H872" s="2">
-        <v>6.7013888888888887E-3</v>
-      </c>
-      <c r="I872" s="1">
-        <v>46118.801388888889</v>
-      </c>
-      <c r="J872">
-        <v>0</v>
-      </c>
-      <c r="K872" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="873" spans="2:11" x14ac:dyDescent="0.25">
@@ -24963,10 +24944,10 @@
         <v>37</v>
       </c>
       <c r="C873">
-        <v>2441</v>
+        <v>2423</v>
       </c>
       <c r="D873" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F873" t="s">
         <v>100</v>
@@ -24975,13 +24956,13 @@
         <v>10</v>
       </c>
       <c r="H873" s="2">
-        <v>6.7476851851851856E-3</v>
+        <v>6.7013888888888887E-3</v>
       </c>
       <c r="I873" s="1">
-        <v>46118.802083333336</v>
+        <v>46118.801388888889</v>
       </c>
       <c r="J873">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K873" t="s">
         <v>11</v>
@@ -24992,25 +24973,25 @@
         <v>37</v>
       </c>
       <c r="C874">
-        <v>2437</v>
+        <v>2441</v>
       </c>
       <c r="D874" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F874" t="s">
         <v>100</v>
       </c>
       <c r="G874" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H874" s="2">
-        <v>0</v>
+        <v>6.7476851851851856E-3</v>
       </c>
       <c r="I874" s="1">
-        <v>46118.802777777775</v>
+        <v>46118.802083333336</v>
       </c>
       <c r="J874">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K874" t="s">
         <v>11</v>
@@ -25021,10 +25002,10 @@
         <v>37</v>
       </c>
       <c r="C875">
-        <v>4886</v>
+        <v>2437</v>
       </c>
       <c r="D875" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="F875" t="s">
         <v>100</v>
@@ -25039,7 +25020,7 @@
         <v>46118.802777777775</v>
       </c>
       <c r="J875">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K875" t="s">
         <v>11</v>
@@ -25050,25 +25031,25 @@
         <v>37</v>
       </c>
       <c r="C876">
-        <v>5188</v>
+        <v>4886</v>
       </c>
       <c r="D876" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F876" t="s">
         <v>100</v>
       </c>
       <c r="G876" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H876" s="2">
-        <v>8.1944444444444452E-3</v>
+        <v>0</v>
       </c>
       <c r="I876" s="1">
-        <v>46118.803472222222</v>
+        <v>46118.802777777775</v>
       </c>
       <c r="J876">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K876" t="s">
         <v>11</v>
@@ -25079,22 +25060,22 @@
         <v>37</v>
       </c>
       <c r="C877">
-        <v>5523</v>
+        <v>5188</v>
       </c>
       <c r="D877" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F877" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G877" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H877" s="2">
-        <v>0</v>
+        <v>8.1944444444444452E-3</v>
       </c>
       <c r="I877" s="1">
-        <v>46136.710763888892</v>
+        <v>46118.803472222222</v>
       </c>
       <c r="J877">
         <v>0</v>
@@ -25108,25 +25089,25 @@
         <v>37</v>
       </c>
       <c r="C878">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D878" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F878" t="s">
         <v>102</v>
       </c>
       <c r="G878" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H878" s="2">
-        <v>0</v>
+        <v>4.5717592592592589E-3</v>
       </c>
       <c r="I878" s="1">
-        <v>46136.711458333331</v>
+        <v>46136.710763888892</v>
       </c>
       <c r="J878">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K878" t="s">
         <v>11</v>
@@ -25137,10 +25118,10 @@
         <v>37</v>
       </c>
       <c r="C879">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D879" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F879" t="s">
         <v>102</v>
@@ -25152,10 +25133,10 @@
         <v>0</v>
       </c>
       <c r="I879" s="1">
-        <v>46136.712152777778</v>
+        <v>46136.711458333331</v>
       </c>
       <c r="J879">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K879" t="s">
         <v>11</v>
@@ -25166,25 +25147,25 @@
         <v>37</v>
       </c>
       <c r="C880">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D880" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F880" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G880" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H880" s="2">
-        <v>0</v>
+        <v>5.4976851851851853E-3</v>
       </c>
       <c r="I880" s="1">
         <v>46136.712152777778</v>
       </c>
       <c r="J880">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K880" t="s">
         <v>11</v>
@@ -25195,25 +25176,25 @@
         <v>37</v>
       </c>
       <c r="C881">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D881" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F881" t="s">
         <v>99</v>
       </c>
       <c r="G881" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H881" s="2">
-        <v>0</v>
+        <v>5.7291666666666663E-3</v>
       </c>
       <c r="I881" s="1">
-        <v>46136.712847222225</v>
+        <v>46136.712152777778</v>
       </c>
       <c r="J881">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K881" t="s">
         <v>11</v>
@@ -25224,25 +25205,25 @@
         <v>37</v>
       </c>
       <c r="C882">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D882" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F882" t="s">
         <v>99</v>
       </c>
       <c r="G882" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H882" s="2">
-        <v>8.2175925925925923E-3</v>
+        <v>0</v>
       </c>
       <c r="I882" s="1">
-        <v>46136.713541666664</v>
+        <v>46136.712847222225</v>
       </c>
       <c r="J882">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K882" t="s">
         <v>11</v>
@@ -25253,19 +25234,19 @@
         <v>37</v>
       </c>
       <c r="C883">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D883" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F883" t="s">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="G883" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H883" s="2">
-        <v>0</v>
+        <v>8.2175925925925923E-3</v>
       </c>
       <c r="I883" s="1">
         <v>46136.713541666664</v>
@@ -25282,25 +25263,25 @@
         <v>37</v>
       </c>
       <c r="C884">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D884" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F884" t="s">
         <v>36</v>
       </c>
       <c r="G884" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H884" s="2">
-        <v>0</v>
+        <v>6.9560185185185185E-3</v>
       </c>
       <c r="I884" s="1">
-        <v>46136.714236111111</v>
+        <v>46136.713541666664</v>
       </c>
       <c r="J884">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K884" t="s">
         <v>11</v>
@@ -25311,10 +25292,10 @@
         <v>37</v>
       </c>
       <c r="C885">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D885" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F885" t="s">
         <v>36</v>
@@ -25326,10 +25307,10 @@
         <v>0</v>
       </c>
       <c r="I885" s="1">
-        <v>46136.714930555558</v>
+        <v>46136.714236111111</v>
       </c>
       <c r="J885">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K885" t="s">
         <v>11</v>
@@ -25340,25 +25321,25 @@
         <v>37</v>
       </c>
       <c r="C886">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D886" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F886" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G886" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H886" s="2">
-        <v>0</v>
+        <v>7.2106481481481483E-3</v>
       </c>
       <c r="I886" s="1">
-        <v>46136.715624999997</v>
+        <v>46136.714930555558</v>
       </c>
       <c r="J886">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K886" t="s">
         <v>11</v>
@@ -25369,25 +25350,25 @@
         <v>37</v>
       </c>
       <c r="C887">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D887" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F887" t="s">
         <v>35</v>
       </c>
       <c r="G887" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H887" s="2">
-        <v>0</v>
+        <v>5.6597222222222222E-3</v>
       </c>
       <c r="I887" s="1">
         <v>46136.715624999997</v>
       </c>
       <c r="J887">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K887" t="s">
         <v>11</v>
@@ -25398,10 +25379,10 @@
         <v>37</v>
       </c>
       <c r="C888">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D888" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F888" t="s">
         <v>35</v>
@@ -25413,10 +25394,10 @@
         <v>0</v>
       </c>
       <c r="I888" s="1">
-        <v>46136.716319444444</v>
+        <v>46136.715624999997</v>
       </c>
       <c r="J888">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K888" t="s">
         <v>11</v>
@@ -25427,25 +25408,25 @@
         <v>37</v>
       </c>
       <c r="C889">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D889" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F889" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G889" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H889" s="2">
-        <v>0</v>
+        <v>7.9398148148148145E-3</v>
       </c>
       <c r="I889" s="1">
-        <v>46136.717013888891</v>
+        <v>46136.716319444444</v>
       </c>
       <c r="J889">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K889" t="s">
         <v>11</v>
@@ -25456,25 +25437,25 @@
         <v>37</v>
       </c>
       <c r="C890">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D890" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F890" t="s">
         <v>20</v>
       </c>
       <c r="G890" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H890" s="2">
-        <v>0</v>
+        <v>4.5254629629629629E-3</v>
       </c>
       <c r="I890" s="1">
         <v>46136.717013888891</v>
       </c>
       <c r="J890">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K890" t="s">
         <v>11</v>
@@ -25485,10 +25466,10 @@
         <v>37</v>
       </c>
       <c r="C891">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D891" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F891" t="s">
         <v>20</v>
@@ -25500,10 +25481,10 @@
         <v>0</v>
       </c>
       <c r="I891" s="1">
-        <v>46136.71770833333</v>
+        <v>46136.717013888891</v>
       </c>
       <c r="J891">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K891" t="s">
         <v>11</v>
@@ -25514,25 +25495,25 @@
         <v>37</v>
       </c>
       <c r="C892">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D892" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F892" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G892" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H892" s="2">
-        <v>0</v>
+        <v>5.2430555555555555E-3</v>
       </c>
       <c r="I892" s="1">
-        <v>46136.718402777777</v>
+        <v>46136.71770833333</v>
       </c>
       <c r="J892">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K892" t="s">
         <v>11</v>
@@ -25543,25 +25524,25 @@
         <v>37</v>
       </c>
       <c r="C893">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D893" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F893" t="s">
         <v>100</v>
       </c>
       <c r="G893" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H893" s="2">
-        <v>0</v>
+        <v>6.7013888888888887E-3</v>
       </c>
       <c r="I893" s="1">
         <v>46136.718402777777</v>
       </c>
       <c r="J893">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K893" t="s">
         <v>11</v>
@@ -25572,10 +25553,10 @@
         <v>37</v>
       </c>
       <c r="C894">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D894" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F894" t="s">
         <v>100</v>
@@ -25587,10 +25568,10 @@
         <v>0</v>
       </c>
       <c r="I894" s="1">
-        <v>46136.719097222223</v>
+        <v>46136.718402777777</v>
       </c>
       <c r="J894">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K894" t="s">
         <v>11</v>
@@ -25601,25 +25582,25 @@
         <v>37</v>
       </c>
       <c r="C895">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D895" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F895" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="G895" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H895" s="2">
-        <v>0</v>
+        <v>5.4976851851851853E-3</v>
       </c>
       <c r="I895" s="1">
-        <v>46136.71979166667</v>
+        <v>46136.719097222223</v>
       </c>
       <c r="J895">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K895" t="s">
         <v>11</v>
@@ -25630,25 +25611,25 @@
         <v>37</v>
       </c>
       <c r="C896">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D896" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F896" t="s">
         <v>16</v>
       </c>
       <c r="G896" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H896" s="2">
-        <v>0</v>
+        <v>6.2037037037037035E-3</v>
       </c>
       <c r="I896" s="1">
         <v>46136.71979166667</v>
       </c>
       <c r="J896">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K896" t="s">
         <v>11</v>
@@ -25659,10 +25640,10 @@
         <v>37</v>
       </c>
       <c r="C897">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D897" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F897" t="s">
         <v>16</v>
@@ -25674,10 +25655,10 @@
         <v>0</v>
       </c>
       <c r="I897" s="1">
-        <v>46136.720486111109</v>
+        <v>46136.71979166667</v>
       </c>
       <c r="J897">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K897" t="s">
         <v>11</v>
@@ -25688,25 +25669,25 @@
         <v>37</v>
       </c>
       <c r="C898">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D898" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F898" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G898" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H898" s="2">
-        <v>0</v>
+        <v>9.0972222222222218E-3</v>
       </c>
       <c r="I898" s="1">
-        <v>46136.721180555556</v>
+        <v>46136.720486111109</v>
       </c>
       <c r="J898">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K898" t="s">
         <v>11</v>
@@ -25717,25 +25698,25 @@
         <v>37</v>
       </c>
       <c r="C899">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D899" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F899" t="s">
         <v>29</v>
       </c>
       <c r="G899" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H899" s="2">
-        <v>0</v>
+        <v>4.1898148148148146E-3</v>
       </c>
       <c r="I899" s="1">
-        <v>46136.721875000003</v>
+        <v>46136.721180555556</v>
       </c>
       <c r="J899">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K899" t="s">
         <v>11</v>
@@ -25746,10 +25727,10 @@
         <v>37</v>
       </c>
       <c r="C900">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D900" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F900" t="s">
         <v>29</v>
@@ -25764,7 +25745,7 @@
         <v>46136.721875000003</v>
       </c>
       <c r="J900">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K900" t="s">
         <v>11</v>
@@ -25775,25 +25756,25 @@
         <v>37</v>
       </c>
       <c r="C901">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D901" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F901" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="G901" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H901" s="2">
-        <v>0</v>
+        <v>1.5416666666666667E-2</v>
       </c>
       <c r="I901" s="1">
-        <v>46136.722569444442</v>
+        <v>46136.721875000003</v>
       </c>
       <c r="J901">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K901" t="s">
         <v>11</v>
@@ -25804,25 +25785,25 @@
         <v>37</v>
       </c>
       <c r="C902">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D902" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F902" t="s">
         <v>105</v>
       </c>
       <c r="G902" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H902" s="2">
-        <v>0</v>
+        <v>4.5138888888888885E-3</v>
       </c>
       <c r="I902" s="1">
-        <v>46136.723263888889</v>
+        <v>46136.722569444442</v>
       </c>
       <c r="J902">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K902" t="s">
         <v>11</v>
@@ -25833,10 +25814,10 @@
         <v>37</v>
       </c>
       <c r="C903">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D903" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F903" t="s">
         <v>105</v>
@@ -25848,175 +25829,1158 @@
         <v>0</v>
       </c>
       <c r="I903" s="1">
+        <v>46136.723263888889</v>
+      </c>
+      <c r="J903">
+        <v>1</v>
+      </c>
+      <c r="K903" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="904" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B904" t="s">
+        <v>37</v>
+      </c>
+      <c r="C904">
+        <v>5447</v>
+      </c>
+      <c r="D904" t="s">
+        <v>104</v>
+      </c>
+      <c r="F904" t="s">
+        <v>105</v>
+      </c>
+      <c r="G904" t="s">
+        <v>10</v>
+      </c>
+      <c r="H904" s="2">
+        <v>7.7777777777777776E-3</v>
+      </c>
+      <c r="I904" s="1">
         <v>46136.723958333336</v>
       </c>
-      <c r="J903">
-        <v>0</v>
-      </c>
-      <c r="K903" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="904" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H904" s="2"/>
-      <c r="I904" s="1"/>
+      <c r="J904">
+        <v>1</v>
+      </c>
+      <c r="K904" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="905" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H905" s="2"/>
-      <c r="I905" s="1"/>
+      <c r="B905" t="s">
+        <v>37</v>
+      </c>
+      <c r="C905">
+        <v>2434</v>
+      </c>
+      <c r="D905" t="s">
+        <v>39</v>
+      </c>
+      <c r="F905" t="s">
+        <v>20</v>
+      </c>
+      <c r="G905" t="s">
+        <v>13</v>
+      </c>
+      <c r="H905" s="2">
+        <v>0</v>
+      </c>
+      <c r="I905" s="1">
+        <v>46146.677314814813</v>
+      </c>
+      <c r="J905">
+        <v>0</v>
+      </c>
+      <c r="K905" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="906" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H906" s="2"/>
-      <c r="I906" s="1"/>
+      <c r="B906" t="s">
+        <v>37</v>
+      </c>
+      <c r="C906">
+        <v>3855</v>
+      </c>
+      <c r="D906" t="s">
+        <v>86</v>
+      </c>
+      <c r="F906" t="s">
+        <v>20</v>
+      </c>
+      <c r="G906" t="s">
+        <v>13</v>
+      </c>
+      <c r="H906" s="2">
+        <v>0</v>
+      </c>
+      <c r="I906" s="1">
+        <v>46146.67800925926</v>
+      </c>
+      <c r="J906">
+        <v>0</v>
+      </c>
+      <c r="K906" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="907" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="I907" s="1"/>
+      <c r="B907" t="s">
+        <v>37</v>
+      </c>
+      <c r="C907">
+        <v>2424</v>
+      </c>
+      <c r="D907" t="s">
+        <v>41</v>
+      </c>
+      <c r="F907" t="s">
+        <v>20</v>
+      </c>
+      <c r="G907" t="s">
+        <v>13</v>
+      </c>
+      <c r="H907">
+        <v>0</v>
+      </c>
+      <c r="I907" s="1">
+        <v>46146.67800925926</v>
+      </c>
+      <c r="J907">
+        <v>0</v>
+      </c>
+      <c r="K907" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="908" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H908" s="2"/>
-      <c r="I908" s="1"/>
+      <c r="B908" t="s">
+        <v>37</v>
+      </c>
+      <c r="C908">
+        <v>2433</v>
+      </c>
+      <c r="D908" t="s">
+        <v>42</v>
+      </c>
+      <c r="F908" t="s">
+        <v>20</v>
+      </c>
+      <c r="G908" t="s">
+        <v>13</v>
+      </c>
+      <c r="H908" s="2">
+        <v>0</v>
+      </c>
+      <c r="I908" s="1">
+        <v>46146.678703703707</v>
+      </c>
+      <c r="J908">
+        <v>0</v>
+      </c>
+      <c r="K908" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="909" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H909" s="2"/>
-      <c r="I909" s="1"/>
+      <c r="B909" t="s">
+        <v>37</v>
+      </c>
+      <c r="C909">
+        <v>2454</v>
+      </c>
+      <c r="D909" t="s">
+        <v>38</v>
+      </c>
+      <c r="F909" t="s">
+        <v>20</v>
+      </c>
+      <c r="G909" t="s">
+        <v>13</v>
+      </c>
+      <c r="H909" s="2">
+        <v>0</v>
+      </c>
+      <c r="I909" s="1">
+        <v>46146.679398148146</v>
+      </c>
+      <c r="J909">
+        <v>0</v>
+      </c>
+      <c r="K909" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="910" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H910" s="2"/>
-      <c r="I910" s="1"/>
+      <c r="B910" t="s">
+        <v>37</v>
+      </c>
+      <c r="C910">
+        <v>5522</v>
+      </c>
+      <c r="D910" t="s">
+        <v>106</v>
+      </c>
+      <c r="F910" t="s">
+        <v>20</v>
+      </c>
+      <c r="G910" t="s">
+        <v>13</v>
+      </c>
+      <c r="H910" s="2">
+        <v>0</v>
+      </c>
+      <c r="I910" s="1">
+        <v>46146.680092592593</v>
+      </c>
+      <c r="J910">
+        <v>0</v>
+      </c>
+      <c r="K910" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="911" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H911" s="2"/>
-      <c r="I911" s="1"/>
+      <c r="B911" t="s">
+        <v>37</v>
+      </c>
+      <c r="C911">
+        <v>3792</v>
+      </c>
+      <c r="D911" t="s">
+        <v>82</v>
+      </c>
+      <c r="F911" t="s">
+        <v>20</v>
+      </c>
+      <c r="G911" t="s">
+        <v>13</v>
+      </c>
+      <c r="H911" s="2">
+        <v>0</v>
+      </c>
+      <c r="I911" s="1">
+        <v>46146.680092592593</v>
+      </c>
+      <c r="J911">
+        <v>0</v>
+      </c>
+      <c r="K911" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="912" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H912" s="2"/>
-      <c r="I912" s="1"/>
-    </row>
-    <row r="913" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H913" s="2"/>
-      <c r="I913" s="1"/>
-    </row>
-    <row r="914" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H914" s="2"/>
-      <c r="I914" s="1"/>
-    </row>
-    <row r="915" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H915" s="2"/>
-      <c r="I915" s="1"/>
-    </row>
-    <row r="916" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H916" s="2"/>
-      <c r="I916" s="1"/>
-    </row>
-    <row r="917" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H917" s="2"/>
-      <c r="I917" s="1"/>
-    </row>
-    <row r="918" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H918" s="2"/>
-      <c r="I918" s="1"/>
-    </row>
-    <row r="919" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H919" s="2"/>
-      <c r="I919" s="1"/>
-    </row>
-    <row r="920" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H920" s="2"/>
-      <c r="I920" s="1"/>
-    </row>
-    <row r="921" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H921" s="2"/>
-      <c r="I921" s="1"/>
-    </row>
-    <row r="922" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H922" s="2"/>
-      <c r="I922" s="1"/>
-    </row>
-    <row r="923" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H923" s="2"/>
-      <c r="I923" s="1"/>
-    </row>
-    <row r="924" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H924" s="2"/>
-      <c r="I924" s="1"/>
-    </row>
-    <row r="925" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H925" s="2"/>
-      <c r="I925" s="1"/>
-    </row>
-    <row r="926" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H926" s="2"/>
-      <c r="I926" s="1"/>
-    </row>
-    <row r="927" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H927" s="2"/>
-      <c r="I927" s="1"/>
-    </row>
-    <row r="928" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H928" s="2"/>
-      <c r="I928" s="1"/>
-    </row>
-    <row r="929" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H929" s="2"/>
-      <c r="I929" s="1"/>
-    </row>
-    <row r="930" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B912" t="s">
+        <v>37</v>
+      </c>
+      <c r="C912">
+        <v>2645</v>
+      </c>
+      <c r="D912" t="s">
+        <v>44</v>
+      </c>
+      <c r="F912" t="s">
+        <v>20</v>
+      </c>
+      <c r="G912" t="s">
+        <v>13</v>
+      </c>
+      <c r="H912" s="2">
+        <v>0</v>
+      </c>
+      <c r="I912" s="1">
+        <v>46146.680787037039</v>
+      </c>
+      <c r="J912">
+        <v>0</v>
+      </c>
+      <c r="K912" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="913" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B913" t="s">
+        <v>37</v>
+      </c>
+      <c r="C913">
+        <v>2428</v>
+      </c>
+      <c r="D913" t="s">
+        <v>45</v>
+      </c>
+      <c r="F913" t="s">
+        <v>20</v>
+      </c>
+      <c r="G913" t="s">
+        <v>10</v>
+      </c>
+      <c r="H913" s="2">
+        <v>2.9513888888888888E-3</v>
+      </c>
+      <c r="I913" s="1">
+        <v>46146.681481481479</v>
+      </c>
+      <c r="J913">
+        <v>0</v>
+      </c>
+      <c r="K913" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="914" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B914" t="s">
+        <v>37</v>
+      </c>
+      <c r="C914">
+        <v>2983</v>
+      </c>
+      <c r="D914" t="s">
+        <v>78</v>
+      </c>
+      <c r="F914" t="s">
+        <v>20</v>
+      </c>
+      <c r="G914" t="s">
+        <v>13</v>
+      </c>
+      <c r="H914" s="2">
+        <v>0</v>
+      </c>
+      <c r="I914" s="1">
+        <v>46146.681481481479</v>
+      </c>
+      <c r="J914">
+        <v>0</v>
+      </c>
+      <c r="K914" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="915" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B915" t="s">
+        <v>37</v>
+      </c>
+      <c r="C915">
+        <v>2425</v>
+      </c>
+      <c r="D915" t="s">
+        <v>49</v>
+      </c>
+      <c r="F915" t="s">
+        <v>20</v>
+      </c>
+      <c r="G915" t="s">
+        <v>10</v>
+      </c>
+      <c r="H915" s="2">
+        <v>4.9189814814814816E-3</v>
+      </c>
+      <c r="I915" s="1">
+        <v>46146.682175925926</v>
+      </c>
+      <c r="J915">
+        <v>0</v>
+      </c>
+      <c r="K915" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="916" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B916" t="s">
+        <v>37</v>
+      </c>
+      <c r="C916">
+        <v>5189</v>
+      </c>
+      <c r="D916" t="s">
+        <v>95</v>
+      </c>
+      <c r="F916" t="s">
+        <v>20</v>
+      </c>
+      <c r="G916" t="s">
+        <v>13</v>
+      </c>
+      <c r="H916" s="2">
+        <v>0</v>
+      </c>
+      <c r="I916" s="1">
+        <v>46146.682870370372</v>
+      </c>
+      <c r="J916">
+        <v>0</v>
+      </c>
+      <c r="K916" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="917" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B917" t="s">
+        <v>37</v>
+      </c>
+      <c r="C917">
+        <v>3791</v>
+      </c>
+      <c r="D917" t="s">
+        <v>83</v>
+      </c>
+      <c r="F917" t="s">
+        <v>20</v>
+      </c>
+      <c r="G917" t="s">
+        <v>10</v>
+      </c>
+      <c r="H917" s="2">
+        <v>5.8217592592592592E-3</v>
+      </c>
+      <c r="I917" s="1">
+        <v>46146.682870370372</v>
+      </c>
+      <c r="J917">
+        <v>0</v>
+      </c>
+      <c r="K917" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="918" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B918" t="s">
+        <v>37</v>
+      </c>
+      <c r="C918">
+        <v>5523</v>
+      </c>
+      <c r="D918" t="s">
+        <v>101</v>
+      </c>
+      <c r="F918" t="s">
+        <v>20</v>
+      </c>
+      <c r="G918" t="s">
+        <v>13</v>
+      </c>
+      <c r="H918" s="2">
+        <v>0</v>
+      </c>
+      <c r="I918" s="1">
+        <v>46146.683564814812</v>
+      </c>
+      <c r="J918">
+        <v>0</v>
+      </c>
+      <c r="K918" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="919" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B919" t="s">
+        <v>37</v>
+      </c>
+      <c r="C919">
+        <v>2435</v>
+      </c>
+      <c r="D919" t="s">
+        <v>53</v>
+      </c>
+      <c r="F919" t="s">
+        <v>20</v>
+      </c>
+      <c r="G919" t="s">
+        <v>13</v>
+      </c>
+      <c r="H919" s="2">
+        <v>0</v>
+      </c>
+      <c r="I919" s="1">
+        <v>46146.684259259258</v>
+      </c>
+      <c r="J919">
+        <v>0</v>
+      </c>
+      <c r="K919" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="920" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B920" t="s">
+        <v>37</v>
+      </c>
+      <c r="C920">
+        <v>5448</v>
+      </c>
+      <c r="D920" t="s">
+        <v>103</v>
+      </c>
+      <c r="F920" t="s">
+        <v>20</v>
+      </c>
+      <c r="G920" t="s">
+        <v>13</v>
+      </c>
+      <c r="H920" s="2">
+        <v>0</v>
+      </c>
+      <c r="I920" s="1">
+        <v>46146.684259259258</v>
+      </c>
+      <c r="J920">
+        <v>0</v>
+      </c>
+      <c r="K920" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="921" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B921" t="s">
+        <v>37</v>
+      </c>
+      <c r="C921">
+        <v>2439</v>
+      </c>
+      <c r="D921" t="s">
+        <v>55</v>
+      </c>
+      <c r="F921" t="s">
+        <v>20</v>
+      </c>
+      <c r="G921" t="s">
+        <v>13</v>
+      </c>
+      <c r="H921" s="2">
+        <v>0</v>
+      </c>
+      <c r="I921" s="1">
+        <v>46146.684953703705</v>
+      </c>
+      <c r="J921">
+        <v>0</v>
+      </c>
+      <c r="K921" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="922" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B922" t="s">
+        <v>37</v>
+      </c>
+      <c r="C922">
+        <v>2432</v>
+      </c>
+      <c r="D922" t="s">
+        <v>56</v>
+      </c>
+      <c r="F922" t="s">
+        <v>20</v>
+      </c>
+      <c r="G922" t="s">
+        <v>13</v>
+      </c>
+      <c r="H922" s="2">
+        <v>0</v>
+      </c>
+      <c r="I922" s="1">
+        <v>46146.685648148145</v>
+      </c>
+      <c r="J922">
+        <v>0</v>
+      </c>
+      <c r="K922" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="923" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B923" t="s">
+        <v>37</v>
+      </c>
+      <c r="C923">
+        <v>5447</v>
+      </c>
+      <c r="D923" t="s">
+        <v>104</v>
+      </c>
+      <c r="F923" t="s">
+        <v>20</v>
+      </c>
+      <c r="G923" t="s">
+        <v>13</v>
+      </c>
+      <c r="H923" s="2">
+        <v>0</v>
+      </c>
+      <c r="I923" s="1">
+        <v>46146.685648148145</v>
+      </c>
+      <c r="J923">
+        <v>0</v>
+      </c>
+      <c r="K923" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="924" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B924" t="s">
+        <v>37</v>
+      </c>
+      <c r="C924">
+        <v>2431</v>
+      </c>
+      <c r="D924" t="s">
+        <v>57</v>
+      </c>
+      <c r="F924" t="s">
+        <v>20</v>
+      </c>
+      <c r="G924" t="s">
+        <v>13</v>
+      </c>
+      <c r="H924" s="2">
+        <v>0</v>
+      </c>
+      <c r="I924" s="1">
+        <v>46146.686342592591</v>
+      </c>
+      <c r="J924">
+        <v>0</v>
+      </c>
+      <c r="K924" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="925" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B925" t="s">
+        <v>37</v>
+      </c>
+      <c r="C925">
+        <v>2772</v>
+      </c>
+      <c r="D925" t="s">
+        <v>77</v>
+      </c>
+      <c r="F925" t="s">
+        <v>20</v>
+      </c>
+      <c r="G925" t="s">
+        <v>13</v>
+      </c>
+      <c r="H925" s="2">
+        <v>0</v>
+      </c>
+      <c r="I925" s="1">
+        <v>46146.687037037038</v>
+      </c>
+      <c r="J925">
+        <v>0</v>
+      </c>
+      <c r="K925" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="926" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B926" t="s">
+        <v>37</v>
+      </c>
+      <c r="C926">
+        <v>3482</v>
+      </c>
+      <c r="D926" t="s">
+        <v>81</v>
+      </c>
+      <c r="F926" t="s">
+        <v>20</v>
+      </c>
+      <c r="G926" t="s">
+        <v>13</v>
+      </c>
+      <c r="H926" s="2">
+        <v>0</v>
+      </c>
+      <c r="I926" s="1">
+        <v>46146.687037037038</v>
+      </c>
+      <c r="J926">
+        <v>0</v>
+      </c>
+      <c r="K926" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="927" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B927" t="s">
+        <v>37</v>
+      </c>
+      <c r="C927">
+        <v>2449</v>
+      </c>
+      <c r="D927" t="s">
+        <v>60</v>
+      </c>
+      <c r="F927" t="s">
+        <v>20</v>
+      </c>
+      <c r="G927" t="s">
+        <v>13</v>
+      </c>
+      <c r="H927" s="2">
+        <v>0</v>
+      </c>
+      <c r="I927" s="1">
+        <v>46146.687731481485</v>
+      </c>
+      <c r="J927">
+        <v>0</v>
+      </c>
+      <c r="K927" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="928" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B928" t="s">
+        <v>37</v>
+      </c>
+      <c r="C928">
+        <v>2418</v>
+      </c>
+      <c r="D928" t="s">
+        <v>63</v>
+      </c>
+      <c r="F928" t="s">
+        <v>20</v>
+      </c>
+      <c r="G928" t="s">
+        <v>13</v>
+      </c>
+      <c r="H928" s="2">
+        <v>0</v>
+      </c>
+      <c r="I928" s="1">
+        <v>46146.688425925924</v>
+      </c>
+      <c r="J928">
+        <v>0</v>
+      </c>
+      <c r="K928" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="929" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B929" t="s">
+        <v>37</v>
+      </c>
+      <c r="C929">
+        <v>2444</v>
+      </c>
+      <c r="D929" t="s">
+        <v>66</v>
+      </c>
+      <c r="F929" t="s">
+        <v>20</v>
+      </c>
+      <c r="G929" t="s">
+        <v>12</v>
+      </c>
+      <c r="H929" s="2">
+        <v>0</v>
+      </c>
+      <c r="I929" s="1">
+        <v>46146.688425925924</v>
+      </c>
+      <c r="J929">
+        <v>0</v>
+      </c>
+      <c r="K929" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="930" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H930" s="2"/>
       <c r="I930" s="1"/>
-    </row>
-    <row r="931" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H931" s="2"/>
-      <c r="I931" s="1"/>
-    </row>
-    <row r="932" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H932" s="2"/>
-      <c r="I932" s="1"/>
-    </row>
-    <row r="933" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K930" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="931" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B931" t="s">
+        <v>37</v>
+      </c>
+      <c r="C931">
+        <v>2426</v>
+      </c>
+      <c r="D931" t="s">
+        <v>67</v>
+      </c>
+      <c r="F931" t="s">
+        <v>20</v>
+      </c>
+      <c r="G931" t="s">
+        <v>13</v>
+      </c>
+      <c r="H931" s="2">
+        <v>0</v>
+      </c>
+      <c r="I931" s="1">
+        <v>46146.689120370371</v>
+      </c>
+      <c r="J931">
+        <v>0</v>
+      </c>
+      <c r="K931" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="932" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B932" t="s">
+        <v>37</v>
+      </c>
+      <c r="C932">
+        <v>4630</v>
+      </c>
+      <c r="D932" t="s">
+        <v>89</v>
+      </c>
+      <c r="F932" t="s">
+        <v>20</v>
+      </c>
+      <c r="G932" t="s">
+        <v>12</v>
+      </c>
+      <c r="H932" s="2">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="I932" s="1">
+        <v>46146.689120370371</v>
+      </c>
+      <c r="J932">
+        <v>0</v>
+      </c>
+      <c r="K932" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="933" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I933" s="1"/>
-    </row>
-    <row r="934" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H934" s="2"/>
-      <c r="I934" s="1"/>
-    </row>
-    <row r="935" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H935" s="2"/>
-      <c r="I935" s="1"/>
-    </row>
-    <row r="936" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H936" s="2"/>
-      <c r="I936" s="1"/>
-    </row>
-    <row r="937" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I937" s="1"/>
-    </row>
-    <row r="938" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H938" s="2"/>
-      <c r="I938" s="1"/>
-    </row>
-    <row r="939" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H939" s="2"/>
-      <c r="I939" s="1"/>
-    </row>
-    <row r="940" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H940" s="2"/>
-      <c r="I940" s="1"/>
-    </row>
-    <row r="941" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H941" s="2"/>
-      <c r="I941" s="1"/>
-    </row>
-    <row r="942" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H942" s="2"/>
-      <c r="I942" s="1"/>
-    </row>
-    <row r="943" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H943" s="2"/>
-      <c r="I943" s="1"/>
-    </row>
-    <row r="944" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H944" s="2"/>
-      <c r="I944" s="1"/>
+      <c r="K933" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="934" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B934" t="s">
+        <v>37</v>
+      </c>
+      <c r="C934">
+        <v>2452</v>
+      </c>
+      <c r="D934" t="s">
+        <v>68</v>
+      </c>
+      <c r="F934" t="s">
+        <v>20</v>
+      </c>
+      <c r="G934" t="s">
+        <v>13</v>
+      </c>
+      <c r="H934" s="2">
+        <v>0</v>
+      </c>
+      <c r="I934" s="1">
+        <v>46146.689814814818</v>
+      </c>
+      <c r="J934">
+        <v>0</v>
+      </c>
+      <c r="K934" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="935" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B935" t="s">
+        <v>37</v>
+      </c>
+      <c r="C935">
+        <v>2447</v>
+      </c>
+      <c r="D935" t="s">
+        <v>69</v>
+      </c>
+      <c r="F935" t="s">
+        <v>20</v>
+      </c>
+      <c r="G935" t="s">
+        <v>10</v>
+      </c>
+      <c r="H935" s="2">
+        <v>5.6597222222222222E-3</v>
+      </c>
+      <c r="I935" s="1">
+        <v>46146.690509259257</v>
+      </c>
+      <c r="J935">
+        <v>0</v>
+      </c>
+      <c r="K935" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="936" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B936" t="s">
+        <v>37</v>
+      </c>
+      <c r="C936">
+        <v>2436</v>
+      </c>
+      <c r="D936" t="s">
+        <v>70</v>
+      </c>
+      <c r="F936" t="s">
+        <v>20</v>
+      </c>
+      <c r="G936" t="s">
+        <v>10</v>
+      </c>
+      <c r="H936" s="2">
+        <v>7.1180555555555554E-3</v>
+      </c>
+      <c r="I936" s="1">
+        <v>46146.690509259257</v>
+      </c>
+      <c r="J936">
+        <v>0</v>
+      </c>
+      <c r="K936" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="937" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B937" t="s">
+        <v>37</v>
+      </c>
+      <c r="C937">
+        <v>2982</v>
+      </c>
+      <c r="D937" t="s">
+        <v>80</v>
+      </c>
+      <c r="F937" t="s">
+        <v>20</v>
+      </c>
+      <c r="G937" t="s">
+        <v>13</v>
+      </c>
+      <c r="H937">
+        <v>0</v>
+      </c>
+      <c r="I937" s="1">
+        <v>46146.691203703704</v>
+      </c>
+      <c r="J937">
+        <v>0</v>
+      </c>
+      <c r="K937" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="938" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B938" t="s">
+        <v>37</v>
+      </c>
+      <c r="C938">
+        <v>3854</v>
+      </c>
+      <c r="D938" t="s">
+        <v>88</v>
+      </c>
+      <c r="F938" t="s">
+        <v>20</v>
+      </c>
+      <c r="G938" t="s">
+        <v>13</v>
+      </c>
+      <c r="H938" s="2">
+        <v>0</v>
+      </c>
+      <c r="I938" s="1">
+        <v>46146.69189814815</v>
+      </c>
+      <c r="J938">
+        <v>0</v>
+      </c>
+      <c r="K938" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="939" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B939" t="s">
+        <v>37</v>
+      </c>
+      <c r="C939">
+        <v>4885</v>
+      </c>
+      <c r="D939" t="s">
+        <v>90</v>
+      </c>
+      <c r="F939" t="s">
+        <v>20</v>
+      </c>
+      <c r="G939" t="s">
+        <v>13</v>
+      </c>
+      <c r="H939" s="2">
+        <v>0</v>
+      </c>
+      <c r="I939" s="1">
+        <v>46146.69189814815</v>
+      </c>
+      <c r="J939">
+        <v>0</v>
+      </c>
+      <c r="K939" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="940" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B940" t="s">
+        <v>37</v>
+      </c>
+      <c r="C940">
+        <v>2423</v>
+      </c>
+      <c r="D940" t="s">
+        <v>72</v>
+      </c>
+      <c r="F940" t="s">
+        <v>20</v>
+      </c>
+      <c r="G940" t="s">
+        <v>10</v>
+      </c>
+      <c r="H940" s="2">
+        <v>4.4444444444444444E-3</v>
+      </c>
+      <c r="I940" s="1">
+        <v>46146.668402777781</v>
+      </c>
+      <c r="J940">
+        <v>0</v>
+      </c>
+      <c r="K940" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="941" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B941" t="s">
+        <v>37</v>
+      </c>
+      <c r="C941">
+        <v>2441</v>
+      </c>
+      <c r="D941" t="s">
+        <v>73</v>
+      </c>
+      <c r="F941" t="s">
+        <v>20</v>
+      </c>
+      <c r="G941" t="s">
+        <v>13</v>
+      </c>
+      <c r="H941" s="2">
+        <v>0</v>
+      </c>
+      <c r="I941" s="1">
+        <v>46146.66909722222</v>
+      </c>
+      <c r="J941">
+        <v>0</v>
+      </c>
+      <c r="K941" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="942" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B942" t="s">
+        <v>37</v>
+      </c>
+      <c r="C942">
+        <v>2437</v>
+      </c>
+      <c r="D942" t="s">
+        <v>75</v>
+      </c>
+      <c r="F942" t="s">
+        <v>20</v>
+      </c>
+      <c r="G942" t="s">
+        <v>13</v>
+      </c>
+      <c r="H942" s="2">
+        <v>0</v>
+      </c>
+      <c r="I942" s="1">
+        <v>46146.66909722222</v>
+      </c>
+      <c r="J942">
+        <v>0</v>
+      </c>
+      <c r="K942" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="943" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B943" t="s">
+        <v>37</v>
+      </c>
+      <c r="C943">
+        <v>4886</v>
+      </c>
+      <c r="D943" t="s">
+        <v>91</v>
+      </c>
+      <c r="F943" t="s">
+        <v>20</v>
+      </c>
+      <c r="G943" t="s">
+        <v>13</v>
+      </c>
+      <c r="H943" s="2">
+        <v>0</v>
+      </c>
+      <c r="I943" s="1">
+        <v>46146.669791666667</v>
+      </c>
+      <c r="J943">
+        <v>0</v>
+      </c>
+      <c r="K943" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="944" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B944" t="s">
+        <v>37</v>
+      </c>
+      <c r="C944">
+        <v>5188</v>
+      </c>
+      <c r="D944" t="s">
+        <v>97</v>
+      </c>
+      <c r="F944" t="s">
+        <v>20</v>
+      </c>
+      <c r="G944" t="s">
+        <v>13</v>
+      </c>
+      <c r="H944" s="2">
+        <v>0</v>
+      </c>
+      <c r="I944" s="1">
+        <v>46146.670486111114</v>
+      </c>
+      <c r="J944">
+        <v>0</v>
+      </c>
+      <c r="K944" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="945" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H945" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\All City Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F35AA3D-287E-4518-8024-9FB10B96C78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F54B6DD-03BA-49D9-9894-5B39F1ED1607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -24072,7 +24072,7 @@
         <v>46118.768634259257</v>
       </c>
       <c r="J837">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K837" t="s">
         <v>11</v>
@@ -24101,7 +24101,7 @@
         <v>46118.769328703704</v>
       </c>
       <c r="J838">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K838" t="s">
         <v>11</v>
@@ -24405,7 +24405,7 @@
         <v>46118.793749999997</v>
       </c>
       <c r="J850">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K850" t="s">
         <v>11</v>
@@ -24586,7 +24586,7 @@
         <v>46118.796527777777</v>
       </c>
       <c r="J857">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K857" t="s">
         <v>11</v>
@@ -24635,16 +24635,16 @@
         <v>100</v>
       </c>
       <c r="G859" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H859" s="2">
-        <v>0</v>
+        <v>1.0613425925925925E-2</v>
       </c>
       <c r="I859" s="1">
         <v>46118.797222222223</v>
       </c>
       <c r="J859">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K859" t="s">
         <v>11</v>
@@ -24673,7 +24673,7 @@
         <v>46118.79791666667</v>
       </c>
       <c r="J860">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K860" t="s">
         <v>11</v>
@@ -24702,7 +24702,7 @@
         <v>46118.798611111109</v>
       </c>
       <c r="J861">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K861" t="s">
         <v>11</v>
@@ -25020,7 +25020,7 @@
         <v>46118.802777777775</v>
       </c>
       <c r="J875">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K875" t="s">
         <v>11</v>
@@ -25049,7 +25049,7 @@
         <v>46118.802777777775</v>
       </c>
       <c r="J876">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K876" t="s">
         <v>11</v>
@@ -25127,48 +25127,26 @@
         <v>102</v>
       </c>
       <c r="G879" t="s">
-        <v>13</v>
-      </c>
-      <c r="H879">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="H879" s="2">
+        <v>3.8194444444444446E-4</v>
       </c>
       <c r="I879" s="1">
         <v>46136.711458333331</v>
       </c>
       <c r="J879">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K879" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="880" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B880" t="s">
-        <v>37</v>
-      </c>
-      <c r="C880">
-        <v>5447</v>
-      </c>
-      <c r="D880" t="s">
-        <v>104</v>
-      </c>
-      <c r="F880" t="s">
-        <v>102</v>
-      </c>
-      <c r="G880" t="s">
-        <v>10</v>
-      </c>
-      <c r="H880" s="2">
-        <v>5.4976851851851853E-3</v>
-      </c>
-      <c r="I880" s="1">
-        <v>46136.712152777778</v>
-      </c>
-      <c r="J880">
-        <v>1</v>
-      </c>
+      <c r="H880" s="2"/>
+      <c r="I880" s="1"/>
       <c r="K880" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="881" spans="2:11" x14ac:dyDescent="0.25">
@@ -25176,19 +25154,19 @@
         <v>37</v>
       </c>
       <c r="C881">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D881" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F881" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G881" t="s">
         <v>10</v>
       </c>
       <c r="H881" s="2">
-        <v>5.7291666666666663E-3</v>
+        <v>5.4976851851851853E-3</v>
       </c>
       <c r="I881" s="1">
         <v>46136.712152777778</v>
@@ -25205,22 +25183,22 @@
         <v>37</v>
       </c>
       <c r="C882">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D882" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F882" t="s">
         <v>99</v>
       </c>
       <c r="G882" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H882" s="2">
-        <v>0</v>
+        <v>5.7291666666666663E-3</v>
       </c>
       <c r="I882" s="1">
-        <v>46136.712847222225</v>
+        <v>46136.712152777778</v>
       </c>
       <c r="J882">
         <v>1</v>
@@ -25234,25 +25212,25 @@
         <v>37</v>
       </c>
       <c r="C883">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D883" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F883" t="s">
         <v>99</v>
       </c>
       <c r="G883" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H883" s="2">
-        <v>8.2175925925925923E-3</v>
+        <v>0</v>
       </c>
       <c r="I883" s="1">
-        <v>46136.713541666664</v>
+        <v>46136.712847222225</v>
       </c>
       <c r="J883">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K883" t="s">
         <v>11</v>
@@ -25263,25 +25241,25 @@
         <v>37</v>
       </c>
       <c r="C884">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D884" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F884" t="s">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="G884" t="s">
         <v>10</v>
       </c>
       <c r="H884" s="2">
-        <v>6.9560185185185185E-3</v>
+        <v>8.2175925925925923E-3</v>
       </c>
       <c r="I884" s="1">
         <v>46136.713541666664</v>
       </c>
       <c r="J884">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K884" t="s">
         <v>11</v>
@@ -25292,22 +25270,22 @@
         <v>37</v>
       </c>
       <c r="C885">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D885" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F885" t="s">
         <v>36</v>
       </c>
       <c r="G885" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H885" s="2">
-        <v>0</v>
+        <v>6.9560185185185185E-3</v>
       </c>
       <c r="I885" s="1">
-        <v>46136.714236111111</v>
+        <v>46136.713541666664</v>
       </c>
       <c r="J885">
         <v>1</v>
@@ -25321,25 +25299,25 @@
         <v>37</v>
       </c>
       <c r="C886">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D886" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F886" t="s">
         <v>36</v>
       </c>
       <c r="G886" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H886" s="2">
-        <v>7.2106481481481483E-3</v>
+        <v>0</v>
       </c>
       <c r="I886" s="1">
-        <v>46136.714930555558</v>
+        <v>46136.714236111111</v>
       </c>
       <c r="J886">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K886" t="s">
         <v>11</v>
@@ -25350,22 +25328,22 @@
         <v>37</v>
       </c>
       <c r="C887">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D887" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F887" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G887" t="s">
         <v>10</v>
       </c>
       <c r="H887" s="2">
-        <v>5.6597222222222222E-3</v>
+        <v>7.2106481481481483E-3</v>
       </c>
       <c r="I887" s="1">
-        <v>46136.715624999997</v>
+        <v>46136.714930555558</v>
       </c>
       <c r="J887">
         <v>1</v>
@@ -25379,19 +25357,19 @@
         <v>37</v>
       </c>
       <c r="C888">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D888" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F888" t="s">
         <v>35</v>
       </c>
       <c r="G888" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H888" s="2">
-        <v>0</v>
+        <v>5.6597222222222222E-3</v>
       </c>
       <c r="I888" s="1">
         <v>46136.715624999997</v>
@@ -25408,25 +25386,25 @@
         <v>37</v>
       </c>
       <c r="C889">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D889" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F889" t="s">
         <v>35</v>
       </c>
       <c r="G889" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H889" s="2">
-        <v>7.9398148148148145E-3</v>
+        <v>0</v>
       </c>
       <c r="I889" s="1">
-        <v>46136.716319444444</v>
+        <v>46136.715624999997</v>
       </c>
       <c r="J889">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K889" t="s">
         <v>11</v>
@@ -25437,22 +25415,22 @@
         <v>37</v>
       </c>
       <c r="C890">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D890" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F890" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G890" t="s">
         <v>10</v>
       </c>
       <c r="H890" s="2">
-        <v>4.5254629629629629E-3</v>
+        <v>7.9398148148148145E-3</v>
       </c>
       <c r="I890" s="1">
-        <v>46136.717013888891</v>
+        <v>46136.716319444444</v>
       </c>
       <c r="J890">
         <v>1</v>
@@ -25466,19 +25444,19 @@
         <v>37</v>
       </c>
       <c r="C891">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D891" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F891" t="s">
         <v>20</v>
       </c>
       <c r="G891" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H891" s="2">
-        <v>0</v>
+        <v>4.5254629629629629E-3</v>
       </c>
       <c r="I891" s="1">
         <v>46136.717013888891</v>
@@ -25495,25 +25473,25 @@
         <v>37</v>
       </c>
       <c r="C892">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D892" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F892" t="s">
         <v>20</v>
       </c>
       <c r="G892" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H892" s="2">
-        <v>5.2430555555555555E-3</v>
+        <v>0</v>
       </c>
       <c r="I892" s="1">
-        <v>46136.71770833333</v>
+        <v>46136.717013888891</v>
       </c>
       <c r="J892">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K892" t="s">
         <v>11</v>
@@ -25524,22 +25502,22 @@
         <v>37</v>
       </c>
       <c r="C893">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D893" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F893" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G893" t="s">
         <v>10</v>
       </c>
       <c r="H893" s="2">
-        <v>6.7013888888888887E-3</v>
+        <v>5.2430555555555555E-3</v>
       </c>
       <c r="I893" s="1">
-        <v>46136.718402777777</v>
+        <v>46136.71770833333</v>
       </c>
       <c r="J893">
         <v>1</v>
@@ -25553,19 +25531,19 @@
         <v>37</v>
       </c>
       <c r="C894">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D894" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F894" t="s">
         <v>100</v>
       </c>
       <c r="G894" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H894" s="2">
-        <v>0</v>
+        <v>6.7013888888888887E-3</v>
       </c>
       <c r="I894" s="1">
         <v>46136.718402777777</v>
@@ -25582,25 +25560,25 @@
         <v>37</v>
       </c>
       <c r="C895">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D895" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F895" t="s">
         <v>100</v>
       </c>
       <c r="G895" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H895" s="2">
-        <v>5.4976851851851853E-3</v>
+        <v>0</v>
       </c>
       <c r="I895" s="1">
-        <v>46136.719097222223</v>
+        <v>46136.718402777777</v>
       </c>
       <c r="J895">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K895" t="s">
         <v>11</v>
@@ -25611,22 +25589,22 @@
         <v>37</v>
       </c>
       <c r="C896">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D896" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F896" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="G896" t="s">
         <v>10</v>
       </c>
       <c r="H896" s="2">
-        <v>6.2037037037037035E-3</v>
+        <v>5.4976851851851853E-3</v>
       </c>
       <c r="I896" s="1">
-        <v>46136.71979166667</v>
+        <v>46136.719097222223</v>
       </c>
       <c r="J896">
         <v>1</v>
@@ -25640,19 +25618,19 @@
         <v>37</v>
       </c>
       <c r="C897">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D897" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F897" t="s">
         <v>16</v>
       </c>
       <c r="G897" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H897" s="2">
-        <v>0</v>
+        <v>6.2037037037037035E-3</v>
       </c>
       <c r="I897" s="1">
         <v>46136.71979166667</v>
@@ -25669,25 +25647,25 @@
         <v>37</v>
       </c>
       <c r="C898">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D898" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F898" t="s">
         <v>16</v>
       </c>
       <c r="G898" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H898" s="2">
-        <v>9.0972222222222218E-3</v>
+        <v>0</v>
       </c>
       <c r="I898" s="1">
-        <v>46136.720486111109</v>
+        <v>46136.71979166667</v>
       </c>
       <c r="J898">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K898" t="s">
         <v>11</v>
@@ -25698,22 +25676,22 @@
         <v>37</v>
       </c>
       <c r="C899">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D899" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F899" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G899" t="s">
         <v>10</v>
       </c>
       <c r="H899" s="2">
-        <v>4.1898148148148146E-3</v>
+        <v>9.0972222222222218E-3</v>
       </c>
       <c r="I899" s="1">
-        <v>46136.721180555556</v>
+        <v>46136.720486111109</v>
       </c>
       <c r="J899">
         <v>1</v>
@@ -25727,22 +25705,22 @@
         <v>37</v>
       </c>
       <c r="C900">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D900" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F900" t="s">
         <v>29</v>
       </c>
       <c r="G900" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H900" s="2">
-        <v>0</v>
+        <v>4.1898148148148146E-3</v>
       </c>
       <c r="I900" s="1">
-        <v>46136.721875000003</v>
+        <v>46136.721180555556</v>
       </c>
       <c r="J900">
         <v>1</v>
@@ -25756,25 +25734,25 @@
         <v>37</v>
       </c>
       <c r="C901">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D901" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F901" t="s">
         <v>29</v>
       </c>
       <c r="G901" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H901" s="2">
-        <v>1.5416666666666667E-2</v>
+        <v>0</v>
       </c>
       <c r="I901" s="1">
         <v>46136.721875000003</v>
       </c>
       <c r="J901">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K901" t="s">
         <v>11</v>
@@ -25785,22 +25763,22 @@
         <v>37</v>
       </c>
       <c r="C902">
-        <v>5523</v>
+        <v>5447</v>
       </c>
       <c r="D902" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F902" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="G902" t="s">
         <v>10</v>
       </c>
       <c r="H902" s="2">
-        <v>4.5138888888888885E-3</v>
+        <v>1.5416666666666667E-2</v>
       </c>
       <c r="I902" s="1">
-        <v>46136.722569444442</v>
+        <v>46136.721875000003</v>
       </c>
       <c r="J902">
         <v>1</v>
@@ -25814,22 +25792,22 @@
         <v>37</v>
       </c>
       <c r="C903">
-        <v>5448</v>
+        <v>5523</v>
       </c>
       <c r="D903" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F903" t="s">
         <v>105</v>
       </c>
       <c r="G903" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H903" s="2">
-        <v>0</v>
+        <v>4.5138888888888885E-3</v>
       </c>
       <c r="I903" s="1">
-        <v>46136.723263888889</v>
+        <v>46136.722569444442</v>
       </c>
       <c r="J903">
         <v>1</v>
@@ -25843,25 +25821,25 @@
         <v>37</v>
       </c>
       <c r="C904">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="D904" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F904" t="s">
         <v>105</v>
       </c>
       <c r="G904" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H904" s="2">
-        <v>7.7777777777777776E-3</v>
+        <v>0</v>
       </c>
       <c r="I904" s="1">
-        <v>46136.723958333336</v>
+        <v>46136.723263888889</v>
       </c>
       <c r="J904">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K904" t="s">
         <v>11</v>
@@ -25872,25 +25850,25 @@
         <v>37</v>
       </c>
       <c r="C905">
-        <v>2434</v>
+        <v>5447</v>
       </c>
       <c r="D905" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="F905" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="G905" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H905" s="2">
-        <v>0</v>
+        <v>7.7777777777777776E-3</v>
       </c>
       <c r="I905" s="1">
-        <v>46146.677314814813</v>
+        <v>46136.723958333336</v>
       </c>
       <c r="J905">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K905" t="s">
         <v>11</v>
@@ -25901,10 +25879,10 @@
         <v>37</v>
       </c>
       <c r="C906">
-        <v>3855</v>
+        <v>2434</v>
       </c>
       <c r="D906" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="F906" t="s">
         <v>20</v>
@@ -25916,7 +25894,7 @@
         <v>0</v>
       </c>
       <c r="I906" s="1">
-        <v>46146.67800925926</v>
+        <v>46146.677314814813</v>
       </c>
       <c r="J906">
         <v>0</v>
@@ -25930,10 +25908,10 @@
         <v>37</v>
       </c>
       <c r="C907">
-        <v>2424</v>
+        <v>3855</v>
       </c>
       <c r="D907" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="F907" t="s">
         <v>20</v>
@@ -25959,10 +25937,10 @@
         <v>37</v>
       </c>
       <c r="C908">
-        <v>2433</v>
+        <v>2424</v>
       </c>
       <c r="D908" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F908" t="s">
         <v>20</v>
@@ -25974,7 +25952,7 @@
         <v>0</v>
       </c>
       <c r="I908" s="1">
-        <v>46146.678703703707</v>
+        <v>46146.67800925926</v>
       </c>
       <c r="J908">
         <v>0</v>
@@ -25988,22 +25966,22 @@
         <v>37</v>
       </c>
       <c r="C909">
-        <v>2454</v>
+        <v>2433</v>
       </c>
       <c r="D909" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F909" t="s">
         <v>20</v>
       </c>
       <c r="G909" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H909" s="2">
-        <v>0</v>
+        <v>1.5092592592592593E-2</v>
       </c>
       <c r="I909" s="1">
-        <v>46146.679398148146</v>
+        <v>46146.678703703707</v>
       </c>
       <c r="J909">
         <v>0</v>
@@ -26017,10 +25995,10 @@
         <v>37</v>
       </c>
       <c r="C910">
-        <v>5522</v>
+        <v>2454</v>
       </c>
       <c r="D910" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="F910" t="s">
         <v>20</v>
@@ -26032,7 +26010,7 @@
         <v>0</v>
       </c>
       <c r="I910" s="1">
-        <v>46146.680092592593</v>
+        <v>46146.679398148146</v>
       </c>
       <c r="J910">
         <v>0</v>
@@ -26046,10 +26024,10 @@
         <v>37</v>
       </c>
       <c r="C911">
-        <v>3792</v>
+        <v>5522</v>
       </c>
       <c r="D911" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="F911" t="s">
         <v>20</v>
@@ -26075,10 +26053,10 @@
         <v>37</v>
       </c>
       <c r="C912">
-        <v>2645</v>
+        <v>3792</v>
       </c>
       <c r="D912" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="F912" t="s">
         <v>20</v>
@@ -26090,7 +26068,7 @@
         <v>0</v>
       </c>
       <c r="I912" s="1">
-        <v>46146.680787037039</v>
+        <v>46146.680092592593</v>
       </c>
       <c r="J912">
         <v>0</v>
@@ -26104,22 +26082,22 @@
         <v>37</v>
       </c>
       <c r="C913">
-        <v>2428</v>
+        <v>2645</v>
       </c>
       <c r="D913" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F913" t="s">
         <v>20</v>
       </c>
       <c r="G913" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H913" s="2">
-        <v>2.9513888888888888E-3</v>
+        <v>0</v>
       </c>
       <c r="I913" s="1">
-        <v>46146.681481481479</v>
+        <v>46146.680787037039</v>
       </c>
       <c r="J913">
         <v>0</v>
@@ -26133,19 +26111,19 @@
         <v>37</v>
       </c>
       <c r="C914">
-        <v>2983</v>
+        <v>2428</v>
       </c>
       <c r="D914" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="F914" t="s">
         <v>20</v>
       </c>
       <c r="G914" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H914" s="2">
-        <v>0</v>
+        <v>2.9513888888888888E-3</v>
       </c>
       <c r="I914" s="1">
         <v>46146.681481481479</v>
@@ -26162,22 +26140,22 @@
         <v>37</v>
       </c>
       <c r="C915">
-        <v>2425</v>
+        <v>2983</v>
       </c>
       <c r="D915" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="F915" t="s">
         <v>20</v>
       </c>
       <c r="G915" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H915" s="2">
-        <v>4.9189814814814816E-3</v>
+        <v>0</v>
       </c>
       <c r="I915" s="1">
-        <v>46146.682175925926</v>
+        <v>46146.681481481479</v>
       </c>
       <c r="J915">
         <v>0</v>
@@ -26191,22 +26169,22 @@
         <v>37</v>
       </c>
       <c r="C916">
-        <v>5189</v>
+        <v>2425</v>
       </c>
       <c r="D916" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="F916" t="s">
         <v>20</v>
       </c>
       <c r="G916" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H916" s="2">
-        <v>0</v>
+        <v>4.9189814814814816E-3</v>
       </c>
       <c r="I916" s="1">
-        <v>46146.682870370372</v>
+        <v>46146.682175925926</v>
       </c>
       <c r="J916">
         <v>0</v>
@@ -26220,19 +26198,19 @@
         <v>37</v>
       </c>
       <c r="C917">
-        <v>3791</v>
+        <v>5189</v>
       </c>
       <c r="D917" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F917" t="s">
         <v>20</v>
       </c>
       <c r="G917" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H917" s="2">
-        <v>5.8217592592592592E-3</v>
+        <v>0</v>
       </c>
       <c r="I917" s="1">
         <v>46146.682870370372</v>
@@ -26249,22 +26227,22 @@
         <v>37</v>
       </c>
       <c r="C918">
-        <v>5523</v>
+        <v>3791</v>
       </c>
       <c r="D918" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F918" t="s">
         <v>20</v>
       </c>
       <c r="G918" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H918" s="2">
-        <v>0</v>
+        <v>5.8217592592592592E-3</v>
       </c>
       <c r="I918" s="1">
-        <v>46146.683564814812</v>
+        <v>46146.682870370372</v>
       </c>
       <c r="J918">
         <v>0</v>
@@ -26278,10 +26256,10 @@
         <v>37</v>
       </c>
       <c r="C919">
-        <v>2435</v>
+        <v>5523</v>
       </c>
       <c r="D919" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="F919" t="s">
         <v>20</v>
@@ -26293,7 +26271,7 @@
         <v>0</v>
       </c>
       <c r="I919" s="1">
-        <v>46146.684259259258</v>
+        <v>46146.683564814812</v>
       </c>
       <c r="J919">
         <v>0</v>
@@ -26307,10 +26285,10 @@
         <v>37</v>
       </c>
       <c r="C920">
-        <v>5448</v>
+        <v>2435</v>
       </c>
       <c r="D920" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="F920" t="s">
         <v>20</v>
@@ -26336,10 +26314,10 @@
         <v>37</v>
       </c>
       <c r="C921">
-        <v>2439</v>
+        <v>5448</v>
       </c>
       <c r="D921" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="F921" t="s">
         <v>20</v>
@@ -26351,7 +26329,7 @@
         <v>0</v>
       </c>
       <c r="I921" s="1">
-        <v>46146.684953703705</v>
+        <v>46146.684259259258</v>
       </c>
       <c r="J921">
         <v>0</v>
@@ -26365,22 +26343,22 @@
         <v>37</v>
       </c>
       <c r="C922">
-        <v>2432</v>
+        <v>2439</v>
       </c>
       <c r="D922" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F922" t="s">
         <v>20</v>
       </c>
       <c r="G922" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H922" s="2">
-        <v>0</v>
+        <v>4.3981481481481484E-3</v>
       </c>
       <c r="I922" s="1">
-        <v>46146.685648148145</v>
+        <v>46146.684953703705</v>
       </c>
       <c r="J922">
         <v>0</v>
@@ -26394,19 +26372,19 @@
         <v>37</v>
       </c>
       <c r="C923">
-        <v>5447</v>
+        <v>2432</v>
       </c>
       <c r="D923" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="F923" t="s">
         <v>20</v>
       </c>
       <c r="G923" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H923" s="2">
-        <v>0</v>
+        <v>4.8495370370370368E-3</v>
       </c>
       <c r="I923" s="1">
         <v>46146.685648148145</v>
@@ -26423,22 +26401,22 @@
         <v>37</v>
       </c>
       <c r="C924">
-        <v>2431</v>
+        <v>5447</v>
       </c>
       <c r="D924" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="F924" t="s">
         <v>20</v>
       </c>
       <c r="G924" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H924" s="2">
-        <v>0</v>
+        <v>7.858796296296296E-3</v>
       </c>
       <c r="I924" s="1">
-        <v>46146.686342592591</v>
+        <v>46146.685648148145</v>
       </c>
       <c r="J924">
         <v>0</v>
@@ -26452,22 +26430,22 @@
         <v>37</v>
       </c>
       <c r="C925">
-        <v>2772</v>
+        <v>2431</v>
       </c>
       <c r="D925" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F925" t="s">
         <v>20</v>
       </c>
       <c r="G925" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H925" s="2">
-        <v>0</v>
+        <v>7.1527777777777779E-3</v>
       </c>
       <c r="I925" s="1">
-        <v>46146.687037037038</v>
+        <v>46146.686342592591</v>
       </c>
       <c r="J925">
         <v>0</v>
@@ -26481,10 +26459,10 @@
         <v>37</v>
       </c>
       <c r="C926">
-        <v>3482</v>
+        <v>2772</v>
       </c>
       <c r="D926" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F926" t="s">
         <v>20</v>
@@ -26510,22 +26488,22 @@
         <v>37</v>
       </c>
       <c r="C927">
-        <v>2449</v>
+        <v>3482</v>
       </c>
       <c r="D927" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="F927" t="s">
         <v>20</v>
       </c>
       <c r="G927" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H927" s="2">
-        <v>0</v>
+        <v>5.0462962962962961E-3</v>
       </c>
       <c r="I927" s="1">
-        <v>46146.687731481485</v>
+        <v>46146.687037037038</v>
       </c>
       <c r="J927">
         <v>0</v>
@@ -26539,22 +26517,22 @@
         <v>37</v>
       </c>
       <c r="C928">
-        <v>2418</v>
+        <v>2449</v>
       </c>
       <c r="D928" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F928" t="s">
         <v>20</v>
       </c>
       <c r="G928" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H928" s="2">
-        <v>0</v>
+        <v>4.8263888888888887E-3</v>
       </c>
       <c r="I928" s="1">
-        <v>46146.688425925924</v>
+        <v>46146.687731481485</v>
       </c>
       <c r="J928">
         <v>0</v>
@@ -26568,16 +26546,16 @@
         <v>37</v>
       </c>
       <c r="C929">
-        <v>2444</v>
+        <v>2418</v>
       </c>
       <c r="D929" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F929" t="s">
         <v>20</v>
       </c>
       <c r="G929" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H929" s="2">
         <v>0</v>
@@ -26593,39 +26571,39 @@
       </c>
     </row>
     <row r="930" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H930" s="2"/>
-      <c r="I930" s="1"/>
+      <c r="B930" t="s">
+        <v>37</v>
+      </c>
+      <c r="C930">
+        <v>2444</v>
+      </c>
+      <c r="D930" t="s">
+        <v>66</v>
+      </c>
+      <c r="F930" t="s">
+        <v>20</v>
+      </c>
+      <c r="G930" t="s">
+        <v>12</v>
+      </c>
+      <c r="H930" s="2">
+        <v>0</v>
+      </c>
+      <c r="I930" s="1">
+        <v>46146.688425925924</v>
+      </c>
+      <c r="J930">
+        <v>0</v>
+      </c>
       <c r="K930" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="931" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H931" s="2"/>
+      <c r="I931" s="1"/>
+      <c r="K931" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="931" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B931" t="s">
-        <v>37</v>
-      </c>
-      <c r="C931">
-        <v>2426</v>
-      </c>
-      <c r="D931" t="s">
-        <v>67</v>
-      </c>
-      <c r="F931" t="s">
-        <v>20</v>
-      </c>
-      <c r="G931" t="s">
-        <v>13</v>
-      </c>
-      <c r="H931" s="2">
-        <v>0</v>
-      </c>
-      <c r="I931" s="1">
-        <v>46146.689120370371</v>
-      </c>
-      <c r="J931">
-        <v>0</v>
-      </c>
-      <c r="K931" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="932" spans="2:11" x14ac:dyDescent="0.25">
@@ -26633,19 +26611,19 @@
         <v>37</v>
       </c>
       <c r="C932">
-        <v>4630</v>
+        <v>2426</v>
       </c>
       <c r="D932" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="F932" t="s">
         <v>20</v>
       </c>
       <c r="G932" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H932" s="2">
-        <v>2.0833333333333335E-4</v>
+        <v>0</v>
       </c>
       <c r="I932" s="1">
         <v>46146.689120370371</v>
@@ -26658,9 +26636,32 @@
       </c>
     </row>
     <row r="933" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="I933" s="1"/>
+      <c r="B933" t="s">
+        <v>37</v>
+      </c>
+      <c r="C933">
+        <v>4630</v>
+      </c>
+      <c r="D933" t="s">
+        <v>89</v>
+      </c>
+      <c r="F933" t="s">
+        <v>20</v>
+      </c>
+      <c r="G933" t="s">
+        <v>10</v>
+      </c>
+      <c r="H933" s="2">
+        <v>5.185185185185185E-3</v>
+      </c>
+      <c r="I933" s="1">
+        <v>46146.689120370371</v>
+      </c>
+      <c r="J933">
+        <v>0</v>
+      </c>
       <c r="K933" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="934" spans="2:11" x14ac:dyDescent="0.25">
@@ -26880,10 +26881,10 @@
         <v>20</v>
       </c>
       <c r="G941" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H941" s="2">
-        <v>0</v>
+        <v>3.9814814814814817E-3</v>
       </c>
       <c r="I941" s="1">
         <v>46146.66909722222</v>
@@ -26967,10 +26968,10 @@
         <v>20</v>
       </c>
       <c r="G944" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H944" s="2">
-        <v>0</v>
+        <v>8.7847222222222215E-3</v>
       </c>
       <c r="I944" s="1">
         <v>46146.670486111114</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\All City Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2C1EED-9A5D-4CAF-9532-42FF1CBCF6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14280D4E-838C-4704-969C-9C2F924BDD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4519" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4518" uniqueCount="107">
   <si>
     <t>Company Name</t>
   </si>
@@ -24244,10 +24244,10 @@
         <v>100</v>
       </c>
       <c r="G844" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H844" s="2">
-        <v>5.5092592592592589E-3</v>
+        <v>8.2754629629629636E-3</v>
       </c>
       <c r="I844" s="1">
         <v>46118.771412037036</v>
@@ -24260,46 +24260,68 @@
       </c>
     </row>
     <row r="845" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H845" s="2"/>
-      <c r="I845" s="1"/>
+      <c r="B845" t="s">
+        <v>37</v>
+      </c>
+      <c r="C845">
+        <v>2983</v>
+      </c>
+      <c r="D845" t="s">
+        <v>78</v>
+      </c>
+      <c r="F845" t="s">
+        <v>100</v>
+      </c>
+      <c r="G845" t="s">
+        <v>14</v>
+      </c>
+      <c r="H845" s="2">
+        <v>0</v>
+      </c>
+      <c r="I845" s="1">
+        <v>46118.771412037036</v>
+      </c>
+      <c r="J845">
+        <v>2</v>
+      </c>
       <c r="K845" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="846" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H846" s="2"/>
+      <c r="I846" s="1"/>
+      <c r="K846" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="846" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B846" t="s">
-        <v>37</v>
-      </c>
-      <c r="C846">
-        <v>2983</v>
-      </c>
-      <c r="D846" t="s">
-        <v>78</v>
-      </c>
-      <c r="F846" t="s">
+    <row r="847" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B847" t="s">
+        <v>37</v>
+      </c>
+      <c r="C847">
+        <v>2425</v>
+      </c>
+      <c r="D847" t="s">
+        <v>49</v>
+      </c>
+      <c r="F847" t="s">
         <v>100</v>
       </c>
-      <c r="G846" t="s">
-        <v>14</v>
-      </c>
-      <c r="H846" s="2">
-        <v>0</v>
-      </c>
-      <c r="I846" s="1">
-        <v>46118.771412037036</v>
-      </c>
-      <c r="J846">
-        <v>2</v>
-      </c>
-      <c r="K846" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="847" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H847" s="2"/>
-      <c r="I847" s="1"/>
+      <c r="G847" t="s">
+        <v>10</v>
+      </c>
+      <c r="H847" s="2">
+        <v>9.3761574074074081E-2</v>
+      </c>
+      <c r="I847" s="1">
+        <v>46118.772106481483</v>
+      </c>
+      <c r="J847">
+        <v>1</v>
+      </c>
       <c r="K847" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="848" spans="2:11" x14ac:dyDescent="0.3">
@@ -24307,10 +24329,10 @@
         <v>37</v>
       </c>
       <c r="C848">
-        <v>2425</v>
+        <v>5189</v>
       </c>
       <c r="D848" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="F848" t="s">
         <v>100</v>
@@ -24319,13 +24341,13 @@
         <v>10</v>
       </c>
       <c r="H848" s="2">
-        <v>9.3761574074074081E-2</v>
+        <v>9.2476851851851852E-3</v>
       </c>
       <c r="I848" s="1">
-        <v>46118.772106481483</v>
+        <v>46118.772800925923</v>
       </c>
       <c r="J848">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K848" t="s">
         <v>11</v>
@@ -24336,10 +24358,10 @@
         <v>37</v>
       </c>
       <c r="C849">
-        <v>5189</v>
+        <v>3791</v>
       </c>
       <c r="D849" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F849" t="s">
         <v>100</v>
@@ -24348,13 +24370,13 @@
         <v>10</v>
       </c>
       <c r="H849" s="2">
-        <v>9.2476851851851852E-3</v>
+        <v>7.8472222222222224E-3</v>
       </c>
       <c r="I849" s="1">
-        <v>46118.772800925923</v>
+        <v>46118.793055555558</v>
       </c>
       <c r="J849">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K849" t="s">
         <v>11</v>
@@ -24365,64 +24387,64 @@
         <v>37</v>
       </c>
       <c r="C850">
-        <v>3791</v>
+        <v>2435</v>
       </c>
       <c r="D850" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="F850" t="s">
         <v>100</v>
       </c>
       <c r="G850" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H850" s="2">
-        <v>7.8472222222222224E-3</v>
+        <v>0</v>
       </c>
       <c r="I850" s="1">
-        <v>46118.793055555558</v>
+        <v>46118.793749999997</v>
       </c>
       <c r="J850">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K850" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="851" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B851" t="s">
-        <v>37</v>
-      </c>
-      <c r="C851">
-        <v>2435</v>
-      </c>
-      <c r="D851" t="s">
-        <v>53</v>
-      </c>
-      <c r="F851" t="s">
+      <c r="H851" s="2"/>
+      <c r="I851" s="1"/>
+      <c r="K851" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="852" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B852" t="s">
+        <v>37</v>
+      </c>
+      <c r="C852">
+        <v>2439</v>
+      </c>
+      <c r="D852" t="s">
+        <v>55</v>
+      </c>
+      <c r="F852" t="s">
         <v>100</v>
       </c>
-      <c r="G851" t="s">
-        <v>14</v>
-      </c>
-      <c r="H851" s="2">
-        <v>0</v>
-      </c>
-      <c r="I851" s="1">
-        <v>46118.793749999997</v>
-      </c>
-      <c r="J851">
-        <v>5</v>
-      </c>
-      <c r="K851" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="852" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H852" s="2"/>
-      <c r="I852" s="1"/>
+      <c r="G852" t="s">
+        <v>10</v>
+      </c>
+      <c r="H852" s="2">
+        <v>7.0254629629629634E-3</v>
+      </c>
+      <c r="I852" s="1">
+        <v>46118.794444444444</v>
+      </c>
+      <c r="J852">
+        <v>1</v>
+      </c>
       <c r="K852" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="853" spans="2:11" x14ac:dyDescent="0.3">
@@ -24430,10 +24452,10 @@
         <v>37</v>
       </c>
       <c r="C853">
-        <v>2439</v>
+        <v>2432</v>
       </c>
       <c r="D853" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F853" t="s">
         <v>100</v>
@@ -24442,13 +24464,13 @@
         <v>10</v>
       </c>
       <c r="H853" s="2">
-        <v>7.0254629629629634E-3</v>
+        <v>1.3101851851851852E-2</v>
       </c>
       <c r="I853" s="1">
         <v>46118.794444444444</v>
       </c>
       <c r="J853">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K853" t="s">
         <v>11</v>
@@ -24459,64 +24481,64 @@
         <v>37</v>
       </c>
       <c r="C854">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="D854" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F854" t="s">
         <v>100</v>
       </c>
       <c r="G854" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H854" s="2">
-        <v>1.3101851851851852E-2</v>
+        <v>0</v>
       </c>
       <c r="I854" s="1">
-        <v>46118.794444444444</v>
+        <v>46118.795138888891</v>
       </c>
       <c r="J854">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K854" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="855" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B855" t="s">
-        <v>37</v>
-      </c>
-      <c r="C855">
-        <v>2431</v>
-      </c>
-      <c r="D855" t="s">
-        <v>57</v>
-      </c>
-      <c r="F855" t="s">
+      <c r="H855" s="2"/>
+      <c r="I855" s="1"/>
+      <c r="K855" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="856" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B856" t="s">
+        <v>37</v>
+      </c>
+      <c r="C856">
+        <v>2772</v>
+      </c>
+      <c r="D856" t="s">
+        <v>77</v>
+      </c>
+      <c r="F856" t="s">
         <v>100</v>
       </c>
-      <c r="G855" t="s">
-        <v>12</v>
-      </c>
-      <c r="H855" s="2">
-        <v>0</v>
-      </c>
-      <c r="I855" s="1">
-        <v>46118.795138888891</v>
-      </c>
-      <c r="J855">
-        <v>1</v>
-      </c>
-      <c r="K855" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="856" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H856" s="2"/>
-      <c r="I856" s="1"/>
+      <c r="G856" t="s">
+        <v>10</v>
+      </c>
+      <c r="H856" s="2">
+        <v>7.2106481481481483E-3</v>
+      </c>
+      <c r="I856" s="1">
+        <v>46118.79583333333</v>
+      </c>
+      <c r="J856">
+        <v>0</v>
+      </c>
       <c r="K856" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="857" spans="2:11" x14ac:dyDescent="0.3">
@@ -24524,10 +24546,10 @@
         <v>37</v>
       </c>
       <c r="C857">
-        <v>2772</v>
+        <v>3482</v>
       </c>
       <c r="D857" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F857" t="s">
         <v>100</v>
@@ -24536,13 +24558,13 @@
         <v>10</v>
       </c>
       <c r="H857" s="2">
-        <v>7.2106481481481483E-3</v>
+        <v>7.0254629629629634E-3</v>
       </c>
       <c r="I857" s="1">
         <v>46118.79583333333</v>
       </c>
       <c r="J857">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K857" t="s">
         <v>11</v>
@@ -24553,25 +24575,25 @@
         <v>37</v>
       </c>
       <c r="C858">
-        <v>3482</v>
+        <v>5204</v>
       </c>
       <c r="D858" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="F858" t="s">
         <v>100</v>
       </c>
       <c r="G858" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H858" s="2">
-        <v>7.0254629629629634E-3</v>
+        <v>0</v>
       </c>
       <c r="I858" s="1">
-        <v>46118.79583333333</v>
+        <v>46118.796527777777</v>
       </c>
       <c r="J858">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K858" t="s">
         <v>11</v>
@@ -24582,25 +24604,25 @@
         <v>37</v>
       </c>
       <c r="C859">
-        <v>5204</v>
+        <v>2449</v>
       </c>
       <c r="D859" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="F859" t="s">
         <v>100</v>
       </c>
       <c r="G859" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H859" s="2">
-        <v>0</v>
+        <v>7.8009259259259256E-3</v>
       </c>
       <c r="I859" s="1">
-        <v>46118.796527777777</v>
+        <v>46118.797222222223</v>
       </c>
       <c r="J859">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K859" t="s">
         <v>11</v>
@@ -24611,10 +24633,10 @@
         <v>37</v>
       </c>
       <c r="C860">
-        <v>2449</v>
+        <v>2418</v>
       </c>
       <c r="D860" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F860" t="s">
         <v>100</v>
@@ -24623,13 +24645,13 @@
         <v>10</v>
       </c>
       <c r="H860" s="2">
-        <v>7.8009259259259256E-3</v>
+        <v>1.0613425925925925E-2</v>
       </c>
       <c r="I860" s="1">
         <v>46118.797222222223</v>
       </c>
       <c r="J860">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K860" t="s">
         <v>11</v>
@@ -24640,22 +24662,22 @@
         <v>37</v>
       </c>
       <c r="C861">
-        <v>2418</v>
+        <v>2444</v>
       </c>
       <c r="D861" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F861" t="s">
         <v>100</v>
       </c>
       <c r="G861" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H861" s="2">
-        <v>1.0613425925925925E-2</v>
+        <v>0</v>
       </c>
       <c r="I861" s="1">
-        <v>46118.797222222223</v>
+        <v>46118.79791666667</v>
       </c>
       <c r="J861">
         <v>5</v>
@@ -24669,10 +24691,10 @@
         <v>37</v>
       </c>
       <c r="C862">
-        <v>2444</v>
+        <v>2426</v>
       </c>
       <c r="D862" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F862" t="s">
         <v>100</v>
@@ -24684,7 +24706,7 @@
         <v>0</v>
       </c>
       <c r="I862" s="1">
-        <v>46118.79791666667</v>
+        <v>46118.798611111109</v>
       </c>
       <c r="J862">
         <v>5</v>
@@ -24698,25 +24720,25 @@
         <v>37</v>
       </c>
       <c r="C863">
-        <v>2426</v>
+        <v>4630</v>
       </c>
       <c r="D863" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="F863" t="s">
         <v>100</v>
       </c>
       <c r="G863" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H863" s="2">
-        <v>0</v>
+        <v>8.5069444444444437E-3</v>
       </c>
       <c r="I863" s="1">
         <v>46118.798611111109</v>
       </c>
       <c r="J863">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K863" t="s">
         <v>11</v>
@@ -24727,22 +24749,22 @@
         <v>37</v>
       </c>
       <c r="C864">
-        <v>4630</v>
+        <v>2452</v>
       </c>
       <c r="D864" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="F864" t="s">
         <v>100</v>
       </c>
       <c r="G864" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H864" s="2">
-        <v>8.5069444444444437E-3</v>
+        <v>0</v>
       </c>
       <c r="I864" s="1">
-        <v>46118.798611111109</v>
+        <v>46118.799305555556</v>
       </c>
       <c r="J864">
         <v>0</v>
@@ -24752,39 +24774,39 @@
       </c>
     </row>
     <row r="865" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B865" t="s">
-        <v>37</v>
-      </c>
-      <c r="C865">
-        <v>2452</v>
-      </c>
-      <c r="D865" t="s">
-        <v>68</v>
-      </c>
-      <c r="F865" t="s">
+      <c r="H865" s="2"/>
+      <c r="I865" s="1"/>
+      <c r="K865" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="866" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B866" t="s">
+        <v>37</v>
+      </c>
+      <c r="C866">
+        <v>2447</v>
+      </c>
+      <c r="D866" t="s">
+        <v>69</v>
+      </c>
+      <c r="F866" t="s">
         <v>100</v>
       </c>
-      <c r="G865" t="s">
-        <v>12</v>
-      </c>
-      <c r="H865" s="2">
-        <v>0</v>
-      </c>
-      <c r="I865" s="1">
+      <c r="G866" t="s">
+        <v>10</v>
+      </c>
+      <c r="H866" s="2">
+        <v>8.0787037037037043E-3</v>
+      </c>
+      <c r="I866" s="1">
         <v>46118.799305555556</v>
       </c>
-      <c r="J865">
-        <v>0</v>
-      </c>
-      <c r="K865" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="866" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H866" s="2"/>
-      <c r="I866" s="1"/>
+      <c r="J866">
+        <v>0</v>
+      </c>
       <c r="K866" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="867" spans="2:11" x14ac:dyDescent="0.3">
@@ -24792,10 +24814,10 @@
         <v>37</v>
       </c>
       <c r="C867">
-        <v>2447</v>
+        <v>2436</v>
       </c>
       <c r="D867" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F867" t="s">
         <v>100</v>
@@ -24804,10 +24826,10 @@
         <v>10</v>
       </c>
       <c r="H867" s="2">
-        <v>8.0787037037037043E-3</v>
+        <v>9.0162037037037034E-3</v>
       </c>
       <c r="I867" s="1">
-        <v>46118.799305555556</v>
+        <v>46118.8</v>
       </c>
       <c r="J867">
         <v>0</v>
@@ -24821,136 +24843,136 @@
         <v>37</v>
       </c>
       <c r="C868">
-        <v>2436</v>
+        <v>2982</v>
       </c>
       <c r="D868" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F868" t="s">
         <v>100</v>
       </c>
       <c r="G868" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H868" s="2">
-        <v>9.0162037037037034E-3</v>
+        <v>5.3240740740740744E-4</v>
       </c>
       <c r="I868" s="1">
-        <v>46118.8</v>
+        <v>46118.800694444442</v>
       </c>
       <c r="J868">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K868" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="869" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B869" t="s">
-        <v>37</v>
-      </c>
-      <c r="C869">
-        <v>2982</v>
-      </c>
-      <c r="D869" t="s">
-        <v>80</v>
-      </c>
-      <c r="F869" t="s">
+      <c r="H869" s="2"/>
+      <c r="I869" s="1"/>
+      <c r="K869" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="870" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B870" t="s">
+        <v>37</v>
+      </c>
+      <c r="C870">
+        <v>3854</v>
+      </c>
+      <c r="D870" t="s">
+        <v>88</v>
+      </c>
+      <c r="F870" t="s">
         <v>100</v>
       </c>
-      <c r="G869" t="s">
+      <c r="G870" t="s">
+        <v>14</v>
+      </c>
+      <c r="H870" s="2">
+        <v>0</v>
+      </c>
+      <c r="I870" s="1">
+        <v>46118.800694444442</v>
+      </c>
+      <c r="J870">
+        <v>1</v>
+      </c>
+      <c r="K870" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="871" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H871" s="2"/>
+      <c r="I871" s="1"/>
+      <c r="K871" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="872" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B872" t="s">
+        <v>37</v>
+      </c>
+      <c r="C872">
+        <v>4885</v>
+      </c>
+      <c r="D872" t="s">
+        <v>90</v>
+      </c>
+      <c r="F872" t="s">
+        <v>100</v>
+      </c>
+      <c r="G872" t="s">
         <v>12</v>
       </c>
-      <c r="H869" s="2">
-        <v>5.3240740740740744E-4</v>
-      </c>
-      <c r="I869" s="1">
-        <v>46118.800694444442</v>
-      </c>
-      <c r="J869">
+      <c r="H872" s="2">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="I872" s="1">
+        <v>46118.801388888889</v>
+      </c>
+      <c r="J872">
         <v>2</v>
       </c>
-      <c r="K869" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="870" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H870" s="2"/>
-      <c r="I870" s="1"/>
-      <c r="K870" t="s">
+      <c r="K872" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="873" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H873" s="2"/>
+      <c r="I873" s="1"/>
+      <c r="K873" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="871" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B871" t="s">
-        <v>37</v>
-      </c>
-      <c r="C871">
-        <v>3854</v>
-      </c>
-      <c r="D871" t="s">
-        <v>88</v>
-      </c>
-      <c r="F871" t="s">
+    <row r="874" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B874" t="s">
+        <v>37</v>
+      </c>
+      <c r="C874">
+        <v>2423</v>
+      </c>
+      <c r="D874" t="s">
+        <v>72</v>
+      </c>
+      <c r="F874" t="s">
         <v>100</v>
       </c>
-      <c r="G871" t="s">
-        <v>14</v>
-      </c>
-      <c r="H871" s="2">
-        <v>0</v>
-      </c>
-      <c r="I871" s="1">
-        <v>46118.800694444442</v>
-      </c>
-      <c r="J871">
-        <v>1</v>
-      </c>
-      <c r="K871" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="872" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H872" s="2"/>
-      <c r="I872" s="1"/>
-      <c r="K872" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="873" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B873" t="s">
-        <v>37</v>
-      </c>
-      <c r="C873">
-        <v>4885</v>
-      </c>
-      <c r="D873" t="s">
-        <v>90</v>
-      </c>
-      <c r="F873" t="s">
-        <v>100</v>
-      </c>
-      <c r="G873" t="s">
-        <v>12</v>
-      </c>
-      <c r="H873" s="2">
-        <v>9.2592592592592588E-5</v>
-      </c>
-      <c r="I873" s="1">
+      <c r="G874" t="s">
+        <v>10</v>
+      </c>
+      <c r="H874" s="2">
+        <v>6.7013888888888887E-3</v>
+      </c>
+      <c r="I874" s="1">
         <v>46118.801388888889</v>
       </c>
-      <c r="J873">
-        <v>2</v>
-      </c>
-      <c r="K873" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="874" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H874" s="2"/>
-      <c r="I874" s="1"/>
+      <c r="J874">
+        <v>0</v>
+      </c>
       <c r="K874" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="875" spans="2:11" x14ac:dyDescent="0.3">
@@ -24958,10 +24980,10 @@
         <v>37</v>
       </c>
       <c r="C875">
-        <v>2423</v>
+        <v>2441</v>
       </c>
       <c r="D875" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F875" t="s">
         <v>100</v>
@@ -24970,13 +24992,13 @@
         <v>10</v>
       </c>
       <c r="H875" s="2">
-        <v>6.7013888888888887E-3</v>
+        <v>6.7476851851851856E-3</v>
       </c>
       <c r="I875" s="1">
-        <v>46118.801388888889</v>
+        <v>46118.802083333336</v>
       </c>
       <c r="J875">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K875" t="s">
         <v>11</v>
@@ -24987,25 +25009,25 @@
         <v>37</v>
       </c>
       <c r="C876">
-        <v>2441</v>
+        <v>2437</v>
       </c>
       <c r="D876" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F876" t="s">
         <v>100</v>
       </c>
       <c r="G876" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H876" s="2">
-        <v>6.7476851851851856E-3</v>
+        <v>0</v>
       </c>
       <c r="I876" s="1">
-        <v>46118.802083333336</v>
+        <v>46118.802777777775</v>
       </c>
       <c r="J876">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K876" t="s">
         <v>11</v>
@@ -25016,19 +25038,19 @@
         <v>37</v>
       </c>
       <c r="C877">
-        <v>2437</v>
+        <v>4886</v>
       </c>
       <c r="D877" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="F877" t="s">
         <v>100</v>
       </c>
       <c r="G877" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H877" s="2">
-        <v>0</v>
+        <v>1.6238425925925927E-2</v>
       </c>
       <c r="I877" s="1">
         <v>46118.802777777775</v>
@@ -25045,10 +25067,10 @@
         <v>37</v>
       </c>
       <c r="C878">
-        <v>4886</v>
+        <v>5188</v>
       </c>
       <c r="D878" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F878" t="s">
         <v>100</v>
@@ -25057,13 +25079,13 @@
         <v>10</v>
       </c>
       <c r="H878" s="2">
-        <v>1.6238425925925927E-2</v>
+        <v>8.1944444444444452E-3</v>
       </c>
       <c r="I878" s="1">
-        <v>46118.802777777775</v>
+        <v>46118.803472222222</v>
       </c>
       <c r="J878">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K878" t="s">
         <v>11</v>
@@ -25074,25 +25096,25 @@
         <v>37</v>
       </c>
       <c r="C879">
-        <v>5188</v>
+        <v>5523</v>
       </c>
       <c r="D879" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F879" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G879" t="s">
         <v>10</v>
       </c>
       <c r="H879" s="2">
-        <v>8.1944444444444452E-3</v>
+        <v>4.5717592592592589E-3</v>
       </c>
       <c r="I879" s="1">
-        <v>46118.803472222222</v>
+        <v>46136.710763888892</v>
       </c>
       <c r="J879">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K879" t="s">
         <v>11</v>
@@ -25103,64 +25125,64 @@
         <v>37</v>
       </c>
       <c r="C880">
-        <v>5523</v>
+        <v>5448</v>
       </c>
       <c r="D880" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F880" t="s">
         <v>102</v>
       </c>
       <c r="G880" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H880" s="2">
-        <v>4.5717592592592589E-3</v>
+        <v>3.8194444444444446E-4</v>
       </c>
       <c r="I880" s="1">
-        <v>46136.710763888892</v>
+        <v>46136.711458333331</v>
       </c>
       <c r="J880">
+        <v>2</v>
+      </c>
+      <c r="K880" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="881" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H881" s="2"/>
+      <c r="I881" s="1"/>
+      <c r="K881" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="882" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B882" t="s">
+        <v>37</v>
+      </c>
+      <c r="C882">
+        <v>5447</v>
+      </c>
+      <c r="D882" t="s">
+        <v>104</v>
+      </c>
+      <c r="F882" t="s">
+        <v>102</v>
+      </c>
+      <c r="G882" t="s">
+        <v>10</v>
+      </c>
+      <c r="H882" s="2">
+        <v>5.4976851851851853E-3</v>
+      </c>
+      <c r="I882" s="1">
+        <v>46136.712152777778</v>
+      </c>
+      <c r="J882">
         <v>1</v>
       </c>
-      <c r="K880" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="881" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B881" t="s">
-        <v>37</v>
-      </c>
-      <c r="C881">
-        <v>5448</v>
-      </c>
-      <c r="D881" t="s">
-        <v>103</v>
-      </c>
-      <c r="F881" t="s">
-        <v>102</v>
-      </c>
-      <c r="G881" t="s">
-        <v>12</v>
-      </c>
-      <c r="H881" s="2">
-        <v>3.8194444444444446E-4</v>
-      </c>
-      <c r="I881" s="1">
-        <v>46136.711458333331</v>
-      </c>
-      <c r="J881">
-        <v>2</v>
-      </c>
-      <c r="K881" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="882" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H882" s="2"/>
-      <c r="I882" s="1"/>
       <c r="K882" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="883" spans="2:11" x14ac:dyDescent="0.3">
@@ -25168,19 +25190,19 @@
         <v>37</v>
       </c>
       <c r="C883">
-        <v>5447</v>
+        <v>5523</v>
       </c>
       <c r="D883" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F883" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G883" t="s">
         <v>10</v>
       </c>
       <c r="H883" s="2">
-        <v>5.4976851851851853E-3</v>
+        <v>5.7291666666666663E-3</v>
       </c>
       <c r="I883" s="1">
         <v>46136.712152777778</v>
@@ -25197,25 +25219,25 @@
         <v>37</v>
       </c>
       <c r="C884">
-        <v>5523</v>
+        <v>5448</v>
       </c>
       <c r="D884" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F884" t="s">
         <v>99</v>
       </c>
       <c r="G884" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H884" s="2">
-        <v>5.7291666666666663E-3</v>
+        <v>0</v>
       </c>
       <c r="I884" s="1">
-        <v>46136.712152777778</v>
+        <v>46136.712847222225</v>
       </c>
       <c r="J884">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K884" t="s">
         <v>11</v>
@@ -25226,25 +25248,25 @@
         <v>37</v>
       </c>
       <c r="C885">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="D885" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F885" t="s">
         <v>99</v>
       </c>
       <c r="G885" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H885" s="2">
-        <v>0</v>
+        <v>8.2175925925925923E-3</v>
       </c>
       <c r="I885" s="1">
-        <v>46136.712847222225</v>
+        <v>46136.713541666664</v>
       </c>
       <c r="J885">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K885" t="s">
         <v>11</v>
@@ -25255,25 +25277,25 @@
         <v>37</v>
       </c>
       <c r="C886">
-        <v>5447</v>
+        <v>5523</v>
       </c>
       <c r="D886" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F886" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="G886" t="s">
         <v>10</v>
       </c>
       <c r="H886" s="2">
-        <v>8.2175925925925923E-3</v>
+        <v>6.9560185185185185E-3</v>
       </c>
       <c r="I886" s="1">
         <v>46136.713541666664</v>
       </c>
       <c r="J886">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K886" t="s">
         <v>11</v>
@@ -25284,25 +25306,25 @@
         <v>37</v>
       </c>
       <c r="C887">
-        <v>5523</v>
+        <v>5448</v>
       </c>
       <c r="D887" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F887" t="s">
         <v>36</v>
       </c>
       <c r="G887" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H887" s="2">
-        <v>6.9560185185185185E-3</v>
+        <v>0</v>
       </c>
       <c r="I887" s="1">
-        <v>46136.713541666664</v>
+        <v>46136.714236111111</v>
       </c>
       <c r="J887">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K887" t="s">
         <v>11</v>
@@ -25313,25 +25335,25 @@
         <v>37</v>
       </c>
       <c r="C888">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="D888" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F888" t="s">
         <v>36</v>
       </c>
       <c r="G888" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H888" s="2">
-        <v>0</v>
+        <v>7.2106481481481483E-3</v>
       </c>
       <c r="I888" s="1">
-        <v>46136.714236111111</v>
+        <v>46136.714930555558</v>
       </c>
       <c r="J888">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K888" t="s">
         <v>11</v>
@@ -25342,22 +25364,22 @@
         <v>37</v>
       </c>
       <c r="C889">
-        <v>5447</v>
+        <v>5523</v>
       </c>
       <c r="D889" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F889" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G889" t="s">
         <v>10</v>
       </c>
       <c r="H889" s="2">
-        <v>7.2106481481481483E-3</v>
+        <v>5.6597222222222222E-3</v>
       </c>
       <c r="I889" s="1">
-        <v>46136.714930555558</v>
+        <v>46136.715624999997</v>
       </c>
       <c r="J889">
         <v>1</v>
@@ -25371,25 +25393,25 @@
         <v>37</v>
       </c>
       <c r="C890">
-        <v>5523</v>
+        <v>5448</v>
       </c>
       <c r="D890" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F890" t="s">
         <v>35</v>
       </c>
       <c r="G890" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H890" s="2">
-        <v>5.6597222222222222E-3</v>
+        <v>0</v>
       </c>
       <c r="I890" s="1">
         <v>46136.715624999997</v>
       </c>
       <c r="J890">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K890" t="s">
         <v>11</v>
@@ -25400,25 +25422,25 @@
         <v>37</v>
       </c>
       <c r="C891">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="D891" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F891" t="s">
         <v>35</v>
       </c>
       <c r="G891" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H891" s="2">
-        <v>0</v>
+        <v>7.9398148148148145E-3</v>
       </c>
       <c r="I891" s="1">
-        <v>46136.715624999997</v>
+        <v>46136.716319444444</v>
       </c>
       <c r="J891">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K891" t="s">
         <v>11</v>
@@ -25429,22 +25451,22 @@
         <v>37</v>
       </c>
       <c r="C892">
-        <v>5447</v>
+        <v>5523</v>
       </c>
       <c r="D892" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F892" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G892" t="s">
         <v>10</v>
       </c>
       <c r="H892" s="2">
-        <v>7.9398148148148145E-3</v>
+        <v>4.5254629629629629E-3</v>
       </c>
       <c r="I892" s="1">
-        <v>46136.716319444444</v>
+        <v>46136.717013888891</v>
       </c>
       <c r="J892">
         <v>1</v>
@@ -25458,25 +25480,25 @@
         <v>37</v>
       </c>
       <c r="C893">
-        <v>5523</v>
+        <v>5448</v>
       </c>
       <c r="D893" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F893" t="s">
         <v>20</v>
       </c>
       <c r="G893" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H893" s="2">
-        <v>4.5254629629629629E-3</v>
+        <v>0</v>
       </c>
       <c r="I893" s="1">
         <v>46136.717013888891</v>
       </c>
       <c r="J893">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K893" t="s">
         <v>11</v>
@@ -25487,25 +25509,25 @@
         <v>37</v>
       </c>
       <c r="C894">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="D894" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F894" t="s">
         <v>20</v>
       </c>
       <c r="G894" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H894" s="2">
-        <v>0</v>
+        <v>5.2430555555555555E-3</v>
       </c>
       <c r="I894" s="1">
-        <v>46136.717013888891</v>
+        <v>46136.71770833333</v>
       </c>
       <c r="J894">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K894" t="s">
         <v>11</v>
@@ -25516,22 +25538,22 @@
         <v>37</v>
       </c>
       <c r="C895">
-        <v>5447</v>
+        <v>5523</v>
       </c>
       <c r="D895" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F895" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G895" t="s">
         <v>10</v>
       </c>
       <c r="H895" s="2">
-        <v>5.2430555555555555E-3</v>
+        <v>6.7013888888888887E-3</v>
       </c>
       <c r="I895" s="1">
-        <v>46136.71770833333</v>
+        <v>46136.718402777777</v>
       </c>
       <c r="J895">
         <v>1</v>
@@ -25545,25 +25567,25 @@
         <v>37</v>
       </c>
       <c r="C896">
-        <v>5523</v>
+        <v>5448</v>
       </c>
       <c r="D896" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F896" t="s">
         <v>100</v>
       </c>
       <c r="G896" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H896" s="2">
-        <v>6.7013888888888887E-3</v>
+        <v>0</v>
       </c>
       <c r="I896" s="1">
         <v>46136.718402777777</v>
       </c>
       <c r="J896">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K896" t="s">
         <v>11</v>
@@ -25574,25 +25596,25 @@
         <v>37</v>
       </c>
       <c r="C897">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="D897" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F897" t="s">
         <v>100</v>
       </c>
       <c r="G897" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H897" s="2">
-        <v>0</v>
+        <v>5.4976851851851853E-3</v>
       </c>
       <c r="I897" s="1">
-        <v>46136.718402777777</v>
+        <v>46136.719097222223</v>
       </c>
       <c r="J897">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K897" t="s">
         <v>11</v>
@@ -25603,22 +25625,22 @@
         <v>37</v>
       </c>
       <c r="C898">
-        <v>5447</v>
+        <v>5523</v>
       </c>
       <c r="D898" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F898" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="G898" t="s">
         <v>10</v>
       </c>
       <c r="H898" s="2">
-        <v>5.4976851851851853E-3</v>
+        <v>6.2037037037037035E-3</v>
       </c>
       <c r="I898" s="1">
-        <v>46136.719097222223</v>
+        <v>46136.71979166667</v>
       </c>
       <c r="J898">
         <v>1</v>
@@ -25632,25 +25654,25 @@
         <v>37</v>
       </c>
       <c r="C899">
-        <v>5523</v>
+        <v>5448</v>
       </c>
       <c r="D899" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F899" t="s">
         <v>16</v>
       </c>
       <c r="G899" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H899" s="2">
-        <v>6.2037037037037035E-3</v>
+        <v>0</v>
       </c>
       <c r="I899" s="1">
         <v>46136.71979166667</v>
       </c>
       <c r="J899">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K899" t="s">
         <v>11</v>
@@ -25661,25 +25683,25 @@
         <v>37</v>
       </c>
       <c r="C900">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="D900" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F900" t="s">
         <v>16</v>
       </c>
       <c r="G900" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H900" s="2">
-        <v>0</v>
+        <v>9.0972222222222218E-3</v>
       </c>
       <c r="I900" s="1">
-        <v>46136.71979166667</v>
+        <v>46136.720486111109</v>
       </c>
       <c r="J900">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K900" t="s">
         <v>11</v>
@@ -25690,22 +25712,22 @@
         <v>37</v>
       </c>
       <c r="C901">
-        <v>5447</v>
+        <v>5523</v>
       </c>
       <c r="D901" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F901" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G901" t="s">
         <v>10</v>
       </c>
       <c r="H901" s="2">
-        <v>9.0972222222222218E-3</v>
+        <v>4.1898148148148146E-3</v>
       </c>
       <c r="I901" s="1">
-        <v>46136.720486111109</v>
+        <v>46136.721180555556</v>
       </c>
       <c r="J901">
         <v>1</v>
@@ -25719,25 +25741,25 @@
         <v>37</v>
       </c>
       <c r="C902">
-        <v>5523</v>
+        <v>5448</v>
       </c>
       <c r="D902" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F902" t="s">
         <v>29</v>
       </c>
       <c r="G902" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H902" s="2">
-        <v>4.1898148148148146E-3</v>
+        <v>0</v>
       </c>
       <c r="I902" s="1">
-        <v>46136.721180555556</v>
+        <v>46136.721875000003</v>
       </c>
       <c r="J902">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K902" t="s">
         <v>11</v>
@@ -25748,25 +25770,25 @@
         <v>37</v>
       </c>
       <c r="C903">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="D903" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F903" t="s">
         <v>29</v>
       </c>
       <c r="G903" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H903" s="2">
-        <v>0</v>
+        <v>1.5416666666666667E-2</v>
       </c>
       <c r="I903" s="1">
         <v>46136.721875000003</v>
       </c>
       <c r="J903">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K903" t="s">
         <v>11</v>
@@ -25777,22 +25799,22 @@
         <v>37</v>
       </c>
       <c r="C904">
-        <v>5447</v>
+        <v>5523</v>
       </c>
       <c r="D904" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F904" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="G904" t="s">
         <v>10</v>
       </c>
       <c r="H904" s="2">
-        <v>1.5416666666666667E-2</v>
+        <v>4.5138888888888885E-3</v>
       </c>
       <c r="I904" s="1">
-        <v>46136.721875000003</v>
+        <v>46136.722569444442</v>
       </c>
       <c r="J904">
         <v>1</v>
@@ -25806,25 +25828,25 @@
         <v>37</v>
       </c>
       <c r="C905">
-        <v>5523</v>
+        <v>5448</v>
       </c>
       <c r="D905" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F905" t="s">
         <v>105</v>
       </c>
       <c r="G905" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H905" s="2">
-        <v>4.5138888888888885E-3</v>
+        <v>0</v>
       </c>
       <c r="I905" s="1">
-        <v>46136.722569444442</v>
+        <v>46136.723263888889</v>
       </c>
       <c r="J905">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K905" t="s">
         <v>11</v>
@@ -25835,25 +25857,25 @@
         <v>37</v>
       </c>
       <c r="C906">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="D906" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F906" t="s">
         <v>105</v>
       </c>
       <c r="G906" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H906" s="2">
-        <v>0</v>
+        <v>7.7777777777777776E-3</v>
       </c>
       <c r="I906" s="1">
-        <v>46136.723263888889</v>
+        <v>46136.723958333336</v>
       </c>
       <c r="J906">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K906" t="s">
         <v>11</v>
@@ -25864,25 +25886,25 @@
         <v>37</v>
       </c>
       <c r="C907">
-        <v>5447</v>
+        <v>2434</v>
       </c>
       <c r="D907" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="F907" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="G907" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H907" s="2">
-        <v>7.7777777777777776E-3</v>
+        <v>0</v>
       </c>
       <c r="I907" s="1">
-        <v>46136.723958333336</v>
+        <v>46146.677314814813</v>
       </c>
       <c r="J907">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K907" t="s">
         <v>11</v>
@@ -25893,22 +25915,22 @@
         <v>37</v>
       </c>
       <c r="C908">
-        <v>2434</v>
+        <v>3855</v>
       </c>
       <c r="D908" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="F908" t="s">
         <v>20</v>
       </c>
       <c r="G908" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H908" s="2">
-        <v>0</v>
+        <v>4.1550925925925922E-3</v>
       </c>
       <c r="I908" s="1">
-        <v>46146.677314814813</v>
+        <v>46146.67800925926</v>
       </c>
       <c r="J908">
         <v>1</v>
@@ -25922,10 +25944,10 @@
         <v>37</v>
       </c>
       <c r="C909">
-        <v>3855</v>
+        <v>2424</v>
       </c>
       <c r="D909" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="F909" t="s">
         <v>20</v>
@@ -25934,7 +25956,7 @@
         <v>10</v>
       </c>
       <c r="H909" s="2">
-        <v>4.1550925925925922E-3</v>
+        <v>4.8611111111111112E-3</v>
       </c>
       <c r="I909" s="1">
         <v>46146.67800925926</v>
@@ -25951,10 +25973,10 @@
         <v>37</v>
       </c>
       <c r="C910">
-        <v>2424</v>
+        <v>2433</v>
       </c>
       <c r="D910" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F910" t="s">
         <v>20</v>
@@ -25963,13 +25985,13 @@
         <v>10</v>
       </c>
       <c r="H910" s="2">
-        <v>4.8611111111111112E-3</v>
+        <v>1.5092592592592593E-2</v>
       </c>
       <c r="I910" s="1">
-        <v>46146.67800925926</v>
+        <v>46146.678703703707</v>
       </c>
       <c r="J910">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K910" t="s">
         <v>11</v>
@@ -25980,10 +26002,10 @@
         <v>37</v>
       </c>
       <c r="C911">
-        <v>2433</v>
+        <v>2454</v>
       </c>
       <c r="D911" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F911" t="s">
         <v>20</v>
@@ -25992,13 +26014,13 @@
         <v>10</v>
       </c>
       <c r="H911" s="2">
-        <v>1.5092592592592593E-2</v>
+        <v>5.4745370370370373E-3</v>
       </c>
       <c r="I911" s="1">
-        <v>46146.678703703707</v>
+        <v>46146.679398148146</v>
       </c>
       <c r="J911">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K911" t="s">
         <v>11</v>
@@ -26009,10 +26031,10 @@
         <v>37</v>
       </c>
       <c r="C912">
-        <v>2454</v>
+        <v>5522</v>
       </c>
       <c r="D912" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="F912" t="s">
         <v>20</v>
@@ -26021,13 +26043,13 @@
         <v>10</v>
       </c>
       <c r="H912" s="2">
-        <v>5.4745370370370373E-3</v>
+        <v>1.3391203703703704E-2</v>
       </c>
       <c r="I912" s="1">
-        <v>46146.679398148146</v>
+        <v>46146.680092592593</v>
       </c>
       <c r="J912">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K912" t="s">
         <v>11</v>
@@ -26038,10 +26060,10 @@
         <v>37</v>
       </c>
       <c r="C913">
-        <v>5522</v>
+        <v>3792</v>
       </c>
       <c r="D913" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="F913" t="s">
         <v>20</v>
@@ -26056,7 +26078,7 @@
         <v>46146.680092592593</v>
       </c>
       <c r="J913">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K913" t="s">
         <v>11</v>
@@ -26067,10 +26089,10 @@
         <v>37</v>
       </c>
       <c r="C914">
-        <v>3792</v>
+        <v>2645</v>
       </c>
       <c r="D914" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="F914" t="s">
         <v>20</v>
@@ -26082,10 +26104,10 @@
         <v>0</v>
       </c>
       <c r="I914" s="1">
-        <v>46146.680092592593</v>
+        <v>46146.680787037039</v>
       </c>
       <c r="J914">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K914" t="s">
         <v>11</v>
@@ -26096,25 +26118,25 @@
         <v>37</v>
       </c>
       <c r="C915">
-        <v>2645</v>
+        <v>2428</v>
       </c>
       <c r="D915" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F915" t="s">
         <v>20</v>
       </c>
       <c r="G915" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H915" s="2">
-        <v>0</v>
+        <v>3.0787037037037037E-3</v>
       </c>
       <c r="I915" s="1">
-        <v>46146.680787037039</v>
+        <v>46146.681481481479</v>
       </c>
       <c r="J915">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K915" t="s">
         <v>11</v>
@@ -26125,25 +26147,25 @@
         <v>37</v>
       </c>
       <c r="C916">
-        <v>2428</v>
+        <v>2983</v>
       </c>
       <c r="D916" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="F916" t="s">
         <v>20</v>
       </c>
       <c r="G916" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H916" s="2">
-        <v>2.9513888888888888E-3</v>
+        <v>0</v>
       </c>
       <c r="I916" s="1">
         <v>46146.681481481479</v>
       </c>
       <c r="J916">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K916" t="s">
         <v>11</v>
@@ -26154,25 +26176,25 @@
         <v>37</v>
       </c>
       <c r="C917">
-        <v>2983</v>
+        <v>2425</v>
       </c>
       <c r="D917" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="F917" t="s">
         <v>20</v>
       </c>
       <c r="G917" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H917" s="2">
-        <v>0</v>
+        <v>4.9189814814814816E-3</v>
       </c>
       <c r="I917" s="1">
-        <v>46146.681481481479</v>
+        <v>46146.682175925926</v>
       </c>
       <c r="J917">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K917" t="s">
         <v>11</v>
@@ -26183,25 +26205,25 @@
         <v>37</v>
       </c>
       <c r="C918">
-        <v>2425</v>
+        <v>5189</v>
       </c>
       <c r="D918" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="F918" t="s">
         <v>20</v>
       </c>
       <c r="G918" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H918" s="2">
-        <v>4.9189814814814816E-3</v>
+        <v>0</v>
       </c>
       <c r="I918" s="1">
-        <v>46146.682175925926</v>
+        <v>46146.682870370372</v>
       </c>
       <c r="J918">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K918" t="s">
         <v>11</v>
@@ -26212,25 +26234,25 @@
         <v>37</v>
       </c>
       <c r="C919">
-        <v>5189</v>
+        <v>3791</v>
       </c>
       <c r="D919" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F919" t="s">
         <v>20</v>
       </c>
       <c r="G919" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H919" s="2">
-        <v>0</v>
+        <v>5.8217592592592592E-3</v>
       </c>
       <c r="I919" s="1">
         <v>46146.682870370372</v>
       </c>
       <c r="J919">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K919" t="s">
         <v>11</v>
@@ -26241,25 +26263,25 @@
         <v>37</v>
       </c>
       <c r="C920">
-        <v>3791</v>
+        <v>5523</v>
       </c>
       <c r="D920" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="F920" t="s">
         <v>20</v>
       </c>
       <c r="G920" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H920" s="2">
-        <v>5.8217592592592592E-3</v>
+        <v>0</v>
       </c>
       <c r="I920" s="1">
-        <v>46146.682870370372</v>
+        <v>46146.683564814812</v>
       </c>
       <c r="J920">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K920" t="s">
         <v>11</v>
@@ -26270,25 +26292,25 @@
         <v>37</v>
       </c>
       <c r="C921">
-        <v>5523</v>
+        <v>2435</v>
       </c>
       <c r="D921" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="F921" t="s">
         <v>20</v>
       </c>
       <c r="G921" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H921" s="2">
-        <v>0</v>
+        <v>5.3935185185185188E-3</v>
       </c>
       <c r="I921" s="1">
-        <v>46146.683564814812</v>
+        <v>46146.684259259258</v>
       </c>
       <c r="J921">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K921" t="s">
         <v>11</v>
@@ -26299,10 +26321,10 @@
         <v>37</v>
       </c>
       <c r="C922">
-        <v>2435</v>
+        <v>5448</v>
       </c>
       <c r="D922" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="F922" t="s">
         <v>20</v>
@@ -26317,7 +26339,7 @@
         <v>46146.684259259258</v>
       </c>
       <c r="J922">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K922" t="s">
         <v>11</v>
@@ -26328,25 +26350,25 @@
         <v>37</v>
       </c>
       <c r="C923">
-        <v>5448</v>
+        <v>2439</v>
       </c>
       <c r="D923" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="F923" t="s">
         <v>20</v>
       </c>
       <c r="G923" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H923" s="2">
-        <v>0</v>
+        <v>4.3981481481481484E-3</v>
       </c>
       <c r="I923" s="1">
-        <v>46146.684259259258</v>
+        <v>46146.684953703705</v>
       </c>
       <c r="J923">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K923" t="s">
         <v>11</v>
@@ -26357,10 +26379,10 @@
         <v>37</v>
       </c>
       <c r="C924">
-        <v>2439</v>
+        <v>2432</v>
       </c>
       <c r="D924" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F924" t="s">
         <v>20</v>
@@ -26369,10 +26391,10 @@
         <v>10</v>
       </c>
       <c r="H924" s="2">
-        <v>4.3981481481481484E-3</v>
+        <v>4.8495370370370368E-3</v>
       </c>
       <c r="I924" s="1">
-        <v>46146.684953703705</v>
+        <v>46146.685648148145</v>
       </c>
       <c r="J924">
         <v>0</v>
@@ -26386,10 +26408,10 @@
         <v>37</v>
       </c>
       <c r="C925">
-        <v>2432</v>
+        <v>5447</v>
       </c>
       <c r="D925" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="F925" t="s">
         <v>20</v>
@@ -26398,7 +26420,7 @@
         <v>10</v>
       </c>
       <c r="H925" s="2">
-        <v>4.8495370370370368E-3</v>
+        <v>7.858796296296296E-3</v>
       </c>
       <c r="I925" s="1">
         <v>46146.685648148145</v>
@@ -26415,10 +26437,10 @@
         <v>37</v>
       </c>
       <c r="C926">
-        <v>5447</v>
+        <v>2431</v>
       </c>
       <c r="D926" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="F926" t="s">
         <v>20</v>
@@ -26427,10 +26449,10 @@
         <v>10</v>
       </c>
       <c r="H926" s="2">
-        <v>7.858796296296296E-3</v>
+        <v>7.1527777777777779E-3</v>
       </c>
       <c r="I926" s="1">
-        <v>46146.685648148145</v>
+        <v>46146.686342592591</v>
       </c>
       <c r="J926">
         <v>0</v>
@@ -26444,25 +26466,25 @@
         <v>37</v>
       </c>
       <c r="C927">
-        <v>2431</v>
+        <v>2772</v>
       </c>
       <c r="D927" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="F927" t="s">
         <v>20</v>
       </c>
       <c r="G927" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H927" s="2">
-        <v>7.1527777777777779E-3</v>
+        <v>0</v>
       </c>
       <c r="I927" s="1">
-        <v>46146.686342592591</v>
+        <v>46146.687037037038</v>
       </c>
       <c r="J927">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K927" t="s">
         <v>11</v>
@@ -26473,25 +26495,25 @@
         <v>37</v>
       </c>
       <c r="C928">
-        <v>2772</v>
+        <v>3482</v>
       </c>
       <c r="D928" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F928" t="s">
         <v>20</v>
       </c>
       <c r="G928" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H928" s="2">
-        <v>0</v>
+        <v>5.0462962962962961E-3</v>
       </c>
       <c r="I928" s="1">
         <v>46146.687037037038</v>
       </c>
       <c r="J928">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K928" t="s">
         <v>11</v>
@@ -26502,10 +26524,10 @@
         <v>37</v>
       </c>
       <c r="C929">
-        <v>3482</v>
+        <v>2449</v>
       </c>
       <c r="D929" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="F929" t="s">
         <v>20</v>
@@ -26514,10 +26536,10 @@
         <v>10</v>
       </c>
       <c r="H929" s="2">
-        <v>5.0462962962962961E-3</v>
+        <v>4.8263888888888887E-3</v>
       </c>
       <c r="I929" s="1">
-        <v>46146.687037037038</v>
+        <v>46146.687731481485</v>
       </c>
       <c r="J929">
         <v>0</v>
@@ -26531,25 +26553,25 @@
         <v>37</v>
       </c>
       <c r="C930">
-        <v>2449</v>
+        <v>2418</v>
       </c>
       <c r="D930" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F930" t="s">
         <v>20</v>
       </c>
       <c r="G930" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H930" s="2">
-        <v>4.8263888888888887E-3</v>
+        <v>0</v>
       </c>
       <c r="I930" s="1">
-        <v>46146.687731481485</v>
+        <v>46146.688425925924</v>
       </c>
       <c r="J930">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K930" t="s">
         <v>11</v>
@@ -26560,16 +26582,16 @@
         <v>37</v>
       </c>
       <c r="C931">
-        <v>2418</v>
+        <v>2444</v>
       </c>
       <c r="D931" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F931" t="s">
         <v>20</v>
       </c>
       <c r="G931" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H931" s="2">
         <v>0</v>
@@ -26578,46 +26600,46 @@
         <v>46146.688425925924</v>
       </c>
       <c r="J931">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K931" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="932" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B932" t="s">
-        <v>37</v>
-      </c>
-      <c r="C932">
-        <v>2444</v>
-      </c>
-      <c r="D932" t="s">
-        <v>66</v>
-      </c>
-      <c r="F932" t="s">
+      <c r="H932" s="2"/>
+      <c r="I932" s="1"/>
+      <c r="K932" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="933" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B933" t="s">
+        <v>37</v>
+      </c>
+      <c r="C933">
+        <v>2426</v>
+      </c>
+      <c r="D933" t="s">
+        <v>67</v>
+      </c>
+      <c r="F933" t="s">
         <v>20</v>
       </c>
-      <c r="G932" t="s">
-        <v>12</v>
-      </c>
-      <c r="H932" s="2">
-        <v>0</v>
-      </c>
-      <c r="I932" s="1">
-        <v>46146.688425925924</v>
-      </c>
-      <c r="J932">
-        <v>0</v>
-      </c>
-      <c r="K932" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="933" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H933" s="2"/>
-      <c r="I933" s="1"/>
+      <c r="G933" t="s">
+        <v>13</v>
+      </c>
+      <c r="H933" s="2">
+        <v>0</v>
+      </c>
+      <c r="I933" s="1">
+        <v>46146.689120370371</v>
+      </c>
+      <c r="J933">
+        <v>2</v>
+      </c>
       <c r="K933" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="934" spans="2:11" x14ac:dyDescent="0.3">
@@ -26625,25 +26647,25 @@
         <v>37</v>
       </c>
       <c r="C934">
-        <v>2426</v>
+        <v>4630</v>
       </c>
       <c r="D934" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="F934" t="s">
         <v>20</v>
       </c>
       <c r="G934" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H934" s="2">
-        <v>0</v>
+        <v>5.185185185185185E-3</v>
       </c>
       <c r="I934" s="1">
         <v>46146.689120370371</v>
       </c>
       <c r="J934">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K934" t="s">
         <v>11</v>
@@ -26654,25 +26676,25 @@
         <v>37</v>
       </c>
       <c r="C935">
-        <v>4630</v>
+        <v>2452</v>
       </c>
       <c r="D935" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="F935" t="s">
         <v>20</v>
       </c>
       <c r="G935" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H935" s="2">
-        <v>5.185185185185185E-3</v>
+        <v>0</v>
       </c>
       <c r="I935" s="1">
-        <v>46146.689120370371</v>
+        <v>46146.689814814818</v>
       </c>
       <c r="J935">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K935" t="s">
         <v>11</v>
@@ -26683,25 +26705,25 @@
         <v>37</v>
       </c>
       <c r="C936">
-        <v>2452</v>
+        <v>2447</v>
       </c>
       <c r="D936" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F936" t="s">
         <v>20</v>
       </c>
       <c r="G936" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H936" s="2">
-        <v>0</v>
+        <v>5.6597222222222222E-3</v>
       </c>
       <c r="I936" s="1">
-        <v>46146.689814814818</v>
+        <v>46146.690509259257</v>
       </c>
       <c r="J936">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K936" t="s">
         <v>11</v>
@@ -26712,10 +26734,10 @@
         <v>37</v>
       </c>
       <c r="C937">
-        <v>2447</v>
+        <v>2436</v>
       </c>
       <c r="D937" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F937" t="s">
         <v>20</v>
@@ -26724,7 +26746,7 @@
         <v>10</v>
       </c>
       <c r="H937" s="2">
-        <v>5.6597222222222222E-3</v>
+        <v>7.1180555555555554E-3</v>
       </c>
       <c r="I937" s="1">
         <v>46146.690509259257</v>
@@ -26741,25 +26763,25 @@
         <v>37</v>
       </c>
       <c r="C938">
-        <v>2436</v>
+        <v>2982</v>
       </c>
       <c r="D938" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F938" t="s">
         <v>20</v>
       </c>
       <c r="G938" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H938" s="2">
-        <v>7.1180555555555554E-3</v>
+        <v>0</v>
       </c>
       <c r="I938" s="1">
-        <v>46146.690509259257</v>
+        <v>46146.691203703704</v>
       </c>
       <c r="J938">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K938" t="s">
         <v>11</v>
@@ -26770,25 +26792,25 @@
         <v>37</v>
       </c>
       <c r="C939">
-        <v>2982</v>
+        <v>3854</v>
       </c>
       <c r="D939" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F939" t="s">
         <v>20</v>
       </c>
       <c r="G939" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H939" s="2">
-        <v>0</v>
+        <v>6.030092592592593E-3</v>
       </c>
       <c r="I939" s="1">
-        <v>46146.691203703704</v>
+        <v>46146.69189814815</v>
       </c>
       <c r="J939">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K939" t="s">
         <v>11</v>
@@ -26799,10 +26821,10 @@
         <v>37</v>
       </c>
       <c r="C940">
-        <v>3854</v>
+        <v>4885</v>
       </c>
       <c r="D940" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F940" t="s">
         <v>20</v>
@@ -26817,7 +26839,7 @@
         <v>46146.69189814815</v>
       </c>
       <c r="J940">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K940" t="s">
         <v>11</v>
@@ -26828,25 +26850,25 @@
         <v>37</v>
       </c>
       <c r="C941">
-        <v>4885</v>
+        <v>2423</v>
       </c>
       <c r="D941" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F941" t="s">
         <v>20</v>
       </c>
       <c r="G941" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H941" s="2">
-        <v>0</v>
+        <v>4.4444444444444444E-3</v>
       </c>
       <c r="I941" s="1">
-        <v>46146.69189814815</v>
+        <v>46146.668402777781</v>
       </c>
       <c r="J941">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K941" t="s">
         <v>11</v>
@@ -26857,10 +26879,10 @@
         <v>37</v>
       </c>
       <c r="C942">
-        <v>2423</v>
+        <v>2441</v>
       </c>
       <c r="D942" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F942" t="s">
         <v>20</v>
@@ -26869,10 +26891,10 @@
         <v>10</v>
       </c>
       <c r="H942" s="2">
-        <v>4.4444444444444444E-3</v>
+        <v>3.9814814814814817E-3</v>
       </c>
       <c r="I942" s="1">
-        <v>46146.668402777781</v>
+        <v>46146.66909722222</v>
       </c>
       <c r="J942">
         <v>0</v>
@@ -26886,25 +26908,25 @@
         <v>37</v>
       </c>
       <c r="C943">
-        <v>2441</v>
+        <v>2437</v>
       </c>
       <c r="D943" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F943" t="s">
         <v>20</v>
       </c>
       <c r="G943" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H943" s="2">
-        <v>3.9814814814814817E-3</v>
+        <v>0</v>
       </c>
       <c r="I943" s="1">
         <v>46146.66909722222</v>
       </c>
       <c r="J943">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K943" t="s">
         <v>11</v>
@@ -26915,22 +26937,22 @@
         <v>37</v>
       </c>
       <c r="C944">
-        <v>2437</v>
+        <v>4886</v>
       </c>
       <c r="D944" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="F944" t="s">
         <v>20</v>
       </c>
       <c r="G944" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H944" s="2">
-        <v>0</v>
+        <v>4.6064814814814814E-3</v>
       </c>
       <c r="I944" s="1">
-        <v>46146.66909722222</v>
+        <v>46146.669791666667</v>
       </c>
       <c r="J944">
         <v>1</v>
@@ -26944,10 +26966,10 @@
         <v>37</v>
       </c>
       <c r="C945">
-        <v>4886</v>
+        <v>5188</v>
       </c>
       <c r="D945" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F945" t="s">
         <v>20</v>
@@ -26956,46 +26978,21 @@
         <v>10</v>
       </c>
       <c r="H945" s="2">
-        <v>4.6064814814814814E-3</v>
+        <v>8.7847222222222215E-3</v>
       </c>
       <c r="I945" s="1">
-        <v>46146.669791666667</v>
+        <v>46146.670486111114</v>
       </c>
       <c r="J945">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K945" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="946" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B946" t="s">
-        <v>37</v>
-      </c>
-      <c r="C946">
-        <v>5188</v>
-      </c>
-      <c r="D946" t="s">
-        <v>97</v>
-      </c>
-      <c r="F946" t="s">
-        <v>20</v>
-      </c>
-      <c r="G946" t="s">
-        <v>10</v>
-      </c>
-      <c r="H946" s="2">
-        <v>8.7847222222222215E-3</v>
-      </c>
-      <c r="I946" s="1">
-        <v>46146.670486111114</v>
-      </c>
-      <c r="J946">
-        <v>0</v>
-      </c>
-      <c r="K946" t="s">
-        <v>11</v>
-      </c>
+      <c r="H946" s="2"/>
+      <c r="I946" s="1"/>
     </row>
     <row r="947" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H947" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\All City Tow- TS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\All-City-Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A220432-1431-4372-9410-72F4427BA07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE596AB-3BF9-4017-B7B7-E8A2A0F85F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27423,7 +27423,7 @@
         <v>46175.805208333331</v>
       </c>
       <c r="J959">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K959" t="s">
         <v>11</v>
@@ -27576,7 +27576,7 @@
         <v>46175.807986111111</v>
       </c>
       <c r="J965">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K965" t="s">
         <v>11</v>
@@ -27605,7 +27605,7 @@
         <v>46175.807986111111</v>
       </c>
       <c r="J966">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K966" t="s">
         <v>11</v>
@@ -27634,7 +27634,7 @@
         <v>46175.808680555558</v>
       </c>
       <c r="J967">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K967" t="s">
         <v>11</v>
@@ -27683,16 +27683,16 @@
         <v>35</v>
       </c>
       <c r="G969" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H969" s="2">
-        <v>0</v>
+        <v>1.3113425925925926E-2</v>
       </c>
       <c r="I969" s="1">
         <v>46175.810069444444</v>
       </c>
       <c r="J969">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K969" t="s">
         <v>11</v>
@@ -27874,7 +27874,7 @@
         <v>46175.81354166667</v>
       </c>
       <c r="J976">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K976" t="s">
         <v>11</v>
@@ -27894,10 +27894,10 @@
         <v>35</v>
       </c>
       <c r="G977" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H977">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H977" s="2">
+        <v>2.5879629629629631E-2</v>
       </c>
       <c r="I977" s="1">
         <v>46175.81354166667</v>
@@ -27970,7 +27970,7 @@
         <v>46175.814930555556</v>
       </c>
       <c r="J980">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K980" t="s">
         <v>11</v>
@@ -27999,7 +27999,7 @@
         <v>46175.815625000003</v>
       </c>
       <c r="J981">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K981" t="s">
         <v>11</v>
@@ -28028,7 +28028,7 @@
         <v>46175.815625000003</v>
       </c>
       <c r="J982">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K982" t="s">
         <v>11</v>
@@ -28115,7 +28115,7 @@
         <v>46175.817708333336</v>
       </c>
       <c r="J985">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K985" t="s">
         <v>11</v>
